--- a/artfynd/A 18527-2025 artfynd.xlsx
+++ b/artfynd/A 18527-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124774634</v>
+        <v>124774975</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>462257</v>
+        <v>462275</v>
       </c>
       <c r="R2" t="n">
-        <v>6768691</v>
+        <v>6768714</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124775556</v>
+        <v>124775446</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124774845</v>
+        <v>124782461</v>
       </c>
       <c r="B4" t="n">
-        <v>8447</v>
+        <v>56722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,34 +900,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462271</v>
+        <v>462374</v>
       </c>
       <c r="R4" t="n">
-        <v>6768703</v>
+        <v>6768823</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124770632</v>
+        <v>124777471</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,39 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462182</v>
+        <v>462331</v>
       </c>
       <c r="R5" t="n">
-        <v>6768583</v>
+        <v>6768680</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,11 +1067,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124782461</v>
+        <v>124774634</v>
       </c>
       <c r="B6" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,43 +1105,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>462374</v>
+        <v>462257</v>
       </c>
       <c r="R6" t="n">
-        <v>6768823</v>
+        <v>6768691</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124781969</v>
+        <v>124776376</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>462389</v>
+        <v>462311</v>
       </c>
       <c r="R7" t="n">
-        <v>6768770</v>
+        <v>6768690</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124777178</v>
+        <v>124775405</v>
       </c>
       <c r="B8" t="n">
-        <v>74901</v>
+        <v>57529</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,34 +1313,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>462340</v>
+        <v>462322</v>
       </c>
       <c r="R8" t="n">
-        <v>6768649</v>
+        <v>6768707</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1378,6 +1378,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1404,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124782138</v>
+        <v>124777178</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1420,21 +1425,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462447</v>
+        <v>462340</v>
       </c>
       <c r="R9" t="n">
-        <v>6768805</v>
+        <v>6768649</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124774056</v>
+        <v>124772212</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,34 +1527,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462291</v>
+        <v>462184</v>
       </c>
       <c r="R10" t="n">
-        <v>6768602</v>
+        <v>6768538</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1582,6 +1592,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1608,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124772023</v>
+        <v>124774845</v>
       </c>
       <c r="B11" t="n">
-        <v>57529</v>
+        <v>8447</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1620,43 +1635,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>462234</v>
+        <v>462271</v>
       </c>
       <c r="R11" t="n">
-        <v>6768605</v>
+        <v>6768703</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1689,11 +1699,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1720,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124774494</v>
+        <v>124782169</v>
       </c>
       <c r="B12" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1732,25 +1737,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>462257</v>
+        <v>462456</v>
       </c>
       <c r="R12" t="n">
-        <v>6768691</v>
+        <v>6768800</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1822,10 +1827,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124774975</v>
+        <v>124771314</v>
       </c>
       <c r="B13" t="n">
-        <v>8447</v>
+        <v>57666</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1834,41 +1839,46 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>462275</v>
+        <v>462210</v>
       </c>
       <c r="R13" t="n">
-        <v>6768714</v>
+        <v>6768591</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1898,11 +1908,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1929,10 +1934,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124776376</v>
+        <v>124776291</v>
       </c>
       <c r="B14" t="n">
-        <v>74901</v>
+        <v>57529</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1945,24 +1950,29 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
@@ -2031,7 +2041,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124778521</v>
+        <v>124775105</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2071,10 +2081,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>462386</v>
+        <v>462281</v>
       </c>
       <c r="R15" t="n">
-        <v>6768724</v>
+        <v>6768705</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2111,7 +2121,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Miljöbilder för närområdet. Hygget börjar bakom lågorna</t>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2138,10 +2148,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124773032</v>
+        <v>124774463</v>
       </c>
       <c r="B16" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2154,39 +2164,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>462235</v>
+        <v>462264</v>
       </c>
       <c r="R16" t="n">
-        <v>6768533</v>
+        <v>6768671</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2245,7 +2250,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124774922</v>
+        <v>124778690</v>
       </c>
       <c r="B17" t="n">
         <v>57529</v>
@@ -2290,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>462275</v>
+        <v>462388</v>
       </c>
       <c r="R17" t="n">
-        <v>6768714</v>
+        <v>6768696</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2326,6 +2331,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2352,7 +2362,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124776291</v>
+        <v>124774922</v>
       </c>
       <c r="B18" t="n">
         <v>57529</v>
@@ -2397,10 +2407,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>462311</v>
+        <v>462275</v>
       </c>
       <c r="R18" t="n">
-        <v>6768690</v>
+        <v>6768714</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2459,10 +2469,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124771314</v>
+        <v>124772894</v>
       </c>
       <c r="B19" t="n">
-        <v>57666</v>
+        <v>74901</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2475,42 +2485,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>462210</v>
+        <v>462230</v>
       </c>
       <c r="R19" t="n">
-        <v>6768591</v>
+        <v>6768556</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2566,7 +2571,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124778690</v>
+        <v>124773032</v>
       </c>
       <c r="B20" t="n">
         <v>57529</v>
@@ -2602,7 +2607,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2611,10 +2616,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>462388</v>
+        <v>462235</v>
       </c>
       <c r="R20" t="n">
-        <v>6768696</v>
+        <v>6768533</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2647,11 +2652,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2678,10 +2678,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124775105</v>
+        <v>124774494</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2690,25 +2690,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2718,10 +2718,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>462281</v>
+        <v>462257</v>
       </c>
       <c r="R21" t="n">
-        <v>6768705</v>
+        <v>6768691</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2754,11 +2754,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2785,10 +2780,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124774814</v>
+        <v>124781969</v>
       </c>
       <c r="B22" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2801,39 +2796,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>462257</v>
+        <v>462389</v>
       </c>
       <c r="R22" t="n">
-        <v>6768691</v>
+        <v>6768770</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2892,10 +2882,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124777598</v>
+        <v>124774814</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2908,34 +2898,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>462331</v>
+        <v>462257</v>
       </c>
       <c r="R23" t="n">
-        <v>6768680</v>
+        <v>6768691</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2994,10 +2989,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124776534</v>
+        <v>124781784</v>
       </c>
       <c r="B24" t="n">
-        <v>74901</v>
+        <v>57529</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3010,34 +3005,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>462302</v>
+        <v>462362</v>
       </c>
       <c r="R24" t="n">
-        <v>6768675</v>
+        <v>6768766</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3070,11 +3070,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3101,10 +3096,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124781784</v>
+        <v>124771180</v>
       </c>
       <c r="B25" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3117,39 +3112,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>462362</v>
+        <v>462198</v>
       </c>
       <c r="R25" t="n">
-        <v>6768766</v>
+        <v>6768579</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3208,10 +3198,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124781860</v>
+        <v>124770579</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3224,21 +3214,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3248,10 +3238,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>462362</v>
+        <v>462182</v>
       </c>
       <c r="R26" t="n">
-        <v>6768766</v>
+        <v>6768583</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3284,11 +3274,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3315,7 +3300,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124774189</v>
+        <v>124778521</v>
       </c>
       <c r="B27" t="n">
         <v>78810</v>
@@ -3355,10 +3340,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>462287</v>
+        <v>462386</v>
       </c>
       <c r="R27" t="n">
-        <v>6768630</v>
+        <v>6768724</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3391,6 +3376,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Miljöbilder för närområdet. Hygget börjar bakom lågorna</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3417,10 +3407,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124775405</v>
+        <v>124781860</v>
       </c>
       <c r="B28" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3433,39 +3423,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>462322</v>
+        <v>462362</v>
       </c>
       <c r="R28" t="n">
-        <v>6768707</v>
+        <v>6768766</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3529,10 +3514,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124772212</v>
+        <v>124782138</v>
       </c>
       <c r="B29" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3545,39 +3530,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>462184</v>
+        <v>462447</v>
       </c>
       <c r="R29" t="n">
-        <v>6768538</v>
+        <v>6768805</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3610,11 +3590,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3641,7 +3616,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124777762</v>
+        <v>124772023</v>
       </c>
       <c r="B30" t="n">
         <v>57529</v>
@@ -3677,7 +3652,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3686,10 +3661,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>462331</v>
+        <v>462234</v>
       </c>
       <c r="R30" t="n">
-        <v>6768680</v>
+        <v>6768605</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3726,7 +3701,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Miljöbilder på bland annat angränsande hygge.</t>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3753,10 +3728,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124782169</v>
+        <v>124781915</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3769,34 +3744,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>462456</v>
+        <v>462389</v>
       </c>
       <c r="R31" t="n">
-        <v>6768800</v>
+        <v>6768770</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3855,10 +3835,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124781915</v>
+        <v>124776534</v>
       </c>
       <c r="B32" t="n">
-        <v>57529</v>
+        <v>74901</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3871,39 +3851,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>462389</v>
+        <v>462302</v>
       </c>
       <c r="R32" t="n">
-        <v>6768770</v>
+        <v>6768675</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3936,6 +3911,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3962,10 +3942,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124772894</v>
+        <v>124770632</v>
       </c>
       <c r="B33" t="n">
-        <v>74901</v>
+        <v>57529</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3978,34 +3958,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>462230</v>
+        <v>462182</v>
       </c>
       <c r="R33" t="n">
-        <v>6768556</v>
+        <v>6768583</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4038,6 +4023,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4064,10 +4054,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124770579</v>
+        <v>124774189</v>
       </c>
       <c r="B34" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4080,21 +4070,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4104,10 +4094,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>462182</v>
+        <v>462287</v>
       </c>
       <c r="R34" t="n">
-        <v>6768583</v>
+        <v>6768630</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4166,10 +4156,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124771180</v>
+        <v>124777762</v>
       </c>
       <c r="B35" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4182,34 +4172,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>462198</v>
+        <v>462331</v>
       </c>
       <c r="R35" t="n">
-        <v>6768579</v>
+        <v>6768680</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4242,6 +4237,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Miljöbilder på bland annat angränsande hygge.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4268,7 +4268,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124774463</v>
+        <v>124774056</v>
       </c>
       <c r="B36" t="n">
         <v>78810</v>
@@ -4308,10 +4308,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>462264</v>
+        <v>462291</v>
       </c>
       <c r="R36" t="n">
-        <v>6768671</v>
+        <v>6768602</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>

--- a/artfynd/A 18527-2025 artfynd.xlsx
+++ b/artfynd/A 18527-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AY48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124774975</v>
+        <v>124774189</v>
       </c>
       <c r="B2" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>462275</v>
+        <v>462287</v>
       </c>
       <c r="R2" t="n">
-        <v>6768714</v>
+        <v>6768630</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124775446</v>
+        <v>124782461</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,38 +789,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>462341</v>
+        <v>462374</v>
       </c>
       <c r="R3" t="n">
-        <v>6768708</v>
+        <v>6768823</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124782461</v>
+        <v>124772212</v>
       </c>
       <c r="B4" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,31 +896,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462374</v>
+        <v>462184</v>
       </c>
       <c r="R4" t="n">
-        <v>6768823</v>
+        <v>6768538</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +965,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124777471</v>
+        <v>124776266</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,34 +1012,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462331</v>
+        <v>462311</v>
       </c>
       <c r="R5" t="n">
-        <v>6768680</v>
+        <v>6768690</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124774634</v>
+        <v>124772023</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,34 +1119,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>462257</v>
+        <v>462234</v>
       </c>
       <c r="R6" t="n">
-        <v>6768691</v>
+        <v>6768605</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,6 +1184,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124776376</v>
+        <v>124778690</v>
       </c>
       <c r="B7" t="n">
-        <v>74901</v>
+        <v>57529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,34 +1231,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>462311</v>
+        <v>462388</v>
       </c>
       <c r="R7" t="n">
-        <v>6768690</v>
+        <v>6768696</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,6 +1296,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,7 +1327,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124775405</v>
+        <v>124781784</v>
       </c>
       <c r="B8" t="n">
         <v>57529</v>
@@ -1342,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>462322</v>
+        <v>462362</v>
       </c>
       <c r="R8" t="n">
-        <v>6768707</v>
+        <v>6768766</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1378,11 +1408,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124777178</v>
+        <v>124774558</v>
       </c>
       <c r="B9" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,21 +1450,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1474,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462340</v>
+        <v>462257</v>
       </c>
       <c r="R9" t="n">
-        <v>6768649</v>
+        <v>6768691</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1511,10 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124772212</v>
+        <v>124781860</v>
       </c>
       <c r="B10" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,39 +1552,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462184</v>
+        <v>462362</v>
       </c>
       <c r="R10" t="n">
-        <v>6768538</v>
+        <v>6768766</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1623,10 +1643,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124774845</v>
+        <v>124775105</v>
       </c>
       <c r="B11" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1635,25 +1655,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>462271</v>
+        <v>462281</v>
       </c>
       <c r="R11" t="n">
-        <v>6768703</v>
+        <v>6768705</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,6 +1719,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1725,7 +1750,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124782169</v>
+        <v>124777598</v>
       </c>
       <c r="B12" t="n">
         <v>78810</v>
@@ -1765,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>462456</v>
+        <v>462331</v>
       </c>
       <c r="R12" t="n">
-        <v>6768800</v>
+        <v>6768680</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1827,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124771314</v>
+        <v>124775405</v>
       </c>
       <c r="B13" t="n">
-        <v>57666</v>
+        <v>57529</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1843,27 +1868,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1872,13 +1897,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>462210</v>
+        <v>462322</v>
       </c>
       <c r="R13" t="n">
-        <v>6768591</v>
+        <v>6768707</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1908,6 +1933,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1934,10 +1964,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124776291</v>
+        <v>124781969</v>
       </c>
       <c r="B14" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1950,39 +1980,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>462311</v>
+        <v>462389</v>
       </c>
       <c r="R14" t="n">
-        <v>6768690</v>
+        <v>6768770</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2041,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124775105</v>
+        <v>124770579</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2057,21 +2082,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2081,10 +2106,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>462281</v>
+        <v>462182</v>
       </c>
       <c r="R15" t="n">
-        <v>6768705</v>
+        <v>6768583</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2117,11 +2142,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2148,7 +2168,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124774463</v>
+        <v>124775556</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2188,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>462264</v>
+        <v>462341</v>
       </c>
       <c r="R16" t="n">
-        <v>6768671</v>
+        <v>6768708</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2250,7 +2270,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124778690</v>
+        <v>124770632</v>
       </c>
       <c r="B17" t="n">
         <v>57529</v>
@@ -2295,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>462388</v>
+        <v>462182</v>
       </c>
       <c r="R17" t="n">
-        <v>6768696</v>
+        <v>6768583</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2335,7 +2355,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Miljöbilder</t>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2362,10 +2382,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124774922</v>
+        <v>124774494</v>
       </c>
       <c r="B18" t="n">
-        <v>57529</v>
+        <v>8447</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2374,43 +2394,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>462275</v>
+        <v>462257</v>
       </c>
       <c r="R18" t="n">
-        <v>6768714</v>
+        <v>6768691</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2469,10 +2484,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124772894</v>
+        <v>124774975</v>
       </c>
       <c r="B19" t="n">
-        <v>74901</v>
+        <v>8447</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2481,25 +2496,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2509,10 +2524,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>462230</v>
+        <v>462275</v>
       </c>
       <c r="R19" t="n">
-        <v>6768556</v>
+        <v>6768714</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2545,6 +2560,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2571,10 +2591,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124773032</v>
+        <v>124774845</v>
       </c>
       <c r="B20" t="n">
-        <v>57529</v>
+        <v>8447</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2583,43 +2603,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>462235</v>
+        <v>462271</v>
       </c>
       <c r="R20" t="n">
-        <v>6768533</v>
+        <v>6768703</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2678,10 +2693,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124774494</v>
+        <v>124774056</v>
       </c>
       <c r="B21" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2690,25 +2705,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2718,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>462257</v>
+        <v>462291</v>
       </c>
       <c r="R21" t="n">
-        <v>6768691</v>
+        <v>6768602</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2780,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124781969</v>
+        <v>124772894</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2796,21 +2811,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2820,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>462389</v>
+        <v>462230</v>
       </c>
       <c r="R22" t="n">
-        <v>6768770</v>
+        <v>6768556</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2882,10 +2897,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124774814</v>
+        <v>124774463</v>
       </c>
       <c r="B23" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2898,39 +2913,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>462257</v>
+        <v>462264</v>
       </c>
       <c r="R23" t="n">
-        <v>6768691</v>
+        <v>6768671</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2989,10 +2999,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124781784</v>
+        <v>124776376</v>
       </c>
       <c r="B24" t="n">
-        <v>57529</v>
+        <v>74901</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3005,39 +3015,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>462362</v>
+        <v>462311</v>
       </c>
       <c r="R24" t="n">
-        <v>6768766</v>
+        <v>6768690</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3096,10 +3101,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124771180</v>
+        <v>124777762</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3112,34 +3117,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>462198</v>
+        <v>462331</v>
       </c>
       <c r="R25" t="n">
-        <v>6768579</v>
+        <v>6768680</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3172,6 +3182,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Miljöbilder på bland annat angränsande hygge.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3198,10 +3213,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124770579</v>
+        <v>124781915</v>
       </c>
       <c r="B26" t="n">
-        <v>74901</v>
+        <v>57529</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3214,34 +3229,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>462182</v>
+        <v>462389</v>
       </c>
       <c r="R26" t="n">
-        <v>6768583</v>
+        <v>6768770</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3300,10 +3320,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124778521</v>
+        <v>124773032</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3316,34 +3336,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>462386</v>
+        <v>462235</v>
       </c>
       <c r="R27" t="n">
-        <v>6768724</v>
+        <v>6768533</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3376,11 +3401,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Miljöbilder för närområdet. Hygget börjar bakom lågorna</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3407,7 +3427,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124781860</v>
+        <v>124782169</v>
       </c>
       <c r="B28" t="n">
         <v>78810</v>
@@ -3447,10 +3467,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>462362</v>
+        <v>462456</v>
       </c>
       <c r="R28" t="n">
-        <v>6768766</v>
+        <v>6768800</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3483,11 +3503,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3514,10 +3529,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124782138</v>
+        <v>124774922</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3530,34 +3545,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>462447</v>
+        <v>462275</v>
       </c>
       <c r="R29" t="n">
-        <v>6768805</v>
+        <v>6768714</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3616,10 +3636,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124772023</v>
+        <v>124771180</v>
       </c>
       <c r="B30" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3632,39 +3652,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>462234</v>
+        <v>462198</v>
       </c>
       <c r="R30" t="n">
-        <v>6768605</v>
+        <v>6768579</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3697,11 +3712,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3728,7 +3738,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124781915</v>
+        <v>124774814</v>
       </c>
       <c r="B31" t="n">
         <v>57529</v>
@@ -3764,7 +3774,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3773,10 +3783,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>462389</v>
+        <v>462257</v>
       </c>
       <c r="R31" t="n">
-        <v>6768770</v>
+        <v>6768691</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3835,10 +3845,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124776534</v>
+        <v>124778521</v>
       </c>
       <c r="B32" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3851,21 +3861,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3875,10 +3885,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>462302</v>
+        <v>462386</v>
       </c>
       <c r="R32" t="n">
-        <v>6768675</v>
+        <v>6768724</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3915,7 +3925,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Miljöbilder</t>
+          <t>Miljöbilder för närområdet. Hygget börjar bakom lågorna</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3942,10 +3952,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124770632</v>
+        <v>124782138</v>
       </c>
       <c r="B33" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3958,39 +3968,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>462182</v>
+        <v>462447</v>
       </c>
       <c r="R33" t="n">
-        <v>6768583</v>
+        <v>6768805</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4023,11 +4028,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4054,10 +4054,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124774189</v>
+        <v>124776534</v>
       </c>
       <c r="B34" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4070,21 +4070,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4094,10 +4094,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>462287</v>
+        <v>462302</v>
       </c>
       <c r="R34" t="n">
-        <v>6768630</v>
+        <v>6768675</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4130,6 +4130,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4156,10 +4161,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124777762</v>
+        <v>124777178</v>
       </c>
       <c r="B35" t="n">
-        <v>57529</v>
+        <v>74901</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4172,39 +4177,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>462331</v>
+        <v>462340</v>
       </c>
       <c r="R35" t="n">
-        <v>6768680</v>
+        <v>6768649</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4237,11 +4237,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Miljöbilder på bland annat angränsande hygge.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4268,10 +4263,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124774056</v>
+        <v>124771314</v>
       </c>
       <c r="B36" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4284,37 +4279,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>462291</v>
+        <v>462210</v>
       </c>
       <c r="R36" t="n">
-        <v>6768602</v>
+        <v>6768591</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4367,6 +4367,1275 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>124834191</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79428</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Salutjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>462814</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6769220</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>124836148</v>
+      </c>
+      <c r="B38" t="n">
+        <v>78546</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Salutjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>462741</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6769142</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>124838423</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57529</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Lädsån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>462456</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6768914</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>124836445</v>
+      </c>
+      <c r="B40" t="n">
+        <v>78546</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Salutjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>462712</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6769143</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>124836354</v>
+      </c>
+      <c r="B41" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Salutjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>462712</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6769143</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Miljöbild, garnlav i äldre tall.</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>124833451</v>
+      </c>
+      <c r="B42" t="n">
+        <v>8447</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Salutjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>462818</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6769164</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>124834205</v>
+      </c>
+      <c r="B43" t="n">
+        <v>78546</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Salutjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>462814</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6769220</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>124833941</v>
+      </c>
+      <c r="B44" t="n">
+        <v>8447</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Salutjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>462816</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6769191</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Miljöbilder för närområdet.</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>124835714</v>
+      </c>
+      <c r="B45" t="n">
+        <v>8447</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Salutjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>462814</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6769220</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>124835908</v>
+      </c>
+      <c r="B46" t="n">
+        <v>8447</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Salutjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>462741</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6769142</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Miljöbilder för närområdet.</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>124836527</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79399</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Salutjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>462712</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6769143</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>124825418</v>
+      </c>
+      <c r="B48" t="n">
+        <v>8447</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Salutjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>462844</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6769302</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18527-2025 artfynd.xlsx
+++ b/artfynd/A 18527-2025 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124782461</v>
+        <v>124772212</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,31 +789,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>462374</v>
+        <v>462184</v>
       </c>
       <c r="R3" t="n">
-        <v>6768823</v>
+        <v>6768538</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124772212</v>
+        <v>124782461</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,31 +901,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -929,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462184</v>
+        <v>462374</v>
       </c>
       <c r="R4" t="n">
-        <v>6768538</v>
+        <v>6768823</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,11 +970,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -2270,10 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124770632</v>
+        <v>124774975</v>
       </c>
       <c r="B17" t="n">
-        <v>57529</v>
+        <v>8447</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2282,43 +2282,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>462182</v>
+        <v>462275</v>
       </c>
       <c r="R17" t="n">
-        <v>6768583</v>
+        <v>6768714</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2355,7 +2350,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Miljöbilder.</t>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2382,10 +2377,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124774494</v>
+        <v>124770632</v>
       </c>
       <c r="B18" t="n">
-        <v>8447</v>
+        <v>57529</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2394,38 +2389,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>462257</v>
+        <v>462182</v>
       </c>
       <c r="R18" t="n">
-        <v>6768691</v>
+        <v>6768583</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2458,6 +2458,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2484,7 +2489,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124774975</v>
+        <v>124774494</v>
       </c>
       <c r="B19" t="n">
         <v>8447</v>
@@ -2524,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>462275</v>
+        <v>462257</v>
       </c>
       <c r="R19" t="n">
-        <v>6768714</v>
+        <v>6768691</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2560,11 +2565,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2591,10 +2591,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124774845</v>
+        <v>124774056</v>
       </c>
       <c r="B20" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2603,25 +2603,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2631,10 +2631,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>462271</v>
+        <v>462291</v>
       </c>
       <c r="R20" t="n">
-        <v>6768703</v>
+        <v>6768602</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2693,10 +2693,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124774056</v>
+        <v>124774845</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2705,25 +2705,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>462291</v>
+        <v>462271</v>
       </c>
       <c r="R21" t="n">
-        <v>6768602</v>
+        <v>6768703</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 18527-2025 artfynd.xlsx
+++ b/artfynd/A 18527-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124774189</v>
+        <v>124776291</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>462287</v>
+        <v>462311</v>
       </c>
       <c r="R2" t="n">
-        <v>6768630</v>
+        <v>6768690</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124772212</v>
+        <v>124771180</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,39 +798,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>462184</v>
+        <v>462198</v>
       </c>
       <c r="R3" t="n">
-        <v>6768538</v>
+        <v>6768579</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124782461</v>
+        <v>124774189</v>
       </c>
       <c r="B4" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,43 +896,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462374</v>
+        <v>462287</v>
       </c>
       <c r="R4" t="n">
-        <v>6768823</v>
+        <v>6768630</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124776266</v>
+        <v>124774845</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>8447</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1008,43 +998,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462311</v>
+        <v>462271</v>
       </c>
       <c r="R5" t="n">
-        <v>6768690</v>
+        <v>6768703</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124772023</v>
+        <v>124774494</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>8447</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,43 +1100,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>462234</v>
+        <v>462257</v>
       </c>
       <c r="R6" t="n">
-        <v>6768605</v>
+        <v>6768691</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,11 +1164,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124778690</v>
+        <v>124770632</v>
       </c>
       <c r="B7" t="n">
         <v>57529</v>
@@ -1260,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>462388</v>
+        <v>462182</v>
       </c>
       <c r="R7" t="n">
-        <v>6768696</v>
+        <v>6768583</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1275,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Miljöbilder</t>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124781784</v>
+        <v>124771314</v>
       </c>
       <c r="B8" t="n">
-        <v>57529</v>
+        <v>57666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,27 +1318,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1372,13 +1347,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>462362</v>
+        <v>462210</v>
       </c>
       <c r="R8" t="n">
-        <v>6768766</v>
+        <v>6768591</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1434,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124774558</v>
+        <v>124776376</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1450,21 +1425,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1474,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462257</v>
+        <v>462311</v>
       </c>
       <c r="R9" t="n">
-        <v>6768691</v>
+        <v>6768690</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124781860</v>
+        <v>124772212</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1552,34 +1527,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462362</v>
+        <v>462184</v>
       </c>
       <c r="R10" t="n">
-        <v>6768766</v>
+        <v>6768538</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1643,7 +1623,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124775105</v>
+        <v>124781860</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1683,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>462281</v>
+        <v>462362</v>
       </c>
       <c r="R11" t="n">
-        <v>6768705</v>
+        <v>6768766</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1750,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124777598</v>
+        <v>124782461</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1762,38 +1742,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>462331</v>
+        <v>462374</v>
       </c>
       <c r="R12" t="n">
-        <v>6768680</v>
+        <v>6768823</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1852,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124775405</v>
+        <v>124778521</v>
       </c>
       <c r="B13" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1868,39 +1853,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>462322</v>
+        <v>462386</v>
       </c>
       <c r="R13" t="n">
-        <v>6768707</v>
+        <v>6768724</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1937,7 +1917,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Miljöbilder</t>
+          <t>Miljöbilder för närområdet. Hygget börjar bakom lågorna</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1964,10 +1944,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124781969</v>
+        <v>124776534</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1980,21 +1960,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2004,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>462389</v>
+        <v>462302</v>
       </c>
       <c r="R14" t="n">
-        <v>6768770</v>
+        <v>6768675</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2040,6 +2020,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124770579</v>
+        <v>124777598</v>
       </c>
       <c r="B15" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2082,21 +2067,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2106,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>462182</v>
+        <v>462331</v>
       </c>
       <c r="R15" t="n">
-        <v>6768583</v>
+        <v>6768680</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2168,7 +2153,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124775556</v>
+        <v>124774558</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2208,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>462341</v>
+        <v>462257</v>
       </c>
       <c r="R16" t="n">
-        <v>6768708</v>
+        <v>6768691</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2270,10 +2255,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124774975</v>
+        <v>124782169</v>
       </c>
       <c r="B17" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2282,25 +2267,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2310,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>462275</v>
+        <v>462456</v>
       </c>
       <c r="R17" t="n">
-        <v>6768714</v>
+        <v>6768800</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2346,11 +2331,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,10 +2357,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124770632</v>
+        <v>124774056</v>
       </c>
       <c r="B18" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2393,39 +2373,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>462182</v>
+        <v>462291</v>
       </c>
       <c r="R18" t="n">
-        <v>6768583</v>
+        <v>6768602</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2458,11 +2433,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2489,10 +2459,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124774494</v>
+        <v>124774463</v>
       </c>
       <c r="B19" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2501,25 +2471,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2529,10 +2499,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>462257</v>
+        <v>462264</v>
       </c>
       <c r="R19" t="n">
-        <v>6768691</v>
+        <v>6768671</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2591,7 +2561,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124774056</v>
+        <v>124775105</v>
       </c>
       <c r="B20" t="n">
         <v>78810</v>
@@ -2631,10 +2601,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>462291</v>
+        <v>462281</v>
       </c>
       <c r="R20" t="n">
-        <v>6768602</v>
+        <v>6768705</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2667,6 +2637,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2693,7 +2668,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124774845</v>
+        <v>124774975</v>
       </c>
       <c r="B21" t="n">
         <v>8447</v>
@@ -2733,10 +2708,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>462271</v>
+        <v>462275</v>
       </c>
       <c r="R21" t="n">
-        <v>6768703</v>
+        <v>6768714</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2769,6 +2744,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2795,10 +2775,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124772894</v>
+        <v>124774814</v>
       </c>
       <c r="B22" t="n">
-        <v>74901</v>
+        <v>57529</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2811,34 +2791,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>462230</v>
+        <v>462257</v>
       </c>
       <c r="R22" t="n">
-        <v>6768556</v>
+        <v>6768691</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2897,10 +2882,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124774463</v>
+        <v>124777762</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2913,34 +2898,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>462264</v>
+        <v>462331</v>
       </c>
       <c r="R23" t="n">
-        <v>6768671</v>
+        <v>6768680</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2973,6 +2963,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Miljöbilder på bland annat angränsande hygge.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2999,10 +2994,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124776376</v>
+        <v>124781915</v>
       </c>
       <c r="B24" t="n">
-        <v>74901</v>
+        <v>57529</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3015,34 +3010,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>462311</v>
+        <v>462389</v>
       </c>
       <c r="R24" t="n">
-        <v>6768690</v>
+        <v>6768770</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3101,7 +3101,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124777762</v>
+        <v>124775405</v>
       </c>
       <c r="B25" t="n">
         <v>57529</v>
@@ -3146,10 +3146,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>462331</v>
+        <v>462322</v>
       </c>
       <c r="R25" t="n">
-        <v>6768680</v>
+        <v>6768707</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3186,7 +3186,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Miljöbilder på bland annat angränsande hygge.</t>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3213,10 +3213,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124781915</v>
+        <v>124777178</v>
       </c>
       <c r="B26" t="n">
-        <v>57529</v>
+        <v>74901</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3229,39 +3229,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>462389</v>
+        <v>462340</v>
       </c>
       <c r="R26" t="n">
-        <v>6768770</v>
+        <v>6768649</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3320,7 +3315,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124773032</v>
+        <v>124781784</v>
       </c>
       <c r="B27" t="n">
         <v>57529</v>
@@ -3356,7 +3351,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3365,10 +3360,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>462235</v>
+        <v>462362</v>
       </c>
       <c r="R27" t="n">
-        <v>6768533</v>
+        <v>6768766</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3427,7 +3422,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124782169</v>
+        <v>124782138</v>
       </c>
       <c r="B28" t="n">
         <v>78810</v>
@@ -3467,10 +3462,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>462456</v>
+        <v>462447</v>
       </c>
       <c r="R28" t="n">
-        <v>6768800</v>
+        <v>6768805</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3529,10 +3524,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124774922</v>
+        <v>124775446</v>
       </c>
       <c r="B29" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3545,39 +3540,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>462275</v>
+        <v>462341</v>
       </c>
       <c r="R29" t="n">
-        <v>6768714</v>
+        <v>6768708</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3636,10 +3626,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124771180</v>
+        <v>124773032</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3652,34 +3642,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>462198</v>
+        <v>462235</v>
       </c>
       <c r="R30" t="n">
-        <v>6768579</v>
+        <v>6768533</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3738,10 +3733,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124774814</v>
+        <v>124781969</v>
       </c>
       <c r="B31" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3754,39 +3749,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>462257</v>
+        <v>462389</v>
       </c>
       <c r="R31" t="n">
-        <v>6768691</v>
+        <v>6768770</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3845,10 +3835,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124778521</v>
+        <v>124772894</v>
       </c>
       <c r="B32" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3861,21 +3851,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3885,10 +3875,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>462386</v>
+        <v>462230</v>
       </c>
       <c r="R32" t="n">
-        <v>6768724</v>
+        <v>6768556</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3921,11 +3911,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Miljöbilder för närområdet. Hygget börjar bakom lågorna</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3952,10 +3937,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124782138</v>
+        <v>124770579</v>
       </c>
       <c r="B33" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3968,21 +3953,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3992,10 +3977,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>462447</v>
+        <v>462182</v>
       </c>
       <c r="R33" t="n">
-        <v>6768805</v>
+        <v>6768583</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4054,10 +4039,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124776534</v>
+        <v>124778690</v>
       </c>
       <c r="B34" t="n">
-        <v>74901</v>
+        <v>57529</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4070,34 +4055,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>462302</v>
+        <v>462388</v>
       </c>
       <c r="R34" t="n">
-        <v>6768675</v>
+        <v>6768696</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4161,10 +4151,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124777178</v>
+        <v>124774922</v>
       </c>
       <c r="B35" t="n">
-        <v>74901</v>
+        <v>57529</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4177,34 +4167,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>462340</v>
+        <v>462275</v>
       </c>
       <c r="R35" t="n">
-        <v>6768649</v>
+        <v>6768714</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4263,10 +4258,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124771314</v>
+        <v>124772023</v>
       </c>
       <c r="B36" t="n">
-        <v>57666</v>
+        <v>57529</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4279,27 +4274,27 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4308,13 +4303,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>462210</v>
+        <v>462234</v>
       </c>
       <c r="R36" t="n">
-        <v>6768591</v>
+        <v>6768605</v>
       </c>
       <c r="S36" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4344,6 +4339,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4370,10 +4370,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124834191</v>
+        <v>124836148</v>
       </c>
       <c r="B37" t="n">
-        <v>79428</v>
+        <v>78546</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4386,21 +4386,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4410,10 +4410,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>462814</v>
+        <v>462741</v>
       </c>
       <c r="R37" t="n">
-        <v>6769220</v>
+        <v>6769142</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4446,6 +4446,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4472,7 +4477,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124836148</v>
+        <v>124836445</v>
       </c>
       <c r="B38" t="n">
         <v>78546</v>
@@ -4512,10 +4517,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>462741</v>
+        <v>462712</v>
       </c>
       <c r="R38" t="n">
-        <v>6769142</v>
+        <v>6769143</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4579,10 +4584,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124838423</v>
+        <v>124833451</v>
       </c>
       <c r="B39" t="n">
-        <v>57529</v>
+        <v>8447</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4591,38 +4596,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lädsån, Dlr</t>
+          <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>462456</v>
+        <v>462818</v>
       </c>
       <c r="R39" t="n">
-        <v>6768914</v>
+        <v>6769164</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4655,11 +4660,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4686,10 +4686,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124836445</v>
+        <v>124835908</v>
       </c>
       <c r="B40" t="n">
-        <v>78546</v>
+        <v>8447</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4698,25 +4698,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4726,10 +4726,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>462712</v>
+        <v>462741</v>
       </c>
       <c r="R40" t="n">
-        <v>6769143</v>
+        <v>6769142</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Miljöbild</t>
+          <t>Miljöbilder för närområdet.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4793,10 +4793,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124836354</v>
+        <v>124838423</v>
       </c>
       <c r="B41" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4809,34 +4809,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Salutjärnen, Dlr</t>
+          <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>462712</v>
+        <v>462456</v>
       </c>
       <c r="R41" t="n">
-        <v>6769143</v>
+        <v>6768914</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4873,7 +4873,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Miljöbild, garnlav i äldre tall.</t>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4900,7 +4900,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124833451</v>
+        <v>124825418</v>
       </c>
       <c r="B42" t="n">
         <v>8447</v>
@@ -4940,10 +4940,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>462818</v>
+        <v>462844</v>
       </c>
       <c r="R42" t="n">
-        <v>6769164</v>
+        <v>6769302</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5216,10 +5216,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124835714</v>
+        <v>124835204</v>
       </c>
       <c r="B45" t="n">
-        <v>8447</v>
+        <v>79428</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5228,25 +5228,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5323,7 +5323,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124835908</v>
+        <v>124835714</v>
       </c>
       <c r="B46" t="n">
         <v>8447</v>
@@ -5363,10 +5363,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>462741</v>
+        <v>462814</v>
       </c>
       <c r="R46" t="n">
-        <v>6769142</v>
+        <v>6769220</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Miljöbilder för närområdet.</t>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5537,10 +5537,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124825418</v>
+        <v>124836271</v>
       </c>
       <c r="B48" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5549,25 +5549,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5577,10 +5577,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>462844</v>
+        <v>462712</v>
       </c>
       <c r="R48" t="n">
-        <v>6769302</v>
+        <v>6769143</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5613,6 +5613,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 18527-2025 artfynd.xlsx
+++ b/artfynd/A 18527-2025 artfynd.xlsx
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124774845</v>
+        <v>124770632</v>
       </c>
       <c r="B5" t="n">
-        <v>8447</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,38 +998,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462271</v>
+        <v>462182</v>
       </c>
       <c r="R5" t="n">
-        <v>6768703</v>
+        <v>6768583</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,6 +1067,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124774494</v>
+        <v>124774845</v>
       </c>
       <c r="B6" t="n">
         <v>8447</v>
@@ -1128,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>462257</v>
+        <v>462271</v>
       </c>
       <c r="R6" t="n">
-        <v>6768691</v>
+        <v>6768703</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124770632</v>
+        <v>124774494</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>8447</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,43 +1212,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>462182</v>
+        <v>462257</v>
       </c>
       <c r="R7" t="n">
-        <v>6768583</v>
+        <v>6768691</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,11 +1276,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1409,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124776376</v>
+        <v>124772212</v>
       </c>
       <c r="B9" t="n">
-        <v>74901</v>
+        <v>57529</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,34 +1425,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462311</v>
+        <v>462184</v>
       </c>
       <c r="R9" t="n">
-        <v>6768690</v>
+        <v>6768538</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,6 +1490,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1511,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124772212</v>
+        <v>124776376</v>
       </c>
       <c r="B10" t="n">
-        <v>57529</v>
+        <v>74901</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,39 +1537,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462184</v>
+        <v>462311</v>
       </c>
       <c r="R10" t="n">
-        <v>6768538</v>
+        <v>6768690</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,11 +1597,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1837,7 +1837,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124778521</v>
+        <v>124777598</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>462386</v>
+        <v>462331</v>
       </c>
       <c r="R13" t="n">
-        <v>6768724</v>
+        <v>6768680</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1913,11 +1913,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Miljöbilder för närområdet. Hygget börjar bakom lågorna</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1944,10 +1939,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124776534</v>
+        <v>124778521</v>
       </c>
       <c r="B14" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1960,21 +1955,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1984,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>462302</v>
+        <v>462386</v>
       </c>
       <c r="R14" t="n">
-        <v>6768675</v>
+        <v>6768724</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2024,7 +2019,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Miljöbilder</t>
+          <t>Miljöbilder för närområdet. Hygget börjar bakom lågorna</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2051,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124777598</v>
+        <v>124776534</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2067,21 +2062,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2091,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>462331</v>
+        <v>462302</v>
       </c>
       <c r="R15" t="n">
-        <v>6768680</v>
+        <v>6768675</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2127,6 +2122,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2668,10 +2668,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124774975</v>
+        <v>124774814</v>
       </c>
       <c r="B21" t="n">
-        <v>8447</v>
+        <v>57529</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2680,38 +2680,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>462275</v>
+        <v>462257</v>
       </c>
       <c r="R21" t="n">
-        <v>6768714</v>
+        <v>6768691</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2744,11 +2749,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2775,10 +2775,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124774814</v>
+        <v>124774975</v>
       </c>
       <c r="B22" t="n">
-        <v>57529</v>
+        <v>8447</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2787,43 +2787,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>462257</v>
+        <v>462275</v>
       </c>
       <c r="R22" t="n">
-        <v>6768691</v>
+        <v>6768714</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2856,6 +2851,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3315,10 +3315,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124781784</v>
+        <v>124782138</v>
       </c>
       <c r="B27" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3331,39 +3331,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>462362</v>
+        <v>462447</v>
       </c>
       <c r="R27" t="n">
-        <v>6768766</v>
+        <v>6768805</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3422,10 +3417,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124782138</v>
+        <v>124781784</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3438,34 +3433,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>462447</v>
+        <v>462362</v>
       </c>
       <c r="R28" t="n">
-        <v>6768805</v>
+        <v>6768766</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -5323,10 +5323,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124835714</v>
+        <v>124836271</v>
       </c>
       <c r="B46" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5335,25 +5335,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5363,10 +5363,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>462814</v>
+        <v>462712</v>
       </c>
       <c r="R46" t="n">
-        <v>6769220</v>
+        <v>6769143</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Miljöbild</t>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5430,10 +5430,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124836527</v>
+        <v>124835714</v>
       </c>
       <c r="B47" t="n">
-        <v>79399</v>
+        <v>8447</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5442,25 +5442,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5470,10 +5470,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>462712</v>
+        <v>462814</v>
       </c>
       <c r="R47" t="n">
-        <v>6769143</v>
+        <v>6769220</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5537,10 +5537,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124836271</v>
+        <v>124836527</v>
       </c>
       <c r="B48" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5553,21 +5553,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5617,7 +5617,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Miljöbilder</t>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 18527-2025 artfynd.xlsx
+++ b/artfynd/A 18527-2025 artfynd.xlsx
@@ -1409,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124772212</v>
+        <v>124776376</v>
       </c>
       <c r="B9" t="n">
-        <v>57529</v>
+        <v>74901</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,39 +1425,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462184</v>
+        <v>462311</v>
       </c>
       <c r="R9" t="n">
-        <v>6768538</v>
+        <v>6768690</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,11 +1485,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124776376</v>
+        <v>124772212</v>
       </c>
       <c r="B10" t="n">
-        <v>74901</v>
+        <v>57529</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,34 +1527,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462311</v>
+        <v>462184</v>
       </c>
       <c r="R10" t="n">
-        <v>6768690</v>
+        <v>6768538</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,6 +1592,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1837,7 +1837,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124777598</v>
+        <v>124778521</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>462331</v>
+        <v>462386</v>
       </c>
       <c r="R13" t="n">
-        <v>6768680</v>
+        <v>6768724</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1913,6 +1913,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Miljöbilder för närområdet. Hygget börjar bakom lågorna</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1939,10 +1944,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124778521</v>
+        <v>124776534</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1955,21 +1960,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1979,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>462386</v>
+        <v>462302</v>
       </c>
       <c r="R14" t="n">
-        <v>6768724</v>
+        <v>6768675</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,7 +2024,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Miljöbilder för närområdet. Hygget börjar bakom lågorna</t>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2046,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124776534</v>
+        <v>124777598</v>
       </c>
       <c r="B15" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2062,21 +2067,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>462302</v>
+        <v>462331</v>
       </c>
       <c r="R15" t="n">
-        <v>6768675</v>
+        <v>6768680</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2122,11 +2127,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -3315,10 +3315,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124782138</v>
+        <v>124781784</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3331,34 +3331,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>462447</v>
+        <v>462362</v>
       </c>
       <c r="R27" t="n">
-        <v>6768805</v>
+        <v>6768766</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3417,10 +3422,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124781784</v>
+        <v>124782138</v>
       </c>
       <c r="B28" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3433,39 +3438,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>462362</v>
+        <v>462447</v>
       </c>
       <c r="R28" t="n">
-        <v>6768766</v>
+        <v>6768805</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3524,10 +3524,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124775446</v>
+        <v>124773032</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3540,34 +3540,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>462341</v>
+        <v>462235</v>
       </c>
       <c r="R29" t="n">
-        <v>6768708</v>
+        <v>6768533</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3626,10 +3631,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124773032</v>
+        <v>124775446</v>
       </c>
       <c r="B30" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3642,39 +3647,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>462235</v>
+        <v>462341</v>
       </c>
       <c r="R30" t="n">
-        <v>6768533</v>
+        <v>6768708</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 18527-2025 artfynd.xlsx
+++ b/artfynd/A 18527-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124774189</v>
+        <v>124774922</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>462287</v>
+        <v>462275</v>
       </c>
       <c r="R2" t="n">
-        <v>6768630</v>
+        <v>6768714</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124777598</v>
+        <v>124774814</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +798,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>462331</v>
+        <v>462257</v>
       </c>
       <c r="R3" t="n">
-        <v>6768680</v>
+        <v>6768691</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124782169</v>
+        <v>124781784</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,34 +905,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462456</v>
+        <v>462362</v>
       </c>
       <c r="R4" t="n">
-        <v>6768800</v>
+        <v>6768766</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124770632</v>
+        <v>124776266</v>
       </c>
       <c r="B5" t="n">
         <v>57529</v>
@@ -1026,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462182</v>
+        <v>462311</v>
       </c>
       <c r="R5" t="n">
-        <v>6768583</v>
+        <v>6768690</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,11 +1077,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124774975</v>
+        <v>124772212</v>
       </c>
       <c r="B6" t="n">
-        <v>8447</v>
+        <v>57529</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,38 +1115,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>462275</v>
+        <v>462184</v>
       </c>
       <c r="R6" t="n">
-        <v>6768714</v>
+        <v>6768538</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124774634</v>
+        <v>124777762</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,34 +1231,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>462257</v>
+        <v>462331</v>
       </c>
       <c r="R7" t="n">
-        <v>6768691</v>
+        <v>6768680</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,6 +1296,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Miljöbilder på bland annat angränsande hygge.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124772212</v>
+        <v>124774975</v>
       </c>
       <c r="B8" t="n">
-        <v>57529</v>
+        <v>8447</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1314,43 +1339,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>462184</v>
+        <v>462275</v>
       </c>
       <c r="R8" t="n">
-        <v>6768538</v>
+        <v>6768714</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124770579</v>
+        <v>124774056</v>
       </c>
       <c r="B9" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,21 +1450,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1474,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462182</v>
+        <v>462291</v>
       </c>
       <c r="R9" t="n">
-        <v>6768583</v>
+        <v>6768602</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,10 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124778690</v>
+        <v>124774189</v>
       </c>
       <c r="B10" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1532,39 +1552,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462388</v>
+        <v>462287</v>
       </c>
       <c r="R10" t="n">
-        <v>6768696</v>
+        <v>6768630</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,11 +1612,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124781784</v>
+        <v>124777178</v>
       </c>
       <c r="B11" t="n">
-        <v>57529</v>
+        <v>74901</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,39 +1654,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>462362</v>
+        <v>462340</v>
       </c>
       <c r="R11" t="n">
-        <v>6768766</v>
+        <v>6768649</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124776376</v>
+        <v>124774634</v>
       </c>
       <c r="B12" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>462311</v>
+        <v>462257</v>
       </c>
       <c r="R12" t="n">
-        <v>6768690</v>
+        <v>6768691</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1837,7 +1842,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124781915</v>
+        <v>124775405</v>
       </c>
       <c r="B13" t="n">
         <v>57529</v>
@@ -1882,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>462389</v>
+        <v>462322</v>
       </c>
       <c r="R13" t="n">
-        <v>6768770</v>
+        <v>6768707</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1918,6 +1923,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1944,10 +1954,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124775405</v>
+        <v>124774845</v>
       </c>
       <c r="B14" t="n">
-        <v>57529</v>
+        <v>8447</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1956,43 +1966,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>462322</v>
+        <v>462271</v>
       </c>
       <c r="R14" t="n">
-        <v>6768707</v>
+        <v>6768703</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2025,11 +2030,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,7 +2056,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124775105</v>
+        <v>124781860</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>462281</v>
+        <v>462362</v>
       </c>
       <c r="R15" t="n">
-        <v>6768705</v>
+        <v>6768766</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2163,10 +2163,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124774463</v>
+        <v>124782461</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2175,38 +2175,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>462264</v>
+        <v>462374</v>
       </c>
       <c r="R16" t="n">
-        <v>6768671</v>
+        <v>6768823</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,7 +2270,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124774814</v>
+        <v>124781915</v>
       </c>
       <c r="B17" t="n">
         <v>57529</v>
@@ -2301,7 +2306,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2310,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>462257</v>
+        <v>462389</v>
       </c>
       <c r="R17" t="n">
-        <v>6768691</v>
+        <v>6768770</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2372,10 +2377,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124774922</v>
+        <v>124776534</v>
       </c>
       <c r="B18" t="n">
-        <v>57529</v>
+        <v>74901</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2388,39 +2393,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>462275</v>
+        <v>462302</v>
       </c>
       <c r="R18" t="n">
-        <v>6768714</v>
+        <v>6768675</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2453,6 +2453,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2479,7 +2484,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124782138</v>
+        <v>124774463</v>
       </c>
       <c r="B19" t="n">
         <v>78810</v>
@@ -2519,10 +2524,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>462447</v>
+        <v>462264</v>
       </c>
       <c r="R19" t="n">
-        <v>6768805</v>
+        <v>6768671</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2581,10 +2586,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124775556</v>
+        <v>124772023</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2597,34 +2602,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>462341</v>
+        <v>462234</v>
       </c>
       <c r="R20" t="n">
-        <v>6768708</v>
+        <v>6768605</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2657,6 +2667,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2683,10 +2698,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124777178</v>
+        <v>124775446</v>
       </c>
       <c r="B21" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2699,21 +2714,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2723,10 +2738,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>462340</v>
+        <v>462341</v>
       </c>
       <c r="R21" t="n">
-        <v>6768649</v>
+        <v>6768708</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2785,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124782461</v>
+        <v>124781969</v>
       </c>
       <c r="B22" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2797,43 +2812,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>462374</v>
+        <v>462389</v>
       </c>
       <c r="R22" t="n">
-        <v>6768823</v>
+        <v>6768770</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2892,7 +2902,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124774056</v>
+        <v>124777598</v>
       </c>
       <c r="B23" t="n">
         <v>78810</v>
@@ -2932,10 +2942,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>462291</v>
+        <v>462331</v>
       </c>
       <c r="R23" t="n">
-        <v>6768602</v>
+        <v>6768680</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2994,10 +3004,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124776291</v>
+        <v>124770579</v>
       </c>
       <c r="B24" t="n">
-        <v>57529</v>
+        <v>74901</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3010,39 +3020,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>462311</v>
+        <v>462182</v>
       </c>
       <c r="R24" t="n">
-        <v>6768690</v>
+        <v>6768583</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3101,7 +3106,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124781969</v>
+        <v>124775105</v>
       </c>
       <c r="B25" t="n">
         <v>78810</v>
@@ -3141,10 +3146,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>462389</v>
+        <v>462281</v>
       </c>
       <c r="R25" t="n">
-        <v>6768770</v>
+        <v>6768705</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3177,6 +3182,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3203,10 +3213,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124774845</v>
+        <v>124778521</v>
       </c>
       <c r="B26" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3215,25 +3225,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3243,10 +3253,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>462271</v>
+        <v>462386</v>
       </c>
       <c r="R26" t="n">
-        <v>6768703</v>
+        <v>6768724</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3279,6 +3289,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Miljöbilder för närområdet. Hygget börjar bakom lågorna</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3305,10 +3320,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124774494</v>
+        <v>124782169</v>
       </c>
       <c r="B27" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3317,25 +3332,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3345,10 +3360,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>462257</v>
+        <v>462456</v>
       </c>
       <c r="R27" t="n">
-        <v>6768691</v>
+        <v>6768800</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3407,10 +3422,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124778521</v>
+        <v>124774494</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3419,25 +3434,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3447,10 +3462,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>462386</v>
+        <v>462257</v>
       </c>
       <c r="R28" t="n">
-        <v>6768724</v>
+        <v>6768691</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3483,11 +3498,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Miljöbilder för närområdet. Hygget börjar bakom lågorna</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3514,10 +3524,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124773032</v>
+        <v>124772894</v>
       </c>
       <c r="B29" t="n">
-        <v>57529</v>
+        <v>74901</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3530,39 +3540,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>462235</v>
+        <v>462230</v>
       </c>
       <c r="R29" t="n">
-        <v>6768533</v>
+        <v>6768556</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3621,10 +3626,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124772894</v>
+        <v>124771180</v>
       </c>
       <c r="B30" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3637,21 +3642,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3661,10 +3666,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>462230</v>
+        <v>462198</v>
       </c>
       <c r="R30" t="n">
-        <v>6768556</v>
+        <v>6768579</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3723,10 +3728,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124771180</v>
+        <v>124771314</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3739,37 +3744,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>462198</v>
+        <v>462210</v>
       </c>
       <c r="R31" t="n">
-        <v>6768579</v>
+        <v>6768591</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3825,10 +3835,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124771314</v>
+        <v>124773032</v>
       </c>
       <c r="B32" t="n">
-        <v>57666</v>
+        <v>57529</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3841,27 +3851,27 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3870,13 +3880,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>462210</v>
+        <v>462235</v>
       </c>
       <c r="R32" t="n">
-        <v>6768591</v>
+        <v>6768533</v>
       </c>
       <c r="S32" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3932,7 +3942,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124776534</v>
+        <v>124776376</v>
       </c>
       <c r="B33" t="n">
         <v>74901</v>
@@ -3972,10 +3982,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>462302</v>
+        <v>462311</v>
       </c>
       <c r="R33" t="n">
-        <v>6768675</v>
+        <v>6768690</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4008,11 +4018,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4039,10 +4044,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124781860</v>
+        <v>124778690</v>
       </c>
       <c r="B34" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4055,34 +4060,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>462362</v>
+        <v>462388</v>
       </c>
       <c r="R34" t="n">
-        <v>6768766</v>
+        <v>6768696</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4146,7 +4156,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124777762</v>
+        <v>124770632</v>
       </c>
       <c r="B35" t="n">
         <v>57529</v>
@@ -4191,10 +4201,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>462331</v>
+        <v>462182</v>
       </c>
       <c r="R35" t="n">
-        <v>6768680</v>
+        <v>6768583</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4231,7 +4241,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Miljöbilder på bland annat angränsande hygge.</t>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4258,10 +4268,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124772023</v>
+        <v>124782138</v>
       </c>
       <c r="B36" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4274,39 +4284,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>462234</v>
+        <v>462447</v>
       </c>
       <c r="R36" t="n">
-        <v>6768605</v>
+        <v>6768805</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4339,11 +4344,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4370,10 +4370,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124836527</v>
+        <v>124833941</v>
       </c>
       <c r="B37" t="n">
-        <v>79399</v>
+        <v>8447</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4382,25 +4382,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4410,10 +4410,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>462712</v>
+        <v>462816</v>
       </c>
       <c r="R37" t="n">
-        <v>6769143</v>
+        <v>6769191</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4450,7 +4450,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Miljöbild</t>
+          <t>Miljöbilder för närområdet.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4477,10 +4477,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124836445</v>
+        <v>124834239</v>
       </c>
       <c r="B38" t="n">
-        <v>78546</v>
+        <v>79428</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4493,21 +4493,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>462712</v>
+        <v>462814</v>
       </c>
       <c r="R38" t="n">
-        <v>6769143</v>
+        <v>6769220</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4686,10 +4686,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124835245</v>
+        <v>124835714</v>
       </c>
       <c r="B40" t="n">
-        <v>78546</v>
+        <v>8447</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4698,25 +4698,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4900,10 +4900,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124838423</v>
+        <v>124836354</v>
       </c>
       <c r="B42" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4916,34 +4916,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lädsån, Dlr</t>
+          <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>462456</v>
+        <v>462712</v>
       </c>
       <c r="R42" t="n">
-        <v>6768914</v>
+        <v>6769143</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Miljöbild</t>
+          <t>Miljöbild, garnlav i äldre tall.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5007,10 +5007,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124835204</v>
+        <v>124836148</v>
       </c>
       <c r="B43" t="n">
-        <v>79428</v>
+        <v>78546</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5023,21 +5023,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5047,10 +5047,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>462814</v>
+        <v>462741</v>
       </c>
       <c r="R43" t="n">
-        <v>6769220</v>
+        <v>6769142</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5114,10 +5114,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124836271</v>
+        <v>124834205</v>
       </c>
       <c r="B44" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5130,21 +5130,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5154,10 +5154,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>462712</v>
+        <v>462814</v>
       </c>
       <c r="R44" t="n">
-        <v>6769143</v>
+        <v>6769220</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5194,7 +5194,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Miljöbilder</t>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5221,10 +5221,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124833451</v>
+        <v>124838423</v>
       </c>
       <c r="B45" t="n">
-        <v>8447</v>
+        <v>57529</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5233,38 +5233,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Salutjärnen, Dlr</t>
+          <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>462818</v>
+        <v>462456</v>
       </c>
       <c r="R45" t="n">
-        <v>6769164</v>
+        <v>6768914</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5297,6 +5297,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5323,10 +5328,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124835714</v>
+        <v>124836445</v>
       </c>
       <c r="B46" t="n">
-        <v>8447</v>
+        <v>78546</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5335,25 +5340,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5363,10 +5368,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>462814</v>
+        <v>462712</v>
       </c>
       <c r="R46" t="n">
-        <v>6769220</v>
+        <v>6769143</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5430,10 +5435,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124833941</v>
+        <v>124836527</v>
       </c>
       <c r="B47" t="n">
-        <v>8447</v>
+        <v>79399</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5442,25 +5447,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5470,10 +5475,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>462816</v>
+        <v>462712</v>
       </c>
       <c r="R47" t="n">
-        <v>6769191</v>
+        <v>6769143</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5510,7 +5515,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Miljöbilder för närområdet.</t>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5537,10 +5542,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124836148</v>
+        <v>124833451</v>
       </c>
       <c r="B48" t="n">
-        <v>78546</v>
+        <v>8447</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5549,25 +5554,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5577,10 +5582,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>462741</v>
+        <v>462818</v>
       </c>
       <c r="R48" t="n">
-        <v>6769142</v>
+        <v>6769164</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5613,11 +5618,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5644,10 +5644,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125017227</v>
+        <v>124999865</v>
       </c>
       <c r="B49" t="n">
-        <v>94959</v>
+        <v>57529</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5656,38 +5656,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2387</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Salutjärnen, Dlr</t>
+          <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>462424</v>
+        <v>462482</v>
       </c>
       <c r="R49" t="n">
-        <v>6768787</v>
+        <v>6768845</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5722,11 +5727,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>I kallkälla</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5739,22 +5739,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125017198</v>
+        <v>125000745</v>
       </c>
       <c r="B50" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5767,16 +5767,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5787,7 +5787,7 @@
       <c r="I50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5796,10 +5796,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>462452</v>
+        <v>462414</v>
       </c>
       <c r="R50" t="n">
-        <v>6768897</v>
+        <v>6768796</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5834,6 +5834,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5846,22 +5851,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125017106</v>
+        <v>125017156</v>
       </c>
       <c r="B51" t="n">
-        <v>79428</v>
+        <v>96354</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5874,21 +5879,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>53</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5898,10 +5903,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>462755</v>
+        <v>462418</v>
       </c>
       <c r="R51" t="n">
-        <v>6769176</v>
+        <v>6768776</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5960,10 +5965,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125017260</v>
+        <v>125017171</v>
       </c>
       <c r="B52" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5976,21 +5981,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6000,10 +6005,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>462575</v>
+        <v>462425</v>
       </c>
       <c r="R52" t="n">
-        <v>6768974</v>
+        <v>6768807</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6062,10 +6067,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125017156</v>
+        <v>125017115</v>
       </c>
       <c r="B53" t="n">
-        <v>96354</v>
+        <v>79428</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6078,21 +6083,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>53</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6102,10 +6107,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>462418</v>
+        <v>462449</v>
       </c>
       <c r="R53" t="n">
-        <v>6768776</v>
+        <v>6768835</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6164,10 +6169,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125017284</v>
+        <v>125017250</v>
       </c>
       <c r="B54" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6180,21 +6185,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6204,10 +6209,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>462409</v>
+        <v>462364</v>
       </c>
       <c r="R54" t="n">
-        <v>6768814</v>
+        <v>6768755</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6266,10 +6271,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125017171</v>
+        <v>125017204</v>
       </c>
       <c r="B55" t="n">
-        <v>91012</v>
+        <v>96979</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6278,25 +6283,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6306,10 +6311,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>462425</v>
+        <v>462438</v>
       </c>
       <c r="R55" t="n">
-        <v>6768807</v>
+        <v>6768787</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6470,7 +6475,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125017119</v>
+        <v>125017113</v>
       </c>
       <c r="B57" t="n">
         <v>79428</v>
@@ -6510,10 +6515,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>462543</v>
+        <v>462356</v>
       </c>
       <c r="R57" t="n">
-        <v>6768929</v>
+        <v>6768753</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6572,10 +6577,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125017154</v>
+        <v>125017137</v>
       </c>
       <c r="B58" t="n">
-        <v>96354</v>
+        <v>78842</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6588,21 +6593,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>53</v>
+        <v>185</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6612,10 +6617,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>462433</v>
+        <v>462506</v>
       </c>
       <c r="R58" t="n">
-        <v>6768784</v>
+        <v>6768894</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6674,10 +6679,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125017105</v>
+        <v>125017263</v>
       </c>
       <c r="B59" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6690,21 +6695,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6714,10 +6719,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>462811</v>
+        <v>462712</v>
       </c>
       <c r="R59" t="n">
-        <v>6769258</v>
+        <v>6769149</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6776,10 +6781,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124999425</v>
+        <v>125017260</v>
       </c>
       <c r="B60" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6788,25 +6793,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6816,10 +6821,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>462616</v>
+        <v>462575</v>
       </c>
       <c r="R60" t="n">
-        <v>6769046</v>
+        <v>6768974</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6854,11 +6859,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -6871,22 +6871,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124999027</v>
+        <v>125017157</v>
       </c>
       <c r="B61" t="n">
-        <v>57529</v>
+        <v>90977</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6895,25 +6895,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6923,10 +6923,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>462741</v>
+        <v>462431</v>
       </c>
       <c r="R61" t="n">
-        <v>6769142</v>
+        <v>6768769</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6961,11 +6961,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Miljöbilder. Sannoligt bohål/hackhål efter spillkråka.</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -6978,22 +6973,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124999142</v>
+        <v>125007719</v>
       </c>
       <c r="B62" t="n">
-        <v>78842</v>
+        <v>79428</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7006,34 +7001,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Salutjärnen, Dlr</t>
+          <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>462684</v>
+        <v>462456</v>
       </c>
       <c r="R62" t="n">
-        <v>6769117</v>
+        <v>6768884</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7066,6 +7061,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7092,10 +7092,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125017232</v>
+        <v>124999142</v>
       </c>
       <c r="B63" t="n">
-        <v>80763</v>
+        <v>78842</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7108,21 +7108,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1049</v>
+        <v>185</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7132,10 +7132,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>462456</v>
+        <v>462684</v>
       </c>
       <c r="R63" t="n">
-        <v>6768781</v>
+        <v>6769117</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7182,22 +7182,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125017238</v>
+        <v>125001637</v>
       </c>
       <c r="B64" t="n">
-        <v>78546</v>
+        <v>56722</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7206,38 +7206,43 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>462685</v>
+        <v>462376</v>
       </c>
       <c r="R64" t="n">
-        <v>6769071</v>
+        <v>6768807</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7284,22 +7289,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125017245</v>
+        <v>124999332</v>
       </c>
       <c r="B65" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7312,21 +7317,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7336,10 +7341,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>462867</v>
+        <v>462658</v>
       </c>
       <c r="R65" t="n">
-        <v>6769346</v>
+        <v>6769079</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7386,22 +7391,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125017261</v>
+        <v>125001392</v>
       </c>
       <c r="B66" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7414,21 +7419,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7438,10 +7443,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>462696</v>
+        <v>462456</v>
       </c>
       <c r="R66" t="n">
-        <v>6769144</v>
+        <v>6768778</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7476,6 +7481,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -7488,22 +7498,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125017270</v>
+        <v>124999177</v>
       </c>
       <c r="B67" t="n">
-        <v>78455</v>
+        <v>57529</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7516,34 +7526,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>353</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>462777</v>
+        <v>462684</v>
       </c>
       <c r="R67" t="n">
-        <v>6769237</v>
+        <v>6769117</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7590,22 +7605,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125017209</v>
+        <v>125017251</v>
       </c>
       <c r="B68" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7614,43 +7629,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>462777</v>
+        <v>462357</v>
       </c>
       <c r="R68" t="n">
-        <v>6769237</v>
+        <v>6768775</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7709,10 +7719,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125017246</v>
+        <v>125017122</v>
       </c>
       <c r="B69" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7725,21 +7735,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7749,10 +7759,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>462868</v>
+        <v>462688</v>
       </c>
       <c r="R69" t="n">
-        <v>6769325</v>
+        <v>6769019</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7811,10 +7821,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125017277</v>
+        <v>125017259</v>
       </c>
       <c r="B70" t="n">
-        <v>78455</v>
+        <v>78810</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7827,21 +7837,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7851,10 +7861,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>462478</v>
+        <v>462444</v>
       </c>
       <c r="R70" t="n">
-        <v>6768887</v>
+        <v>6768832</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7913,10 +7923,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125017254</v>
+        <v>124999653</v>
       </c>
       <c r="B71" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7929,21 +7939,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7953,10 +7963,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>462424</v>
+        <v>462598</v>
       </c>
       <c r="R71" t="n">
-        <v>6768802</v>
+        <v>6769000</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7991,6 +8001,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -8003,22 +8018,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125017241</v>
+        <v>125017255</v>
       </c>
       <c r="B72" t="n">
-        <v>91026</v>
+        <v>78810</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8031,21 +8046,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8055,10 +8070,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>462418</v>
+        <v>462419</v>
       </c>
       <c r="R72" t="n">
-        <v>6768776</v>
+        <v>6768798</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8117,10 +8132,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125017186</v>
+        <v>125017139</v>
       </c>
       <c r="B73" t="n">
-        <v>57529</v>
+        <v>78842</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8133,43 +8148,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>462647</v>
+        <v>462539</v>
       </c>
       <c r="R73" t="n">
-        <v>6769118</v>
+        <v>6768915</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8228,10 +8234,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125000267</v>
+        <v>125017228</v>
       </c>
       <c r="B74" t="n">
-        <v>8447</v>
+        <v>94766</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8244,34 +8250,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>2412</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Philonotis fontana</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Lädsån, Dlr</t>
+          <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>462482</v>
+        <v>462418</v>
       </c>
       <c r="R74" t="n">
-        <v>6768845</v>
+        <v>6768790</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8308,7 +8314,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Miljöbilder</t>
+          <t>I kallkälla</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8323,22 +8329,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125000074</v>
+        <v>125017227</v>
       </c>
       <c r="B75" t="n">
-        <v>57529</v>
+        <v>94959</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8347,43 +8353,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>2387</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Lädsån, Dlr</t>
+          <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>462482</v>
+        <v>462424</v>
       </c>
       <c r="R75" t="n">
-        <v>6768845</v>
+        <v>6768787</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8418,6 +8419,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>I kallkälla</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -8430,22 +8436,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125007547</v>
+        <v>125017241</v>
       </c>
       <c r="B76" t="n">
-        <v>79428</v>
+        <v>91026</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8458,21 +8464,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>1204</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8482,10 +8488,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>462441</v>
+        <v>462418</v>
       </c>
       <c r="R76" t="n">
-        <v>6768886</v>
+        <v>6768776</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8520,11 +8526,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -8537,22 +8538,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125007648</v>
+        <v>125017284</v>
       </c>
       <c r="B77" t="n">
-        <v>79428</v>
+        <v>91012</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8565,21 +8566,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8589,10 +8590,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>462431</v>
+        <v>462409</v>
       </c>
       <c r="R77" t="n">
-        <v>6768885</v>
+        <v>6768814</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8627,11 +8628,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -8644,22 +8640,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124999332</v>
+        <v>125001339</v>
       </c>
       <c r="B78" t="n">
-        <v>79428</v>
+        <v>57529</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8672,34 +8668,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>462658</v>
+        <v>462456</v>
       </c>
       <c r="R78" t="n">
-        <v>6769079</v>
+        <v>6768778</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8732,6 +8733,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8758,10 +8764,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125017157</v>
+        <v>125017198</v>
       </c>
       <c r="B79" t="n">
-        <v>90977</v>
+        <v>57529</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8770,38 +8776,43 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>462431</v>
+        <v>462452</v>
       </c>
       <c r="R79" t="n">
-        <v>6768769</v>
+        <v>6768897</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8860,10 +8871,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125017162</v>
+        <v>125017262</v>
       </c>
       <c r="B80" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8876,21 +8887,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8900,10 +8911,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>462763</v>
+        <v>462703</v>
       </c>
       <c r="R80" t="n">
-        <v>6769126</v>
+        <v>6769146</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8962,10 +8973,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125017136</v>
+        <v>125017273</v>
       </c>
       <c r="B81" t="n">
-        <v>78842</v>
+        <v>78455</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8978,21 +8989,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9002,10 +9013,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>462449</v>
+        <v>462642</v>
       </c>
       <c r="R81" t="n">
-        <v>6768898</v>
+        <v>6769092</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9064,10 +9075,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125017278</v>
+        <v>125017112</v>
       </c>
       <c r="B82" t="n">
-        <v>78455</v>
+        <v>79428</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9080,21 +9091,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9104,10 +9115,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>462544</v>
+        <v>462453</v>
       </c>
       <c r="R82" t="n">
-        <v>6768928</v>
+        <v>6768876</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9166,10 +9177,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125017257</v>
+        <v>125017141</v>
       </c>
       <c r="B83" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9182,21 +9193,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9206,10 +9217,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>462417</v>
+        <v>462579</v>
       </c>
       <c r="R83" t="n">
-        <v>6768771</v>
+        <v>6768990</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9268,10 +9279,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125017264</v>
+        <v>125017135</v>
       </c>
       <c r="B84" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9284,21 +9295,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9308,10 +9319,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>462713</v>
+        <v>462439</v>
       </c>
       <c r="R84" t="n">
-        <v>6769148</v>
+        <v>6768813</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9370,10 +9381,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125017220</v>
+        <v>125017224</v>
       </c>
       <c r="B85" t="n">
-        <v>8447</v>
+        <v>78547</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9382,43 +9393,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>462472</v>
+        <v>462683</v>
       </c>
       <c r="R85" t="n">
-        <v>6768856</v>
+        <v>6769060</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9477,10 +9483,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125017139</v>
+        <v>125007547</v>
       </c>
       <c r="B86" t="n">
-        <v>78842</v>
+        <v>79428</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9493,21 +9499,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9517,10 +9523,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>462539</v>
+        <v>462441</v>
       </c>
       <c r="R86" t="n">
-        <v>6768915</v>
+        <v>6768886</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9555,6 +9561,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -9567,22 +9578,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125017205</v>
+        <v>125017236</v>
       </c>
       <c r="B87" t="n">
-        <v>8447</v>
+        <v>78546</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9591,43 +9602,38 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>462864</v>
+        <v>462688</v>
       </c>
       <c r="R87" t="n">
-        <v>6769317</v>
+        <v>6769019</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9686,10 +9692,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124999177</v>
+        <v>125001616</v>
       </c>
       <c r="B88" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9698,31 +9704,31 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -9731,10 +9737,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>462684</v>
+        <v>462456</v>
       </c>
       <c r="R88" t="n">
-        <v>6769117</v>
+        <v>6768778</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9767,6 +9773,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Miljöbilder. Så kallad tjädertall</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9793,10 +9804,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125017166</v>
+        <v>125000045</v>
       </c>
       <c r="B89" t="n">
-        <v>91361</v>
+        <v>78810</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9805,38 +9816,38 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Salutjärnen, Dlr</t>
+          <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>462312</v>
+        <v>462482</v>
       </c>
       <c r="R89" t="n">
-        <v>6768750</v>
+        <v>6768845</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9883,22 +9894,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125017185</v>
+        <v>125017205</v>
       </c>
       <c r="B90" t="n">
-        <v>98122</v>
+        <v>8447</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9911,34 +9922,39 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221952</v>
+        <v>106545</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>462417</v>
+        <v>462864</v>
       </c>
       <c r="R90" t="n">
-        <v>6768771</v>
+        <v>6769317</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9997,10 +10013,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125017280</v>
+        <v>125017166</v>
       </c>
       <c r="B91" t="n">
-        <v>96227</v>
+        <v>91361</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10009,25 +10025,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2869</v>
+        <v>2062</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10037,10 +10053,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>462403</v>
+        <v>462312</v>
       </c>
       <c r="R91" t="n">
-        <v>6768799</v>
+        <v>6768750</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10099,10 +10115,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125017282</v>
+        <v>125017124</v>
       </c>
       <c r="B92" t="n">
-        <v>78194</v>
+        <v>79428</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10115,21 +10131,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10139,10 +10155,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>462759</v>
+        <v>462679</v>
       </c>
       <c r="R92" t="n">
-        <v>6769121</v>
+        <v>6769045</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10201,10 +10217,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125017114</v>
+        <v>125017193</v>
       </c>
       <c r="B93" t="n">
-        <v>79428</v>
+        <v>57529</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10217,34 +10233,39 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>462451</v>
+        <v>462585</v>
       </c>
       <c r="R93" t="n">
-        <v>6768820</v>
+        <v>6769050</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10303,10 +10324,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125017199</v>
+        <v>125017252</v>
       </c>
       <c r="B94" t="n">
-        <v>96345</v>
+        <v>78810</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10319,21 +10340,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>54</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skogstrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Anastrophyllum michauxii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(F.Weber.) H.Buch</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10343,10 +10364,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>462249</v>
+        <v>462426</v>
       </c>
       <c r="R94" t="n">
-        <v>6768580</v>
+        <v>6768812</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10387,7 +10408,6 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10406,10 +10426,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125017236</v>
+        <v>125017105</v>
       </c>
       <c r="B95" t="n">
-        <v>78546</v>
+        <v>79428</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10422,21 +10442,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10446,10 +10466,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>462688</v>
+        <v>462811</v>
       </c>
       <c r="R95" t="n">
-        <v>6769019</v>
+        <v>6769258</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10508,7 +10528,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125017112</v>
+        <v>125017125</v>
       </c>
       <c r="B96" t="n">
         <v>79428</v>
@@ -10548,10 +10568,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>462453</v>
+        <v>462683</v>
       </c>
       <c r="R96" t="n">
-        <v>6768876</v>
+        <v>6769060</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10610,10 +10630,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125017212</v>
+        <v>125017128</v>
       </c>
       <c r="B97" t="n">
-        <v>8447</v>
+        <v>79428</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10622,43 +10642,38 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>462295</v>
+        <v>462680</v>
       </c>
       <c r="R97" t="n">
-        <v>6768622</v>
+        <v>6769078</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10717,10 +10732,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125017273</v>
+        <v>125017134</v>
       </c>
       <c r="B98" t="n">
-        <v>78455</v>
+        <v>78842</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10733,21 +10748,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10757,10 +10772,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>462642</v>
+        <v>462385</v>
       </c>
       <c r="R98" t="n">
-        <v>6769092</v>
+        <v>6768840</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10819,10 +10834,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125017224</v>
+        <v>125017127</v>
       </c>
       <c r="B99" t="n">
-        <v>78547</v>
+        <v>79428</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10835,21 +10850,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10859,10 +10874,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>462683</v>
+        <v>462685</v>
       </c>
       <c r="R99" t="n">
-        <v>6769060</v>
+        <v>6769071</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10921,10 +10936,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125017122</v>
+        <v>125017254</v>
       </c>
       <c r="B100" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10937,21 +10952,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10961,10 +10976,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>462688</v>
+        <v>462424</v>
       </c>
       <c r="R100" t="n">
-        <v>6769019</v>
+        <v>6768802</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11023,7 +11038,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125017108</v>
+        <v>125017130</v>
       </c>
       <c r="B101" t="n">
         <v>79428</v>
@@ -11063,10 +11078,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>462569</v>
+        <v>462444</v>
       </c>
       <c r="R101" t="n">
-        <v>6769031</v>
+        <v>6768840</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11125,10 +11140,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125001339</v>
+        <v>125017170</v>
       </c>
       <c r="B102" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11141,39 +11156,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>462456</v>
+        <v>462313</v>
       </c>
       <c r="R102" t="n">
-        <v>6768778</v>
+        <v>6768749</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11208,11 +11218,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
@@ -11225,22 +11230,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125001392</v>
+        <v>125000267</v>
       </c>
       <c r="B103" t="n">
-        <v>79428</v>
+        <v>8447</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11249,38 +11254,38 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Salutjärnen, Dlr</t>
+          <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>462456</v>
+        <v>462482</v>
       </c>
       <c r="R103" t="n">
-        <v>6768778</v>
+        <v>6768845</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11317,7 +11322,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Miljöbild</t>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11344,10 +11349,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125017173</v>
+        <v>125000794</v>
       </c>
       <c r="B104" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11356,43 +11361,38 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>462440</v>
+        <v>462420</v>
       </c>
       <c r="R104" t="n">
-        <v>6768764</v>
+        <v>6768785</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11427,6 +11427,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
@@ -11439,22 +11444,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125017250</v>
+        <v>125017202</v>
       </c>
       <c r="B105" t="n">
-        <v>78810</v>
+        <v>91299</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11467,21 +11472,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11491,10 +11496,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>462364</v>
+        <v>462414</v>
       </c>
       <c r="R105" t="n">
-        <v>6768755</v>
+        <v>6768758</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11553,10 +11558,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125017210</v>
+        <v>125017246</v>
       </c>
       <c r="B106" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11565,43 +11570,38 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>462636</v>
+        <v>462868</v>
       </c>
       <c r="R106" t="n">
-        <v>6769113</v>
+        <v>6769325</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11660,10 +11660,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125017175</v>
+        <v>125017247</v>
       </c>
       <c r="B107" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11672,43 +11672,38 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>462419</v>
+        <v>462756</v>
       </c>
       <c r="R107" t="n">
-        <v>6768798</v>
+        <v>6769225</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11767,10 +11762,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125017115</v>
+        <v>125017277</v>
       </c>
       <c r="B108" t="n">
-        <v>79428</v>
+        <v>78455</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11783,21 +11778,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11807,10 +11802,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>462449</v>
+        <v>462478</v>
       </c>
       <c r="R108" t="n">
-        <v>6768835</v>
+        <v>6768887</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11869,10 +11864,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125017219</v>
+        <v>125017155</v>
       </c>
       <c r="B109" t="n">
-        <v>8447</v>
+        <v>96354</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11881,43 +11876,38 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>462585</v>
+        <v>462427</v>
       </c>
       <c r="R109" t="n">
-        <v>6769050</v>
+        <v>6768776</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11976,10 +11966,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125000666</v>
+        <v>125017212</v>
       </c>
       <c r="B110" t="n">
-        <v>57529</v>
+        <v>8447</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11988,31 +11978,31 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -12021,10 +12011,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>462422</v>
+        <v>462295</v>
       </c>
       <c r="R110" t="n">
-        <v>6768811</v>
+        <v>6768622</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12071,22 +12061,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125004378</v>
+        <v>125017266</v>
       </c>
       <c r="B111" t="n">
-        <v>57529</v>
+        <v>92293</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12095,43 +12085,47 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Lädsån, Dlr</t>
+          <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>462261</v>
+        <v>462462</v>
       </c>
       <c r="R111" t="n">
-        <v>6768593</v>
+        <v>6768863</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12166,11 +12160,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
@@ -12183,22 +12172,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125017225</v>
+        <v>125017185</v>
       </c>
       <c r="B112" t="n">
-        <v>8447</v>
+        <v>98122</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12211,39 +12200,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>106545</v>
+        <v>221952</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>462449</v>
+        <v>462417</v>
       </c>
       <c r="R112" t="n">
-        <v>6768765</v>
+        <v>6768771</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12302,10 +12286,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125017266</v>
+        <v>125017119</v>
       </c>
       <c r="B113" t="n">
-        <v>92293</v>
+        <v>79428</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12314,47 +12298,38 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>462462</v>
+        <v>462543</v>
       </c>
       <c r="R113" t="n">
-        <v>6768863</v>
+        <v>6768929</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12413,10 +12388,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>124999607</v>
+        <v>125017238</v>
       </c>
       <c r="B114" t="n">
-        <v>79428</v>
+        <v>78546</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12429,21 +12404,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12453,10 +12428,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>462598</v>
+        <v>462685</v>
       </c>
       <c r="R114" t="n">
-        <v>6769000</v>
+        <v>6769071</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12491,11 +12466,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
-        </is>
-      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
@@ -12508,22 +12478,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125017181</v>
+        <v>125017279</v>
       </c>
       <c r="B115" t="n">
-        <v>79920</v>
+        <v>78455</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12532,25 +12502,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6462</v>
+        <v>353</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12560,10 +12530,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>462422</v>
+        <v>462581</v>
       </c>
       <c r="R115" t="n">
-        <v>6768816</v>
+        <v>6768944</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12596,11 +12566,6 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-05-12</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12627,10 +12592,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125017190</v>
+        <v>125017220</v>
       </c>
       <c r="B116" t="n">
-        <v>57529</v>
+        <v>8447</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12639,31 +12604,31 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -12672,10 +12637,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>462791</v>
+        <v>462472</v>
       </c>
       <c r="R116" t="n">
-        <v>6769257</v>
+        <v>6768856</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12734,10 +12699,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125017259</v>
+        <v>125017270</v>
       </c>
       <c r="B117" t="n">
-        <v>78810</v>
+        <v>78455</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12750,21 +12715,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12774,10 +12739,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>462444</v>
+        <v>462777</v>
       </c>
       <c r="R117" t="n">
-        <v>6768832</v>
+        <v>6769237</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12836,10 +12801,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125017251</v>
+        <v>124999425</v>
       </c>
       <c r="B118" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12848,25 +12813,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12876,10 +12841,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>462357</v>
+        <v>462616</v>
       </c>
       <c r="R118" t="n">
-        <v>6768775</v>
+        <v>6769046</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12914,6 +12879,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
+        </is>
+      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
@@ -12926,22 +12896,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125017253</v>
+        <v>125017186</v>
       </c>
       <c r="B119" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12954,34 +12924,43 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>462425</v>
+        <v>462647</v>
       </c>
       <c r="R119" t="n">
-        <v>6768806</v>
+        <v>6769118</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13040,10 +13019,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125017117</v>
+        <v>125017225</v>
       </c>
       <c r="B120" t="n">
-        <v>79428</v>
+        <v>8447</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13052,38 +13031,43 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>462501</v>
+        <v>462449</v>
       </c>
       <c r="R120" t="n">
-        <v>6768895</v>
+        <v>6768765</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13142,10 +13126,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125007719</v>
+        <v>125017240</v>
       </c>
       <c r="B121" t="n">
-        <v>79428</v>
+        <v>58191</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13154,38 +13138,38 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6453</v>
+        <v>103044</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Lädsån, Dlr</t>
+          <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>462456</v>
+        <v>462248</v>
       </c>
       <c r="R121" t="n">
-        <v>6768884</v>
+        <v>6768584</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13220,11 +13204,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
@@ -13237,22 +13216,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125017204</v>
+        <v>125017106</v>
       </c>
       <c r="B122" t="n">
-        <v>96979</v>
+        <v>79428</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13261,25 +13240,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13289,10 +13268,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>462438</v>
+        <v>462755</v>
       </c>
       <c r="R122" t="n">
-        <v>6768787</v>
+        <v>6769176</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13351,10 +13330,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125017134</v>
+        <v>125017188</v>
       </c>
       <c r="B123" t="n">
-        <v>78842</v>
+        <v>57529</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13367,34 +13346,39 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>462385</v>
+        <v>462760</v>
       </c>
       <c r="R123" t="n">
-        <v>6768840</v>
+        <v>6769122</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13453,10 +13437,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125017193</v>
+        <v>125017181</v>
       </c>
       <c r="B124" t="n">
-        <v>57529</v>
+        <v>79920</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13465,43 +13449,38 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>462585</v>
+        <v>462422</v>
       </c>
       <c r="R124" t="n">
-        <v>6769050</v>
+        <v>6768816</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13534,6 +13513,11 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13560,10 +13544,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125017228</v>
+        <v>125017253</v>
       </c>
       <c r="B125" t="n">
-        <v>94766</v>
+        <v>78810</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13572,25 +13556,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>2412</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Philonotis fontana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13600,10 +13584,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>462418</v>
+        <v>462425</v>
       </c>
       <c r="R125" t="n">
-        <v>6768790</v>
+        <v>6768806</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13636,11 +13620,6 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-05-12</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>I kallkälla</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13667,7 +13646,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125000045</v>
+        <v>125017258</v>
       </c>
       <c r="B126" t="n">
         <v>78810</v>
@@ -13703,14 +13682,14 @@
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Lädsån, Dlr</t>
+          <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>462482</v>
+        <v>462449</v>
       </c>
       <c r="R126" t="n">
-        <v>6768845</v>
+        <v>6768783</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13757,12 +13736,12 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
@@ -13871,10 +13850,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125017142</v>
+        <v>125017245</v>
       </c>
       <c r="B128" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13887,21 +13866,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13911,10 +13890,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>462682</v>
+        <v>462867</v>
       </c>
       <c r="R128" t="n">
-        <v>6769024</v>
+        <v>6769346</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13973,10 +13952,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125000745</v>
+        <v>125001767</v>
       </c>
       <c r="B129" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13989,16 +13968,16 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -14014,14 +13993,14 @@
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Salutjärnen, Dlr</t>
+          <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>462414</v>
+        <v>462346</v>
       </c>
       <c r="R129" t="n">
-        <v>6768796</v>
+        <v>6768794</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14058,7 +14037,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>Miljöbilder</t>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14085,10 +14064,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>125017155</v>
+        <v>125000666</v>
       </c>
       <c r="B130" t="n">
-        <v>96354</v>
+        <v>57529</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14101,34 +14080,39 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>462427</v>
+        <v>462422</v>
       </c>
       <c r="R130" t="n">
-        <v>6768776</v>
+        <v>6768811</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14175,22 +14159,22 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125017125</v>
+        <v>125017173</v>
       </c>
       <c r="B131" t="n">
-        <v>79428</v>
+        <v>56722</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14199,38 +14183,43 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>462683</v>
+        <v>462440</v>
       </c>
       <c r="R131" t="n">
-        <v>6769060</v>
+        <v>6768764</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14289,10 +14278,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125017271</v>
+        <v>125017199</v>
       </c>
       <c r="B132" t="n">
-        <v>78455</v>
+        <v>96345</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14305,21 +14294,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>353</v>
+        <v>54</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skogstrappmossa</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anastrophyllum michauxii</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(F.Weber.) H.Buch</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14329,10 +14318,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>462755</v>
+        <v>462249</v>
       </c>
       <c r="R132" t="n">
-        <v>6769176</v>
+        <v>6768580</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14373,6 +14362,7 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -14391,10 +14381,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125017265</v>
+        <v>125017142</v>
       </c>
       <c r="B133" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14407,21 +14397,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14431,10 +14421,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>462762</v>
+        <v>462682</v>
       </c>
       <c r="R133" t="n">
-        <v>6769125</v>
+        <v>6769024</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14493,10 +14483,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125017116</v>
+        <v>125017257</v>
       </c>
       <c r="B134" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14509,21 +14499,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14533,10 +14523,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>462460</v>
+        <v>462417</v>
       </c>
       <c r="R134" t="n">
-        <v>6768868</v>
+        <v>6768771</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14595,10 +14585,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>124999190</v>
+        <v>125017237</v>
       </c>
       <c r="B135" t="n">
-        <v>8447</v>
+        <v>78546</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14607,25 +14597,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14635,10 +14625,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>462672</v>
+        <v>462684</v>
       </c>
       <c r="R135" t="n">
-        <v>6769113</v>
+        <v>6769060</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14685,22 +14675,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125001767</v>
+        <v>125017282</v>
       </c>
       <c r="B136" t="n">
-        <v>57529</v>
+        <v>78194</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14713,39 +14703,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100049</v>
+        <v>6437</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Lädsån, Dlr</t>
+          <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>462346</v>
+        <v>462759</v>
       </c>
       <c r="R136" t="n">
-        <v>6768794</v>
+        <v>6769121</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14780,11 +14765,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD136" t="b">
         <v>0</v>
       </c>
@@ -14797,22 +14777,22 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125001637</v>
+        <v>125017278</v>
       </c>
       <c r="B137" t="n">
-        <v>56722</v>
+        <v>78455</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -14821,43 +14801,38 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>462376</v>
+        <v>462544</v>
       </c>
       <c r="R137" t="n">
-        <v>6768807</v>
+        <v>6768928</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14904,22 +14879,22 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>125017127</v>
+        <v>125017136</v>
       </c>
       <c r="B138" t="n">
-        <v>79428</v>
+        <v>78842</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -14932,21 +14907,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14956,10 +14931,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>462685</v>
+        <v>462449</v>
       </c>
       <c r="R138" t="n">
-        <v>6769071</v>
+        <v>6768898</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15018,10 +14993,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>125017285</v>
+        <v>125017154</v>
       </c>
       <c r="B139" t="n">
-        <v>91065</v>
+        <v>96354</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15030,25 +15005,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5321</v>
+        <v>53</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15058,10 +15033,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>462561</v>
+        <v>462433</v>
       </c>
       <c r="R139" t="n">
-        <v>6768949</v>
+        <v>6768784</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15096,18 +15071,12 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>På asp</t>
-        </is>
-      </c>
       <c r="AD139" t="b">
         <v>0</v>
       </c>
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -15126,10 +15095,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>125017255</v>
+        <v>125017138</v>
       </c>
       <c r="B140" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15142,21 +15111,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15166,10 +15135,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>462419</v>
+        <v>462516</v>
       </c>
       <c r="R140" t="n">
-        <v>6768798</v>
+        <v>6768902</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15228,10 +15197,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>125017138</v>
+        <v>125017210</v>
       </c>
       <c r="B141" t="n">
-        <v>78842</v>
+        <v>8447</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15240,38 +15209,43 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P141" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>462516</v>
+        <v>462636</v>
       </c>
       <c r="R141" t="n">
-        <v>6768902</v>
+        <v>6769113</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15330,10 +15304,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>125017141</v>
+        <v>125004378</v>
       </c>
       <c r="B142" t="n">
-        <v>78842</v>
+        <v>57529</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15346,34 +15320,39 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Salutjärnen, Dlr</t>
+          <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>462579</v>
+        <v>462261</v>
       </c>
       <c r="R142" t="n">
-        <v>6768990</v>
+        <v>6768593</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15408,6 +15387,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD142" t="b">
         <v>0</v>
       </c>
@@ -15420,22 +15404,22 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>125017128</v>
+        <v>124999190</v>
       </c>
       <c r="B143" t="n">
-        <v>79428</v>
+        <v>8447</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15444,25 +15428,25 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15472,10 +15456,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>462680</v>
+        <v>462672</v>
       </c>
       <c r="R143" t="n">
-        <v>6769078</v>
+        <v>6769113</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15522,22 +15506,22 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>125017237</v>
+        <v>124999088</v>
       </c>
       <c r="B144" t="n">
-        <v>78546</v>
+        <v>57529</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15550,21 +15534,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15574,10 +15558,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>462684</v>
+        <v>462698</v>
       </c>
       <c r="R144" t="n">
-        <v>6769060</v>
+        <v>6769146</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15612,6 +15596,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>Miljöbilder. Sannoligt spillkråka, hackhål/bohål.</t>
+        </is>
+      </c>
       <c r="AD144" t="b">
         <v>0</v>
       </c>
@@ -15624,22 +15613,22 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>125017263</v>
+        <v>125017123</v>
       </c>
       <c r="B145" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15652,21 +15641,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15676,10 +15665,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>462712</v>
+        <v>462680</v>
       </c>
       <c r="R145" t="n">
-        <v>6769149</v>
+        <v>6769027</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15738,10 +15727,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>125017135</v>
+        <v>125017116</v>
       </c>
       <c r="B146" t="n">
-        <v>78842</v>
+        <v>79428</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15754,21 +15743,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15778,10 +15767,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>462439</v>
+        <v>462460</v>
       </c>
       <c r="R146" t="n">
-        <v>6768813</v>
+        <v>6768868</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15840,10 +15829,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>124999088</v>
+        <v>125017162</v>
       </c>
       <c r="B147" t="n">
-        <v>57529</v>
+        <v>79428</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15856,21 +15845,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15880,10 +15869,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>462698</v>
+        <v>462763</v>
       </c>
       <c r="R147" t="n">
-        <v>6769146</v>
+        <v>6769126</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15918,11 +15907,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC147" t="inlineStr">
-        <is>
-          <t>Miljöbilder. Sannoligt spillkråka, hackhål/bohål.</t>
-        </is>
-      </c>
       <c r="AD147" t="b">
         <v>0</v>
       </c>
@@ -15935,22 +15919,22 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125017113</v>
+        <v>125017175</v>
       </c>
       <c r="B148" t="n">
-        <v>79428</v>
+        <v>56722</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15959,38 +15943,43 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P148" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>462356</v>
+        <v>462419</v>
       </c>
       <c r="R148" t="n">
-        <v>6768753</v>
+        <v>6768798</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16049,10 +16038,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125017256</v>
+        <v>125017114</v>
       </c>
       <c r="B149" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16065,21 +16054,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16089,10 +16078,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>462409</v>
+        <v>462451</v>
       </c>
       <c r="R149" t="n">
-        <v>6768798</v>
+        <v>6768820</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16151,10 +16140,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125017207</v>
+        <v>125017108</v>
       </c>
       <c r="B150" t="n">
-        <v>8447</v>
+        <v>79428</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16163,43 +16152,38 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>462840</v>
+        <v>462569</v>
       </c>
       <c r="R150" t="n">
-        <v>6769309</v>
+        <v>6769031</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16258,7 +16242,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>125017262</v>
+        <v>125017261</v>
       </c>
       <c r="B151" t="n">
         <v>78810</v>
@@ -16298,10 +16282,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>462703</v>
+        <v>462696</v>
       </c>
       <c r="R151" t="n">
-        <v>6769146</v>
+        <v>6769144</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16360,10 +16344,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>125017247</v>
+        <v>124999027</v>
       </c>
       <c r="B152" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16376,21 +16360,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16400,10 +16384,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>462756</v>
+        <v>462741</v>
       </c>
       <c r="R152" t="n">
-        <v>6769225</v>
+        <v>6769142</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16438,6 +16422,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>Miljöbilder. Sannoligt bohål/hackhål efter spillkråka.</t>
+        </is>
+      </c>
       <c r="AD152" t="b">
         <v>0</v>
       </c>
@@ -16450,22 +16439,22 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>125017124</v>
+        <v>125017207</v>
       </c>
       <c r="B153" t="n">
-        <v>79428</v>
+        <v>8447</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16474,38 +16463,43 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P153" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>462679</v>
+        <v>462840</v>
       </c>
       <c r="R153" t="n">
-        <v>6769045</v>
+        <v>6769309</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16564,10 +16558,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>125017137</v>
+        <v>125017271</v>
       </c>
       <c r="B154" t="n">
-        <v>78842</v>
+        <v>78455</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16580,21 +16574,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16604,10 +16598,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>462506</v>
+        <v>462755</v>
       </c>
       <c r="R154" t="n">
-        <v>6768894</v>
+        <v>6769176</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16666,10 +16660,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>125017123</v>
+        <v>125017219</v>
       </c>
       <c r="B155" t="n">
-        <v>79428</v>
+        <v>8447</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16678,38 +16672,43 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P155" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>462680</v>
+        <v>462585</v>
       </c>
       <c r="R155" t="n">
-        <v>6769027</v>
+        <v>6769050</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16768,10 +16767,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>125017240</v>
+        <v>125017190</v>
       </c>
       <c r="B156" t="n">
-        <v>58191</v>
+        <v>57529</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16780,20 +16779,20 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>103044</v>
+        <v>100049</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -16802,16 +16801,21 @@
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P156" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>462248</v>
+        <v>462791</v>
       </c>
       <c r="R156" t="n">
-        <v>6768584</v>
+        <v>6769257</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16870,10 +16874,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>125017268</v>
+        <v>125017265</v>
       </c>
       <c r="B157" t="n">
-        <v>92293</v>
+        <v>78810</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16882,47 +16886,38 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>462470</v>
+        <v>462762</v>
       </c>
       <c r="R157" t="n">
-        <v>6768894</v>
+        <v>6769125</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16981,10 +16976,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>125017252</v>
+        <v>125017117</v>
       </c>
       <c r="B158" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16997,21 +16992,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17021,10 +17016,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>462426</v>
+        <v>462501</v>
       </c>
       <c r="R158" t="n">
-        <v>6768812</v>
+        <v>6768895</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17083,10 +17078,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>125017188</v>
+        <v>125017256</v>
       </c>
       <c r="B159" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -17099,39 +17094,34 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P159" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>462760</v>
+        <v>462409</v>
       </c>
       <c r="R159" t="n">
-        <v>6769122</v>
+        <v>6768798</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17190,10 +17180,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>125017258</v>
+        <v>125017268</v>
       </c>
       <c r="B160" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17202,38 +17192,47 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P160" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>462449</v>
+        <v>462470</v>
       </c>
       <c r="R160" t="n">
-        <v>6768783</v>
+        <v>6768894</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17292,10 +17291,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>125017170</v>
+        <v>125017280</v>
       </c>
       <c r="B161" t="n">
-        <v>91012</v>
+        <v>96227</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17304,25 +17303,25 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17332,10 +17331,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>462313</v>
+        <v>462403</v>
       </c>
       <c r="R161" t="n">
-        <v>6768749</v>
+        <v>6768799</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17394,10 +17393,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>125001616</v>
+        <v>125017264</v>
       </c>
       <c r="B162" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17406,43 +17405,38 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P162" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>462456</v>
+        <v>462713</v>
       </c>
       <c r="R162" t="n">
-        <v>6768778</v>
+        <v>6769148</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17477,11 +17471,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC162" t="inlineStr">
-        <is>
-          <t>Miljöbilder. Så kallad tjädertall</t>
-        </is>
-      </c>
       <c r="AD162" t="b">
         <v>0</v>
       </c>
@@ -17494,22 +17483,22 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>125000794</v>
+        <v>125017285</v>
       </c>
       <c r="B163" t="n">
-        <v>78810</v>
+        <v>91065</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17518,25 +17507,25 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6425</v>
+        <v>5321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17546,10 +17535,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>462420</v>
+        <v>462561</v>
       </c>
       <c r="R163" t="n">
-        <v>6768785</v>
+        <v>6768949</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17586,7 +17575,7 @@
       </c>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>Miljöbild</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17595,25 +17584,26 @@
       <c r="AE163" t="b">
         <v>0</v>
       </c>
+      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>125017130</v>
+        <v>125007648</v>
       </c>
       <c r="B164" t="n">
         <v>79428</v>
@@ -17653,10 +17643,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>462444</v>
+        <v>462431</v>
       </c>
       <c r="R164" t="n">
-        <v>6768840</v>
+        <v>6768885</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17691,6 +17681,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD164" t="b">
         <v>0</v>
       </c>
@@ -17703,22 +17698,22 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>125017140</v>
+        <v>125017232</v>
       </c>
       <c r="B165" t="n">
-        <v>78842</v>
+        <v>80763</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -17731,21 +17726,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>185</v>
+        <v>1049</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17755,10 +17750,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>462575</v>
+        <v>462456</v>
       </c>
       <c r="R165" t="n">
-        <v>6768972</v>
+        <v>6768781</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17817,10 +17812,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>125017202</v>
+        <v>125017209</v>
       </c>
       <c r="B166" t="n">
-        <v>91299</v>
+        <v>8447</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -17829,38 +17824,43 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>658</v>
+        <v>106545</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P166" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>462414</v>
+        <v>462777</v>
       </c>
       <c r="R166" t="n">
-        <v>6768758</v>
+        <v>6769237</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17919,10 +17919,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>125017279</v>
+        <v>125017140</v>
       </c>
       <c r="B167" t="n">
-        <v>78455</v>
+        <v>78842</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -17935,21 +17935,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17959,10 +17959,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>462581</v>
+        <v>462575</v>
       </c>
       <c r="R167" t="n">
-        <v>6768944</v>
+        <v>6768972</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>

--- a/artfynd/A 18527-2025 artfynd.xlsx
+++ b/artfynd/A 18527-2025 artfynd.xlsx
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124772212</v>
+        <v>124777762</v>
       </c>
       <c r="B6" t="n">
         <v>57529</v>
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>462184</v>
+        <v>462331</v>
       </c>
       <c r="R6" t="n">
-        <v>6768538</v>
+        <v>6768680</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Miljöbilder</t>
+          <t>Miljöbilder på bland annat angränsande hygge.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,7 +1215,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124777762</v>
+        <v>124772212</v>
       </c>
       <c r="B7" t="n">
         <v>57529</v>
@@ -1260,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>462331</v>
+        <v>462184</v>
       </c>
       <c r="R7" t="n">
-        <v>6768680</v>
+        <v>6768538</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Miljöbilder på bland annat angränsande hygge.</t>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124774975</v>
+        <v>124774056</v>
       </c>
       <c r="B8" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1339,25 +1339,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>462275</v>
+        <v>462291</v>
       </c>
       <c r="R8" t="n">
-        <v>6768714</v>
+        <v>6768602</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1403,11 +1403,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,7 +1429,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124774056</v>
+        <v>124774189</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1474,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462291</v>
+        <v>462287</v>
       </c>
       <c r="R9" t="n">
-        <v>6768602</v>
+        <v>6768630</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124774189</v>
+        <v>124774975</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1548,25 +1543,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462287</v>
+        <v>462275</v>
       </c>
       <c r="R10" t="n">
-        <v>6768630</v>
+        <v>6768714</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1612,6 +1607,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124777178</v>
+        <v>124774634</v>
       </c>
       <c r="B11" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1654,21 +1654,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>462340</v>
+        <v>462257</v>
       </c>
       <c r="R11" t="n">
-        <v>6768649</v>
+        <v>6768691</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124774634</v>
+        <v>124775405</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1756,34 +1756,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>462257</v>
+        <v>462322</v>
       </c>
       <c r="R12" t="n">
-        <v>6768691</v>
+        <v>6768707</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1816,6 +1821,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1842,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124775405</v>
+        <v>124777178</v>
       </c>
       <c r="B13" t="n">
-        <v>57529</v>
+        <v>74901</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1858,39 +1868,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>462322</v>
+        <v>462340</v>
       </c>
       <c r="R13" t="n">
-        <v>6768707</v>
+        <v>6768649</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1923,11 +1928,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -3626,10 +3626,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124771180</v>
+        <v>124773032</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3642,34 +3642,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>462198</v>
+        <v>462235</v>
       </c>
       <c r="R30" t="n">
-        <v>6768579</v>
+        <v>6768533</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3835,10 +3840,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124773032</v>
+        <v>124771180</v>
       </c>
       <c r="B32" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3851,39 +3856,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>462235</v>
+        <v>462198</v>
       </c>
       <c r="R32" t="n">
-        <v>6768533</v>
+        <v>6768579</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -7194,10 +7194,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125001637</v>
+        <v>125001392</v>
       </c>
       <c r="B64" t="n">
-        <v>56722</v>
+        <v>79428</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7206,43 +7206,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>462376</v>
+        <v>462456</v>
       </c>
       <c r="R64" t="n">
-        <v>6768807</v>
+        <v>6768778</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7275,6 +7270,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7301,10 +7301,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124999332</v>
+        <v>125001637</v>
       </c>
       <c r="B65" t="n">
-        <v>79428</v>
+        <v>56722</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7313,38 +7313,43 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>462658</v>
+        <v>462376</v>
       </c>
       <c r="R65" t="n">
-        <v>6769079</v>
+        <v>6768807</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7403,7 +7408,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125001392</v>
+        <v>124999332</v>
       </c>
       <c r="B66" t="n">
         <v>79428</v>
@@ -7443,10 +7448,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>462456</v>
+        <v>462658</v>
       </c>
       <c r="R66" t="n">
-        <v>6768778</v>
+        <v>6769079</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7479,11 +7484,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-05-12</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7923,10 +7923,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124999653</v>
+        <v>125001339</v>
       </c>
       <c r="B71" t="n">
-        <v>79428</v>
+        <v>57529</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7939,34 +7939,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>462598</v>
+        <v>462456</v>
       </c>
       <c r="R71" t="n">
-        <v>6769000</v>
+        <v>6768778</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8030,10 +8035,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125017255</v>
+        <v>124999653</v>
       </c>
       <c r="B72" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8046,21 +8051,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8070,10 +8075,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>462419</v>
+        <v>462598</v>
       </c>
       <c r="R72" t="n">
-        <v>6768798</v>
+        <v>6769000</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8108,6 +8113,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -8120,22 +8130,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125017139</v>
+        <v>125017255</v>
       </c>
       <c r="B73" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8148,21 +8158,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8172,10 +8182,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>462539</v>
+        <v>462419</v>
       </c>
       <c r="R73" t="n">
-        <v>6768915</v>
+        <v>6768798</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8234,10 +8244,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125017228</v>
+        <v>125017139</v>
       </c>
       <c r="B74" t="n">
-        <v>94766</v>
+        <v>78842</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8246,25 +8256,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2412</v>
+        <v>185</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Philonotis fontana</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8274,10 +8284,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>462418</v>
+        <v>462539</v>
       </c>
       <c r="R74" t="n">
-        <v>6768790</v>
+        <v>6768915</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8310,11 +8320,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-05-12</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>I kallkälla</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8341,10 +8346,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125017227</v>
+        <v>125017228</v>
       </c>
       <c r="B75" t="n">
-        <v>94959</v>
+        <v>94766</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8357,21 +8362,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2387</v>
+        <v>2412</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Philonotis fontana</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8381,10 +8386,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>462424</v>
+        <v>462418</v>
       </c>
       <c r="R75" t="n">
-        <v>6768787</v>
+        <v>6768790</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8448,10 +8453,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125017241</v>
+        <v>125017227</v>
       </c>
       <c r="B76" t="n">
-        <v>91026</v>
+        <v>94959</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8460,25 +8465,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1204</v>
+        <v>2387</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8488,10 +8493,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>462418</v>
+        <v>462424</v>
       </c>
       <c r="R76" t="n">
-        <v>6768776</v>
+        <v>6768787</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8524,6 +8529,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>I kallkälla</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8550,10 +8560,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125017284</v>
+        <v>125017241</v>
       </c>
       <c r="B77" t="n">
-        <v>91012</v>
+        <v>91026</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8566,21 +8576,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8590,10 +8600,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>462409</v>
+        <v>462418</v>
       </c>
       <c r="R77" t="n">
-        <v>6768814</v>
+        <v>6768776</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8652,10 +8662,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125001339</v>
+        <v>125017284</v>
       </c>
       <c r="B78" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8668,39 +8678,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>462456</v>
+        <v>462409</v>
       </c>
       <c r="R78" t="n">
-        <v>6768778</v>
+        <v>6768814</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8735,11 +8740,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -8752,12 +8752,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -9804,10 +9804,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125000045</v>
+        <v>125017124</v>
       </c>
       <c r="B89" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9820,34 +9820,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Lädsån, Dlr</t>
+          <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>462482</v>
+        <v>462679</v>
       </c>
       <c r="R89" t="n">
-        <v>6768845</v>
+        <v>6769045</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9894,22 +9894,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125017205</v>
+        <v>125017193</v>
       </c>
       <c r="B90" t="n">
-        <v>8447</v>
+        <v>57529</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9918,31 +9918,31 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -9951,10 +9951,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>462864</v>
+        <v>462585</v>
       </c>
       <c r="R90" t="n">
-        <v>6769317</v>
+        <v>6769050</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10013,10 +10013,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125017166</v>
+        <v>125000045</v>
       </c>
       <c r="B91" t="n">
-        <v>91361</v>
+        <v>78810</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10025,38 +10025,38 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Salutjärnen, Dlr</t>
+          <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>462312</v>
+        <v>462482</v>
       </c>
       <c r="R91" t="n">
-        <v>6768750</v>
+        <v>6768845</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10103,22 +10103,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125017124</v>
+        <v>125017205</v>
       </c>
       <c r="B92" t="n">
-        <v>79428</v>
+        <v>8447</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10127,38 +10127,43 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>462679</v>
+        <v>462864</v>
       </c>
       <c r="R92" t="n">
-        <v>6769045</v>
+        <v>6769317</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10217,10 +10222,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125017193</v>
+        <v>125017166</v>
       </c>
       <c r="B93" t="n">
-        <v>57529</v>
+        <v>91361</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10229,43 +10234,38 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100049</v>
+        <v>2062</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>462585</v>
+        <v>462312</v>
       </c>
       <c r="R93" t="n">
-        <v>6769050</v>
+        <v>6768750</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -12699,10 +12699,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125017270</v>
+        <v>124999425</v>
       </c>
       <c r="B117" t="n">
-        <v>78455</v>
+        <v>8447</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12711,25 +12711,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12739,10 +12739,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>462777</v>
+        <v>462616</v>
       </c>
       <c r="R117" t="n">
-        <v>6769237</v>
+        <v>6769046</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12777,6 +12777,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
+        </is>
+      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
@@ -12789,22 +12794,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>124999425</v>
+        <v>125017186</v>
       </c>
       <c r="B118" t="n">
-        <v>8447</v>
+        <v>57529</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12813,38 +12818,47 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>462616</v>
+        <v>462647</v>
       </c>
       <c r="R118" t="n">
-        <v>6769046</v>
+        <v>6769118</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12879,11 +12893,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
-        </is>
-      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
@@ -12896,22 +12905,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125017186</v>
+        <v>125017225</v>
       </c>
       <c r="B119" t="n">
-        <v>57529</v>
+        <v>8447</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12920,35 +12929,31 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="M119" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -12957,10 +12962,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>462647</v>
+        <v>462449</v>
       </c>
       <c r="R119" t="n">
-        <v>6769118</v>
+        <v>6768765</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13019,10 +13024,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125017225</v>
+        <v>125017240</v>
       </c>
       <c r="B120" t="n">
-        <v>8447</v>
+        <v>58191</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13035,39 +13040,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>106545</v>
+        <v>103044</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>462449</v>
+        <v>462248</v>
       </c>
       <c r="R120" t="n">
-        <v>6768765</v>
+        <v>6768584</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13126,10 +13126,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125017240</v>
+        <v>125017270</v>
       </c>
       <c r="B121" t="n">
-        <v>58191</v>
+        <v>78455</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13138,25 +13138,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>103044</v>
+        <v>353</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13166,10 +13166,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>462248</v>
+        <v>462777</v>
       </c>
       <c r="R121" t="n">
-        <v>6768584</v>
+        <v>6769237</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14064,10 +14064,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>125000666</v>
+        <v>125017257</v>
       </c>
       <c r="B130" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14080,39 +14080,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>462422</v>
+        <v>462417</v>
       </c>
       <c r="R130" t="n">
-        <v>6768811</v>
+        <v>6768771</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14159,22 +14154,22 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125017173</v>
+        <v>125000666</v>
       </c>
       <c r="B131" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14183,31 +14178,31 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="M131" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
@@ -14216,10 +14211,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>462440</v>
+        <v>462422</v>
       </c>
       <c r="R131" t="n">
-        <v>6768764</v>
+        <v>6768811</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14266,22 +14261,22 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125017199</v>
+        <v>125017173</v>
       </c>
       <c r="B132" t="n">
-        <v>96345</v>
+        <v>56722</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14290,38 +14285,43 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>54</v>
+        <v>100138</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Skogstrappmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Anastrophyllum michauxii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(F.Weber.) H.Buch</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>462249</v>
+        <v>462440</v>
       </c>
       <c r="R132" t="n">
-        <v>6768580</v>
+        <v>6768764</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14362,7 +14362,6 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -14381,10 +14380,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125017142</v>
+        <v>125017199</v>
       </c>
       <c r="B133" t="n">
-        <v>78842</v>
+        <v>96345</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14397,21 +14396,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>185</v>
+        <v>54</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skogstrappmossa</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Anastrophyllum michauxii</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(F.Weber.) H.Buch</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14421,10 +14420,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>462682</v>
+        <v>462249</v>
       </c>
       <c r="R133" t="n">
-        <v>6769024</v>
+        <v>6768580</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14465,6 +14464,7 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -14483,10 +14483,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125017257</v>
+        <v>125017142</v>
       </c>
       <c r="B134" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14499,21 +14499,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14523,10 +14523,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>462417</v>
+        <v>462682</v>
       </c>
       <c r="R134" t="n">
-        <v>6768771</v>
+        <v>6769024</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14687,10 +14687,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125017282</v>
+        <v>125017278</v>
       </c>
       <c r="B136" t="n">
-        <v>78194</v>
+        <v>78455</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14703,21 +14703,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14727,10 +14727,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>462759</v>
+        <v>462544</v>
       </c>
       <c r="R136" t="n">
-        <v>6769121</v>
+        <v>6768928</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14789,10 +14789,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125017278</v>
+        <v>125017282</v>
       </c>
       <c r="B137" t="n">
-        <v>78455</v>
+        <v>78194</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -14805,21 +14805,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14829,10 +14829,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>462544</v>
+        <v>462759</v>
       </c>
       <c r="R137" t="n">
-        <v>6768928</v>
+        <v>6769121</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>

--- a/artfynd/A 18527-2025 artfynd.xlsx
+++ b/artfynd/A 18527-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124774922</v>
+        <v>124774494</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>8447</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>462275</v>
+        <v>462257</v>
       </c>
       <c r="R2" t="n">
-        <v>6768714</v>
+        <v>6768691</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124774814</v>
+        <v>124777178</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>74901</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>462257</v>
+        <v>462340</v>
       </c>
       <c r="R3" t="n">
-        <v>6768691</v>
+        <v>6768649</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124781784</v>
+        <v>124772894</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>74901</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,39 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462362</v>
+        <v>462230</v>
       </c>
       <c r="R4" t="n">
-        <v>6768766</v>
+        <v>6768556</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124776266</v>
+        <v>124778690</v>
       </c>
       <c r="B5" t="n">
         <v>57529</v>
@@ -1041,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462311</v>
+        <v>462388</v>
       </c>
       <c r="R5" t="n">
-        <v>6768690</v>
+        <v>6768696</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1077,6 +1062,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124777762</v>
+        <v>124775446</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,39 +1109,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>462331</v>
+        <v>462341</v>
       </c>
       <c r="R6" t="n">
-        <v>6768680</v>
+        <v>6768708</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,11 +1169,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Miljöbilder på bland annat angränsande hygge.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124772212</v>
+        <v>124776376</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>74901</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,39 +1211,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>462184</v>
+        <v>462311</v>
       </c>
       <c r="R7" t="n">
-        <v>6768538</v>
+        <v>6768690</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,11 +1271,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124774056</v>
+        <v>124774558</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1367,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>462291</v>
+        <v>462257</v>
       </c>
       <c r="R8" t="n">
-        <v>6768602</v>
+        <v>6768691</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124774189</v>
+        <v>124781784</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1445,34 +1415,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462287</v>
+        <v>462362</v>
       </c>
       <c r="R9" t="n">
-        <v>6768630</v>
+        <v>6768766</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124774975</v>
+        <v>124774922</v>
       </c>
       <c r="B10" t="n">
-        <v>8447</v>
+        <v>57529</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1543,28 +1518,33 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
@@ -1607,11 +1587,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124774634</v>
+        <v>124773032</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1654,34 +1629,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>462257</v>
+        <v>462235</v>
       </c>
       <c r="R11" t="n">
-        <v>6768691</v>
+        <v>6768533</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,7 +1720,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124775405</v>
+        <v>124777762</v>
       </c>
       <c r="B12" t="n">
         <v>57529</v>
@@ -1785,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>462322</v>
+        <v>462331</v>
       </c>
       <c r="R12" t="n">
-        <v>6768707</v>
+        <v>6768680</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1805,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Miljöbilder</t>
+          <t>Miljöbilder på bland annat angränsande hygge.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124777178</v>
+        <v>124782169</v>
       </c>
       <c r="B13" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1868,21 +1848,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1892,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>462340</v>
+        <v>462456</v>
       </c>
       <c r="R13" t="n">
-        <v>6768649</v>
+        <v>6768800</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1954,10 +1934,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124774845</v>
+        <v>124776291</v>
       </c>
       <c r="B14" t="n">
-        <v>8447</v>
+        <v>57529</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1966,38 +1946,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>462271</v>
+        <v>462311</v>
       </c>
       <c r="R14" t="n">
-        <v>6768703</v>
+        <v>6768690</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2056,7 +2041,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124781860</v>
+        <v>124774056</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2096,10 +2081,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>462362</v>
+        <v>462291</v>
       </c>
       <c r="R15" t="n">
-        <v>6768766</v>
+        <v>6768602</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2132,11 +2117,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2270,10 +2250,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124781915</v>
+        <v>124774845</v>
       </c>
       <c r="B17" t="n">
-        <v>57529</v>
+        <v>8447</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2282,43 +2262,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>462389</v>
+        <v>462271</v>
       </c>
       <c r="R17" t="n">
-        <v>6768770</v>
+        <v>6768703</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2377,10 +2352,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124776534</v>
+        <v>124772212</v>
       </c>
       <c r="B18" t="n">
-        <v>74901</v>
+        <v>57529</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2393,34 +2368,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>462302</v>
+        <v>462184</v>
       </c>
       <c r="R18" t="n">
-        <v>6768675</v>
+        <v>6768538</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2484,10 +2464,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124774463</v>
+        <v>124781915</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2500,34 +2480,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>462264</v>
+        <v>462389</v>
       </c>
       <c r="R19" t="n">
-        <v>6768671</v>
+        <v>6768770</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2586,10 +2571,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124772023</v>
+        <v>124777471</v>
       </c>
       <c r="B20" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2602,39 +2587,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>462234</v>
+        <v>462331</v>
       </c>
       <c r="R20" t="n">
-        <v>6768605</v>
+        <v>6768680</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2667,11 +2647,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2698,10 +2673,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124775446</v>
+        <v>124776534</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2714,21 +2689,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2738,10 +2713,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>462341</v>
+        <v>462302</v>
       </c>
       <c r="R21" t="n">
-        <v>6768708</v>
+        <v>6768675</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2774,6 +2749,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2800,7 +2780,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124781969</v>
+        <v>124774463</v>
       </c>
       <c r="B22" t="n">
         <v>78810</v>
@@ -2840,10 +2820,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>462389</v>
+        <v>462264</v>
       </c>
       <c r="R22" t="n">
-        <v>6768770</v>
+        <v>6768671</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2902,7 +2882,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124777598</v>
+        <v>124771180</v>
       </c>
       <c r="B23" t="n">
         <v>78810</v>
@@ -2942,10 +2922,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>462331</v>
+        <v>462198</v>
       </c>
       <c r="R23" t="n">
-        <v>6768680</v>
+        <v>6768579</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3004,10 +2984,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124770579</v>
+        <v>124770632</v>
       </c>
       <c r="B24" t="n">
-        <v>74901</v>
+        <v>57529</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3020,24 +3000,29 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
@@ -3080,6 +3065,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3106,10 +3096,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124775105</v>
+        <v>124771314</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3122,37 +3112,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>462281</v>
+        <v>462210</v>
       </c>
       <c r="R25" t="n">
-        <v>6768705</v>
+        <v>6768591</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3182,11 +3177,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3213,7 +3203,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124778521</v>
+        <v>124775105</v>
       </c>
       <c r="B26" t="n">
         <v>78810</v>
@@ -3253,10 +3243,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>462386</v>
+        <v>462281</v>
       </c>
       <c r="R26" t="n">
-        <v>6768724</v>
+        <v>6768705</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3293,7 +3283,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Miljöbilder för närområdet. Hygget börjar bakom lågorna</t>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3320,7 +3310,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124782169</v>
+        <v>124781969</v>
       </c>
       <c r="B27" t="n">
         <v>78810</v>
@@ -3360,10 +3350,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>462456</v>
+        <v>462389</v>
       </c>
       <c r="R27" t="n">
-        <v>6768800</v>
+        <v>6768770</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3422,10 +3412,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124774494</v>
+        <v>124774814</v>
       </c>
       <c r="B28" t="n">
-        <v>8447</v>
+        <v>57529</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3434,28 +3424,33 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
@@ -3524,10 +3519,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124772894</v>
+        <v>124775405</v>
       </c>
       <c r="B29" t="n">
-        <v>74901</v>
+        <v>57529</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3540,34 +3535,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>462230</v>
+        <v>462322</v>
       </c>
       <c r="R29" t="n">
-        <v>6768556</v>
+        <v>6768707</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3600,6 +3600,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3626,10 +3631,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124773032</v>
+        <v>124774189</v>
       </c>
       <c r="B30" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3642,39 +3647,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>462235</v>
+        <v>462287</v>
       </c>
       <c r="R30" t="n">
-        <v>6768533</v>
+        <v>6768630</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3733,10 +3733,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124771314</v>
+        <v>124774975</v>
       </c>
       <c r="B31" t="n">
-        <v>57666</v>
+        <v>8447</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3745,46 +3745,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>462210</v>
+        <v>462275</v>
       </c>
       <c r="R31" t="n">
-        <v>6768591</v>
+        <v>6768714</v>
       </c>
       <c r="S31" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3814,6 +3809,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3840,7 +3840,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124771180</v>
+        <v>124781860</v>
       </c>
       <c r="B32" t="n">
         <v>78810</v>
@@ -3880,10 +3880,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>462198</v>
+        <v>462362</v>
       </c>
       <c r="R32" t="n">
-        <v>6768579</v>
+        <v>6768766</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3916,6 +3916,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3942,10 +3947,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124776376</v>
+        <v>124782138</v>
       </c>
       <c r="B33" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3958,21 +3963,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3982,10 +3987,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>462311</v>
+        <v>462447</v>
       </c>
       <c r="R33" t="n">
-        <v>6768690</v>
+        <v>6768805</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4044,10 +4049,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124778690</v>
+        <v>124770579</v>
       </c>
       <c r="B34" t="n">
-        <v>57529</v>
+        <v>74901</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4060,39 +4065,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>462388</v>
+        <v>462182</v>
       </c>
       <c r="R34" t="n">
-        <v>6768696</v>
+        <v>6768583</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4125,11 +4125,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4156,7 +4151,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124770632</v>
+        <v>124772023</v>
       </c>
       <c r="B35" t="n">
         <v>57529</v>
@@ -4192,7 +4187,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4201,10 +4196,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>462182</v>
+        <v>462234</v>
       </c>
       <c r="R35" t="n">
-        <v>6768583</v>
+        <v>6768605</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4241,7 +4236,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Miljöbilder.</t>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4268,7 +4263,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124782138</v>
+        <v>124778521</v>
       </c>
       <c r="B36" t="n">
         <v>78810</v>
@@ -4308,10 +4303,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>462447</v>
+        <v>462386</v>
       </c>
       <c r="R36" t="n">
-        <v>6768805</v>
+        <v>6768724</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4344,6 +4339,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Miljöbilder för närområdet. Hygget börjar bakom lågorna</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4370,7 +4370,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124833941</v>
+        <v>124833451</v>
       </c>
       <c r="B37" t="n">
         <v>8447</v>
@@ -4410,10 +4410,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>462816</v>
+        <v>462818</v>
       </c>
       <c r="R37" t="n">
-        <v>6769191</v>
+        <v>6769164</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4446,11 +4446,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Miljöbilder för närområdet.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4477,10 +4472,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124834239</v>
+        <v>124835245</v>
       </c>
       <c r="B38" t="n">
-        <v>79428</v>
+        <v>78546</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4493,21 +4488,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4584,10 +4579,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124825418</v>
+        <v>124834191</v>
       </c>
       <c r="B39" t="n">
-        <v>8447</v>
+        <v>79428</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4596,25 +4591,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4624,10 +4619,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>462844</v>
+        <v>462814</v>
       </c>
       <c r="R39" t="n">
-        <v>6769302</v>
+        <v>6769220</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4686,10 +4681,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124835714</v>
+        <v>124838423</v>
       </c>
       <c r="B40" t="n">
-        <v>8447</v>
+        <v>57529</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4698,38 +4693,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Salutjärnen, Dlr</t>
+          <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>462814</v>
+        <v>462456</v>
       </c>
       <c r="R40" t="n">
-        <v>6769220</v>
+        <v>6768914</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4900,10 +4895,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124836354</v>
+        <v>124836527</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4916,21 +4911,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4980,7 +4975,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Miljöbild, garnlav i äldre tall.</t>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5007,10 +5002,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124836148</v>
+        <v>124836354</v>
       </c>
       <c r="B43" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5023,21 +5018,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5047,10 +5042,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>462741</v>
+        <v>462712</v>
       </c>
       <c r="R43" t="n">
-        <v>6769142</v>
+        <v>6769143</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5087,7 +5082,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Miljöbild</t>
+          <t>Miljöbild, garnlav i äldre tall.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5114,7 +5109,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124834205</v>
+        <v>124836445</v>
       </c>
       <c r="B44" t="n">
         <v>78546</v>
@@ -5154,10 +5149,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>462814</v>
+        <v>462712</v>
       </c>
       <c r="R44" t="n">
-        <v>6769220</v>
+        <v>6769143</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5221,10 +5216,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124838423</v>
+        <v>124835714</v>
       </c>
       <c r="B45" t="n">
-        <v>57529</v>
+        <v>8447</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5233,38 +5228,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lädsån, Dlr</t>
+          <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>462456</v>
+        <v>462814</v>
       </c>
       <c r="R45" t="n">
-        <v>6768914</v>
+        <v>6769220</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5328,10 +5323,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124836445</v>
+        <v>124833941</v>
       </c>
       <c r="B46" t="n">
-        <v>78546</v>
+        <v>8447</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5340,25 +5335,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5368,10 +5363,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>462712</v>
+        <v>462816</v>
       </c>
       <c r="R46" t="n">
-        <v>6769143</v>
+        <v>6769191</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5408,7 +5403,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Miljöbild</t>
+          <t>Miljöbilder för närområdet.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5435,10 +5430,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124836527</v>
+        <v>124836148</v>
       </c>
       <c r="B47" t="n">
-        <v>79399</v>
+        <v>78546</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5451,21 +5446,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5475,10 +5470,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>462712</v>
+        <v>462741</v>
       </c>
       <c r="R47" t="n">
-        <v>6769143</v>
+        <v>6769142</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5542,7 +5537,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124833451</v>
+        <v>124825418</v>
       </c>
       <c r="B48" t="n">
         <v>8447</v>
@@ -5582,10 +5577,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>462818</v>
+        <v>462844</v>
       </c>
       <c r="R48" t="n">
-        <v>6769164</v>
+        <v>6769302</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5644,10 +5639,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124999865</v>
+        <v>125000045</v>
       </c>
       <c r="B49" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5660,29 +5655,24 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
@@ -5751,10 +5741,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125000745</v>
+        <v>125017245</v>
       </c>
       <c r="B50" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5767,39 +5757,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>462414</v>
+        <v>462867</v>
       </c>
       <c r="R50" t="n">
-        <v>6768796</v>
+        <v>6769346</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5834,11 +5819,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5851,22 +5831,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125017156</v>
+        <v>125017162</v>
       </c>
       <c r="B51" t="n">
-        <v>96354</v>
+        <v>79428</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5879,21 +5859,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>53</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5903,10 +5883,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>462418</v>
+        <v>462763</v>
       </c>
       <c r="R51" t="n">
-        <v>6768776</v>
+        <v>6769126</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5965,10 +5945,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125017171</v>
+        <v>125017140</v>
       </c>
       <c r="B52" t="n">
-        <v>91012</v>
+        <v>78842</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5981,21 +5961,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6005,10 +5985,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>462425</v>
+        <v>462575</v>
       </c>
       <c r="R52" t="n">
-        <v>6768807</v>
+        <v>6768972</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6067,10 +6047,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125017115</v>
+        <v>125017279</v>
       </c>
       <c r="B53" t="n">
-        <v>79428</v>
+        <v>78455</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6083,21 +6063,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6107,10 +6087,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>462449</v>
+        <v>462581</v>
       </c>
       <c r="R53" t="n">
-        <v>6768835</v>
+        <v>6768944</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6169,7 +6149,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125017250</v>
+        <v>125017255</v>
       </c>
       <c r="B54" t="n">
         <v>78810</v>
@@ -6209,10 +6189,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>462364</v>
+        <v>462419</v>
       </c>
       <c r="R54" t="n">
-        <v>6768755</v>
+        <v>6768798</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6271,10 +6251,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125017204</v>
+        <v>125017185</v>
       </c>
       <c r="B55" t="n">
-        <v>96979</v>
+        <v>98122</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6287,21 +6267,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6311,10 +6291,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>462438</v>
+        <v>462417</v>
       </c>
       <c r="R55" t="n">
-        <v>6768787</v>
+        <v>6768771</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6373,10 +6353,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125017234</v>
+        <v>125017127</v>
       </c>
       <c r="B56" t="n">
-        <v>78546</v>
+        <v>79428</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6389,21 +6369,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6413,10 +6393,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>462501</v>
+        <v>462685</v>
       </c>
       <c r="R56" t="n">
-        <v>6768890</v>
+        <v>6769071</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6475,7 +6455,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125017113</v>
+        <v>125017112</v>
       </c>
       <c r="B57" t="n">
         <v>79428</v>
@@ -6515,10 +6495,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>462356</v>
+        <v>462453</v>
       </c>
       <c r="R57" t="n">
-        <v>6768753</v>
+        <v>6768876</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6577,10 +6557,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125017137</v>
+        <v>125017122</v>
       </c>
       <c r="B58" t="n">
-        <v>78842</v>
+        <v>79428</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6593,21 +6573,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6617,10 +6597,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>462506</v>
+        <v>462688</v>
       </c>
       <c r="R58" t="n">
-        <v>6768894</v>
+        <v>6769019</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6679,10 +6659,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125017263</v>
+        <v>125017232</v>
       </c>
       <c r="B59" t="n">
-        <v>78810</v>
+        <v>80763</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6695,21 +6675,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6719,10 +6699,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>462712</v>
+        <v>462456</v>
       </c>
       <c r="R59" t="n">
-        <v>6769149</v>
+        <v>6768781</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6781,10 +6761,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125017260</v>
+        <v>125017142</v>
       </c>
       <c r="B60" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6797,21 +6777,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6821,10 +6801,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>462575</v>
+        <v>462682</v>
       </c>
       <c r="R60" t="n">
-        <v>6768974</v>
+        <v>6769024</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6883,10 +6863,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125017157</v>
+        <v>125017154</v>
       </c>
       <c r="B61" t="n">
-        <v>90977</v>
+        <v>96354</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6895,25 +6875,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6923,10 +6903,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>462431</v>
+        <v>462433</v>
       </c>
       <c r="R61" t="n">
-        <v>6768769</v>
+        <v>6768784</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6985,10 +6965,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125007719</v>
+        <v>125001616</v>
       </c>
       <c r="B62" t="n">
-        <v>79428</v>
+        <v>56722</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6997,38 +6977,43 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Lädsån, Dlr</t>
+          <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
         <v>462456</v>
       </c>
       <c r="R62" t="n">
-        <v>6768884</v>
+        <v>6768778</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7065,7 +7050,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Miljöbild</t>
+          <t>Miljöbilder. Så kallad tjädertall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7092,10 +7077,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124999142</v>
+        <v>124999190</v>
       </c>
       <c r="B63" t="n">
-        <v>78842</v>
+        <v>8447</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7104,25 +7089,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7132,10 +7117,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>462684</v>
+        <v>462672</v>
       </c>
       <c r="R63" t="n">
-        <v>6769117</v>
+        <v>6769113</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7194,10 +7179,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125001392</v>
+        <v>125017258</v>
       </c>
       <c r="B64" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7210,21 +7195,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7234,10 +7219,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>462456</v>
+        <v>462449</v>
       </c>
       <c r="R64" t="n">
-        <v>6768778</v>
+        <v>6768783</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7272,11 +7257,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -7289,22 +7269,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125001637</v>
+        <v>125017238</v>
       </c>
       <c r="B65" t="n">
-        <v>56722</v>
+        <v>78546</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7313,43 +7293,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>462376</v>
+        <v>462685</v>
       </c>
       <c r="R65" t="n">
-        <v>6768807</v>
+        <v>6769071</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7396,19 +7371,19 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124999332</v>
+        <v>125008171</v>
       </c>
       <c r="B66" t="n">
         <v>79428</v>
@@ -7444,14 +7419,14 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Salutjärnen, Dlr</t>
+          <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>462658</v>
+        <v>462456</v>
       </c>
       <c r="R66" t="n">
-        <v>6769079</v>
+        <v>6768884</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7484,6 +7459,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7510,10 +7490,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124999177</v>
+        <v>125017202</v>
       </c>
       <c r="B67" t="n">
-        <v>57529</v>
+        <v>91299</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7526,39 +7506,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>462684</v>
+        <v>462414</v>
       </c>
       <c r="R67" t="n">
-        <v>6769117</v>
+        <v>6768758</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7605,22 +7580,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125017251</v>
+        <v>125017136</v>
       </c>
       <c r="B68" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7633,21 +7608,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7657,10 +7632,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>462357</v>
+        <v>462449</v>
       </c>
       <c r="R68" t="n">
-        <v>6768775</v>
+        <v>6768898</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7719,10 +7694,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125017122</v>
+        <v>125017141</v>
       </c>
       <c r="B69" t="n">
-        <v>79428</v>
+        <v>78842</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7735,21 +7710,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7759,10 +7734,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>462688</v>
+        <v>462579</v>
       </c>
       <c r="R69" t="n">
-        <v>6769019</v>
+        <v>6768990</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7821,10 +7796,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125017259</v>
+        <v>125004378</v>
       </c>
       <c r="B70" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7837,34 +7812,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Salutjärnen, Dlr</t>
+          <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>462444</v>
+        <v>462261</v>
       </c>
       <c r="R70" t="n">
-        <v>6768832</v>
+        <v>6768593</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7899,6 +7879,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -7911,19 +7896,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125001339</v>
+        <v>125017190</v>
       </c>
       <c r="B71" t="n">
         <v>57529</v>
@@ -7959,7 +7944,7 @@
       <c r="I71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -7968,10 +7953,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>462456</v>
+        <v>462791</v>
       </c>
       <c r="R71" t="n">
-        <v>6768778</v>
+        <v>6769257</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8006,11 +7991,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -8023,22 +8003,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124999653</v>
+        <v>124999027</v>
       </c>
       <c r="B72" t="n">
-        <v>79428</v>
+        <v>57529</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8051,21 +8031,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8075,10 +8055,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>462598</v>
+        <v>462741</v>
       </c>
       <c r="R72" t="n">
-        <v>6769000</v>
+        <v>6769142</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8115,7 +8095,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Miljöbild</t>
+          <t>Miljöbilder. Sannoligt bohål/hackhål efter spillkråka.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8142,7 +8122,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125017255</v>
+        <v>125017262</v>
       </c>
       <c r="B73" t="n">
         <v>78810</v>
@@ -8182,10 +8162,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>462419</v>
+        <v>462703</v>
       </c>
       <c r="R73" t="n">
-        <v>6768798</v>
+        <v>6769146</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8244,10 +8224,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125017139</v>
+        <v>125001767</v>
       </c>
       <c r="B74" t="n">
-        <v>78842</v>
+        <v>57529</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8260,34 +8240,39 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Salutjärnen, Dlr</t>
+          <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>462539</v>
+        <v>462346</v>
       </c>
       <c r="R74" t="n">
-        <v>6768915</v>
+        <v>6768794</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8322,6 +8307,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -8334,22 +8324,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125017228</v>
+        <v>125017193</v>
       </c>
       <c r="B75" t="n">
-        <v>94766</v>
+        <v>57529</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8358,38 +8348,43 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2412</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Philonotis fontana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>462418</v>
+        <v>462585</v>
       </c>
       <c r="R75" t="n">
-        <v>6768790</v>
+        <v>6769050</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8422,11 +8417,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-05-12</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>I kallkälla</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8453,10 +8443,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125017227</v>
+        <v>125017173</v>
       </c>
       <c r="B76" t="n">
-        <v>94959</v>
+        <v>56722</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8469,34 +8459,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2387</v>
+        <v>100138</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>462424</v>
+        <v>462440</v>
       </c>
       <c r="R76" t="n">
-        <v>6768787</v>
+        <v>6768764</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8529,11 +8524,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-05-12</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>I kallkälla</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8560,10 +8550,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125017241</v>
+        <v>125017225</v>
       </c>
       <c r="B77" t="n">
-        <v>91026</v>
+        <v>8447</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8572,38 +8562,43 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1204</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>462418</v>
+        <v>462449</v>
       </c>
       <c r="R77" t="n">
-        <v>6768776</v>
+        <v>6768765</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8662,10 +8657,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125017284</v>
+        <v>125017123</v>
       </c>
       <c r="B78" t="n">
-        <v>91012</v>
+        <v>79428</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8678,21 +8673,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8702,10 +8697,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>462409</v>
+        <v>462680</v>
       </c>
       <c r="R78" t="n">
-        <v>6768814</v>
+        <v>6769027</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8764,10 +8759,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125017198</v>
+        <v>125007648</v>
       </c>
       <c r="B79" t="n">
-        <v>57529</v>
+        <v>79428</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8780,39 +8775,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>462452</v>
+        <v>462431</v>
       </c>
       <c r="R79" t="n">
-        <v>6768897</v>
+        <v>6768885</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8847,6 +8837,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -8859,19 +8854,19 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125017262</v>
+        <v>125017259</v>
       </c>
       <c r="B80" t="n">
         <v>78810</v>
@@ -8911,10 +8906,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>462703</v>
+        <v>462444</v>
       </c>
       <c r="R80" t="n">
-        <v>6769146</v>
+        <v>6768832</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8973,7 +8968,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125017273</v>
+        <v>125017270</v>
       </c>
       <c r="B81" t="n">
         <v>78455</v>
@@ -9013,10 +9008,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>462642</v>
+        <v>462777</v>
       </c>
       <c r="R81" t="n">
-        <v>6769092</v>
+        <v>6769237</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9075,10 +9070,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125017112</v>
+        <v>125000666</v>
       </c>
       <c r="B82" t="n">
-        <v>79428</v>
+        <v>57529</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9091,34 +9086,39 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>462453</v>
+        <v>462422</v>
       </c>
       <c r="R82" t="n">
-        <v>6768876</v>
+        <v>6768811</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9165,22 +9165,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125017141</v>
+        <v>125017212</v>
       </c>
       <c r="B83" t="n">
-        <v>78842</v>
+        <v>8447</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9189,38 +9189,43 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>462579</v>
+        <v>462295</v>
       </c>
       <c r="R83" t="n">
-        <v>6768990</v>
+        <v>6768622</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9279,10 +9284,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125017135</v>
+        <v>125017251</v>
       </c>
       <c r="B84" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9295,21 +9300,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9319,10 +9324,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>462439</v>
+        <v>462357</v>
       </c>
       <c r="R84" t="n">
-        <v>6768813</v>
+        <v>6768775</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9381,10 +9386,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125017224</v>
+        <v>125001145</v>
       </c>
       <c r="B85" t="n">
-        <v>78547</v>
+        <v>79428</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9397,21 +9402,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9421,10 +9426,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>462683</v>
+        <v>462456</v>
       </c>
       <c r="R85" t="n">
-        <v>6769060</v>
+        <v>6768778</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9459,6 +9464,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -9471,19 +9481,19 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125007547</v>
+        <v>125017128</v>
       </c>
       <c r="B86" t="n">
         <v>79428</v>
@@ -9523,10 +9533,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>462441</v>
+        <v>462680</v>
       </c>
       <c r="R86" t="n">
-        <v>6768886</v>
+        <v>6769078</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9561,11 +9571,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -9578,22 +9583,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125017236</v>
+        <v>125001339</v>
       </c>
       <c r="B87" t="n">
-        <v>78546</v>
+        <v>57529</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9606,34 +9611,39 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>462688</v>
+        <v>462456</v>
       </c>
       <c r="R87" t="n">
-        <v>6769019</v>
+        <v>6768778</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9668,6 +9678,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
@@ -9680,22 +9695,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125001616</v>
+        <v>125017113</v>
       </c>
       <c r="B88" t="n">
-        <v>56722</v>
+        <v>79428</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9704,43 +9719,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>462456</v>
+        <v>462356</v>
       </c>
       <c r="R88" t="n">
-        <v>6768778</v>
+        <v>6768753</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9775,11 +9785,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Miljöbilder. Så kallad tjädertall</t>
-        </is>
-      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
@@ -9792,19 +9797,19 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125017124</v>
+        <v>125017105</v>
       </c>
       <c r="B89" t="n">
         <v>79428</v>
@@ -9844,10 +9849,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>462679</v>
+        <v>462811</v>
       </c>
       <c r="R89" t="n">
-        <v>6769045</v>
+        <v>6769258</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9906,10 +9911,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125017193</v>
+        <v>125000745</v>
       </c>
       <c r="B90" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9922,16 +9927,16 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -9942,7 +9947,7 @@
       <c r="I90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -9951,10 +9956,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>462585</v>
+        <v>462414</v>
       </c>
       <c r="R90" t="n">
-        <v>6769050</v>
+        <v>6768796</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9989,6 +9994,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
+        </is>
+      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
@@ -10001,22 +10011,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125000045</v>
+        <v>125017240</v>
       </c>
       <c r="B91" t="n">
-        <v>78810</v>
+        <v>58191</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10025,38 +10035,38 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>103044</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Lädsån, Dlr</t>
+          <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>462482</v>
+        <v>462248</v>
       </c>
       <c r="R91" t="n">
-        <v>6768845</v>
+        <v>6768584</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10103,22 +10113,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125017205</v>
+        <v>124999240</v>
       </c>
       <c r="B92" t="n">
-        <v>8447</v>
+        <v>79428</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10127,43 +10137,38 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>462864</v>
+        <v>462658</v>
       </c>
       <c r="R92" t="n">
-        <v>6769317</v>
+        <v>6769079</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10210,22 +10215,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125017166</v>
+        <v>125017155</v>
       </c>
       <c r="B93" t="n">
-        <v>91361</v>
+        <v>96354</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10234,25 +10239,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2062</v>
+        <v>53</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10262,10 +10267,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>462312</v>
+        <v>462427</v>
       </c>
       <c r="R93" t="n">
-        <v>6768750</v>
+        <v>6768776</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10324,10 +10329,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125017252</v>
+        <v>125017205</v>
       </c>
       <c r="B94" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10336,38 +10341,43 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>462426</v>
+        <v>462864</v>
       </c>
       <c r="R94" t="n">
-        <v>6768812</v>
+        <v>6769317</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10426,10 +10436,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125017105</v>
+        <v>125017263</v>
       </c>
       <c r="B95" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10442,21 +10452,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10466,10 +10476,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>462811</v>
+        <v>462712</v>
       </c>
       <c r="R95" t="n">
-        <v>6769258</v>
+        <v>6769149</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10528,10 +10538,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125017125</v>
+        <v>125017264</v>
       </c>
       <c r="B96" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10544,21 +10554,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10568,10 +10578,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>462683</v>
+        <v>462713</v>
       </c>
       <c r="R96" t="n">
-        <v>6769060</v>
+        <v>6769148</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10630,10 +10640,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125017128</v>
+        <v>125017138</v>
       </c>
       <c r="B97" t="n">
-        <v>79428</v>
+        <v>78842</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10646,21 +10656,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10670,10 +10680,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>462680</v>
+        <v>462516</v>
       </c>
       <c r="R97" t="n">
-        <v>6769078</v>
+        <v>6768902</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10732,10 +10742,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125017134</v>
+        <v>125017227</v>
       </c>
       <c r="B98" t="n">
-        <v>78842</v>
+        <v>94959</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10744,25 +10754,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>185</v>
+        <v>2387</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10772,10 +10782,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>462385</v>
+        <v>462424</v>
       </c>
       <c r="R98" t="n">
-        <v>6768840</v>
+        <v>6768787</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10808,6 +10818,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>I kallkälla</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10834,7 +10849,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125017127</v>
+        <v>125017125</v>
       </c>
       <c r="B99" t="n">
         <v>79428</v>
@@ -10874,10 +10889,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>462685</v>
+        <v>462683</v>
       </c>
       <c r="R99" t="n">
-        <v>6769071</v>
+        <v>6769060</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10936,10 +10951,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125017254</v>
+        <v>125000074</v>
       </c>
       <c r="B100" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10952,34 +10967,39 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Salutjärnen, Dlr</t>
+          <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>462424</v>
+        <v>462482</v>
       </c>
       <c r="R100" t="n">
-        <v>6768802</v>
+        <v>6768845</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11026,22 +11046,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125017130</v>
+        <v>124999177</v>
       </c>
       <c r="B101" t="n">
-        <v>79428</v>
+        <v>57529</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11054,34 +11074,39 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>462444</v>
+        <v>462684</v>
       </c>
       <c r="R101" t="n">
-        <v>6768840</v>
+        <v>6769117</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11128,22 +11153,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125017170</v>
+        <v>125017118</v>
       </c>
       <c r="B102" t="n">
-        <v>91012</v>
+        <v>79428</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11156,21 +11181,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11180,10 +11205,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>462313</v>
+        <v>462542</v>
       </c>
       <c r="R102" t="n">
-        <v>6768749</v>
+        <v>6768916</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11242,10 +11267,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125000267</v>
+        <v>125017106</v>
       </c>
       <c r="B103" t="n">
-        <v>8447</v>
+        <v>79428</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11254,38 +11279,38 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Lädsån, Dlr</t>
+          <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>462482</v>
+        <v>462755</v>
       </c>
       <c r="R103" t="n">
-        <v>6768845</v>
+        <v>6769176</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11320,11 +11345,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
-        </is>
-      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
@@ -11337,19 +11357,19 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125000794</v>
+        <v>125017247</v>
       </c>
       <c r="B104" t="n">
         <v>78810</v>
@@ -11389,10 +11409,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>462420</v>
+        <v>462756</v>
       </c>
       <c r="R104" t="n">
-        <v>6768785</v>
+        <v>6769225</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11427,11 +11447,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
@@ -11444,22 +11459,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125017202</v>
+        <v>125017166</v>
       </c>
       <c r="B105" t="n">
-        <v>91299</v>
+        <v>91361</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11468,25 +11483,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>658</v>
+        <v>2062</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11496,10 +11511,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>462414</v>
+        <v>462312</v>
       </c>
       <c r="R105" t="n">
-        <v>6768758</v>
+        <v>6768750</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11558,10 +11573,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125017246</v>
+        <v>125017285</v>
       </c>
       <c r="B106" t="n">
-        <v>78810</v>
+        <v>91065</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11570,25 +11585,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>5321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11598,10 +11613,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>462868</v>
+        <v>462561</v>
       </c>
       <c r="R106" t="n">
-        <v>6769325</v>
+        <v>6768949</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11636,12 +11651,18 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>På asp</t>
+        </is>
+      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -11660,10 +11681,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125017247</v>
+        <v>124999607</v>
       </c>
       <c r="B107" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11676,21 +11697,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11700,10 +11721,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>462756</v>
+        <v>462598</v>
       </c>
       <c r="R107" t="n">
-        <v>6769225</v>
+        <v>6769000</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11738,6 +11759,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
+        </is>
+      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
@@ -11750,22 +11776,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125017277</v>
+        <v>125017253</v>
       </c>
       <c r="B108" t="n">
-        <v>78455</v>
+        <v>78810</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11778,21 +11804,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11802,10 +11828,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>462478</v>
+        <v>462425</v>
       </c>
       <c r="R108" t="n">
-        <v>6768887</v>
+        <v>6768806</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11864,10 +11890,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125017155</v>
+        <v>125017119</v>
       </c>
       <c r="B109" t="n">
-        <v>96354</v>
+        <v>79428</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11880,21 +11906,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>53</v>
+        <v>6453</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11904,10 +11930,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>462427</v>
+        <v>462543</v>
       </c>
       <c r="R109" t="n">
-        <v>6768776</v>
+        <v>6768929</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11966,10 +11992,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125017212</v>
+        <v>125017157</v>
       </c>
       <c r="B110" t="n">
-        <v>8447</v>
+        <v>90977</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11982,39 +12008,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>462295</v>
+        <v>462431</v>
       </c>
       <c r="R110" t="n">
-        <v>6768622</v>
+        <v>6768769</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12073,10 +12094,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125017266</v>
+        <v>125017219</v>
       </c>
       <c r="B111" t="n">
-        <v>92293</v>
+        <v>8447</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12089,31 +12110,27 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -12122,10 +12139,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>462462</v>
+        <v>462585</v>
       </c>
       <c r="R111" t="n">
-        <v>6768863</v>
+        <v>6769050</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12184,10 +12201,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125017185</v>
+        <v>125017204</v>
       </c>
       <c r="B112" t="n">
-        <v>98122</v>
+        <v>96979</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12200,21 +12217,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12224,10 +12241,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>462417</v>
+        <v>462438</v>
       </c>
       <c r="R112" t="n">
-        <v>6768771</v>
+        <v>6768787</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12286,10 +12303,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125017119</v>
+        <v>125000267</v>
       </c>
       <c r="B113" t="n">
-        <v>79428</v>
+        <v>8447</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12298,38 +12315,38 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Salutjärnen, Dlr</t>
+          <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>462543</v>
+        <v>462482</v>
       </c>
       <c r="R113" t="n">
-        <v>6768929</v>
+        <v>6768845</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12364,6 +12381,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
+        </is>
+      </c>
       <c r="AD113" t="b">
         <v>0</v>
       </c>
@@ -12376,22 +12398,22 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125017238</v>
+        <v>125017241</v>
       </c>
       <c r="B114" t="n">
-        <v>78546</v>
+        <v>91026</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12404,21 +12426,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6446</v>
+        <v>1204</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12428,10 +12450,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>462685</v>
+        <v>462418</v>
       </c>
       <c r="R114" t="n">
-        <v>6769071</v>
+        <v>6768776</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12490,10 +12512,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125017279</v>
+        <v>125017170</v>
       </c>
       <c r="B115" t="n">
-        <v>78455</v>
+        <v>91012</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12506,21 +12528,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>353</v>
+        <v>1202</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12530,10 +12552,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>462581</v>
+        <v>462313</v>
       </c>
       <c r="R115" t="n">
-        <v>6768944</v>
+        <v>6768749</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12592,10 +12614,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125017220</v>
+        <v>125017137</v>
       </c>
       <c r="B116" t="n">
-        <v>8447</v>
+        <v>78842</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12604,43 +12626,38 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>462472</v>
+        <v>462506</v>
       </c>
       <c r="R116" t="n">
-        <v>6768856</v>
+        <v>6768894</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12699,10 +12716,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>124999425</v>
+        <v>125017139</v>
       </c>
       <c r="B117" t="n">
-        <v>8447</v>
+        <v>78842</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12711,25 +12728,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12739,10 +12756,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>462616</v>
+        <v>462539</v>
       </c>
       <c r="R117" t="n">
-        <v>6769046</v>
+        <v>6768915</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12777,11 +12794,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
-        </is>
-      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
@@ -12794,22 +12806,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125017186</v>
+        <v>125017117</v>
       </c>
       <c r="B118" t="n">
-        <v>57529</v>
+        <v>79428</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12822,43 +12834,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>462647</v>
+        <v>462501</v>
       </c>
       <c r="R118" t="n">
-        <v>6769118</v>
+        <v>6768895</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12917,10 +12920,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125017225</v>
+        <v>125017256</v>
       </c>
       <c r="B119" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12929,43 +12932,38 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>462449</v>
+        <v>462409</v>
       </c>
       <c r="R119" t="n">
-        <v>6768765</v>
+        <v>6768798</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13024,10 +13022,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125017240</v>
+        <v>125017280</v>
       </c>
       <c r="B120" t="n">
-        <v>58191</v>
+        <v>96227</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13040,21 +13038,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>103044</v>
+        <v>2869</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13064,10 +13062,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>462248</v>
+        <v>462403</v>
       </c>
       <c r="R120" t="n">
-        <v>6768584</v>
+        <v>6768799</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13126,10 +13124,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125017270</v>
+        <v>125017181</v>
       </c>
       <c r="B121" t="n">
-        <v>78455</v>
+        <v>79920</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13138,25 +13136,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>353</v>
+        <v>6462</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13166,10 +13164,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>462777</v>
+        <v>462422</v>
       </c>
       <c r="R121" t="n">
-        <v>6769237</v>
+        <v>6768816</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13202,6 +13200,11 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13228,10 +13231,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125017106</v>
+        <v>125017282</v>
       </c>
       <c r="B122" t="n">
-        <v>79428</v>
+        <v>78194</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13244,21 +13247,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13268,10 +13271,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>462755</v>
+        <v>462759</v>
       </c>
       <c r="R122" t="n">
-        <v>6769176</v>
+        <v>6769121</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13330,10 +13333,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125017188</v>
+        <v>125017277</v>
       </c>
       <c r="B123" t="n">
-        <v>57529</v>
+        <v>78455</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13346,39 +13349,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>462760</v>
+        <v>462478</v>
       </c>
       <c r="R123" t="n">
-        <v>6769122</v>
+        <v>6768887</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13437,10 +13435,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125017181</v>
+        <v>125017135</v>
       </c>
       <c r="B124" t="n">
-        <v>79920</v>
+        <v>78842</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13449,25 +13447,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6462</v>
+        <v>185</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13477,10 +13475,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>462422</v>
+        <v>462439</v>
       </c>
       <c r="R124" t="n">
-        <v>6768816</v>
+        <v>6768813</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13513,11 +13511,6 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-05-12</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13544,10 +13537,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125017253</v>
+        <v>125017134</v>
       </c>
       <c r="B125" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13560,21 +13553,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13584,10 +13577,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>462425</v>
+        <v>462385</v>
       </c>
       <c r="R125" t="n">
-        <v>6768806</v>
+        <v>6768840</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13646,10 +13639,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125017258</v>
+        <v>125017234</v>
       </c>
       <c r="B126" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13662,21 +13655,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13686,10 +13679,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>462449</v>
+        <v>462501</v>
       </c>
       <c r="R126" t="n">
-        <v>6768783</v>
+        <v>6768890</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13748,10 +13741,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125017118</v>
+        <v>125017198</v>
       </c>
       <c r="B127" t="n">
-        <v>79428</v>
+        <v>57529</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13764,34 +13757,39 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>462542</v>
+        <v>462452</v>
       </c>
       <c r="R127" t="n">
-        <v>6768916</v>
+        <v>6768897</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13850,10 +13848,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125017245</v>
+        <v>125017224</v>
       </c>
       <c r="B128" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13866,21 +13864,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13890,10 +13888,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>462867</v>
+        <v>462683</v>
       </c>
       <c r="R128" t="n">
-        <v>6769346</v>
+        <v>6769060</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13952,10 +13950,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125001767</v>
+        <v>125000794</v>
       </c>
       <c r="B129" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13968,39 +13966,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Lädsån, Dlr</t>
+          <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>462346</v>
+        <v>462420</v>
       </c>
       <c r="R129" t="n">
-        <v>6768794</v>
+        <v>6768785</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14166,10 +14159,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125000666</v>
+        <v>125017265</v>
       </c>
       <c r="B131" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14182,39 +14175,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>462422</v>
+        <v>462762</v>
       </c>
       <c r="R131" t="n">
-        <v>6768811</v>
+        <v>6769125</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14261,22 +14249,22 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125017173</v>
+        <v>125017124</v>
       </c>
       <c r="B132" t="n">
-        <v>56722</v>
+        <v>79428</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14285,43 +14273,38 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>462440</v>
+        <v>462679</v>
       </c>
       <c r="R132" t="n">
-        <v>6768764</v>
+        <v>6769045</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14380,10 +14363,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125017199</v>
+        <v>125017237</v>
       </c>
       <c r="B133" t="n">
-        <v>96345</v>
+        <v>78546</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14396,21 +14379,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>54</v>
+        <v>6446</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Skogstrappmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Anastrophyllum michauxii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(F.Weber.) H.Buch</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14420,10 +14403,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>462249</v>
+        <v>462684</v>
       </c>
       <c r="R133" t="n">
-        <v>6768580</v>
+        <v>6769060</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14464,7 +14447,6 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -14483,10 +14465,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125017142</v>
+        <v>125017116</v>
       </c>
       <c r="B134" t="n">
-        <v>78842</v>
+        <v>79428</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14499,21 +14481,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14523,10 +14505,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>462682</v>
+        <v>462460</v>
       </c>
       <c r="R134" t="n">
-        <v>6769024</v>
+        <v>6768868</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14585,10 +14567,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125017237</v>
+        <v>125017271</v>
       </c>
       <c r="B135" t="n">
-        <v>78546</v>
+        <v>78455</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14601,21 +14583,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14625,10 +14607,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>462684</v>
+        <v>462755</v>
       </c>
       <c r="R135" t="n">
-        <v>6769060</v>
+        <v>6769176</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14687,10 +14669,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125017278</v>
+        <v>125017209</v>
       </c>
       <c r="B136" t="n">
-        <v>78455</v>
+        <v>8447</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14699,38 +14681,43 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>462544</v>
+        <v>462777</v>
       </c>
       <c r="R136" t="n">
-        <v>6768928</v>
+        <v>6769237</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14789,10 +14776,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125017282</v>
+        <v>125017210</v>
       </c>
       <c r="B137" t="n">
-        <v>78194</v>
+        <v>8447</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -14801,38 +14788,43 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6437</v>
+        <v>106545</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>462759</v>
+        <v>462636</v>
       </c>
       <c r="R137" t="n">
-        <v>6769121</v>
+        <v>6769113</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14891,10 +14883,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>125017136</v>
+        <v>124999425</v>
       </c>
       <c r="B138" t="n">
-        <v>78842</v>
+        <v>8447</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -14903,25 +14895,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14931,10 +14923,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>462449</v>
+        <v>462616</v>
       </c>
       <c r="R138" t="n">
-        <v>6768898</v>
+        <v>6769046</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14969,6 +14961,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
+        </is>
+      </c>
       <c r="AD138" t="b">
         <v>0</v>
       </c>
@@ -14981,22 +14978,22 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>125017154</v>
+        <v>125017252</v>
       </c>
       <c r="B139" t="n">
-        <v>96354</v>
+        <v>78810</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15009,21 +15006,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15033,10 +15030,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>462433</v>
+        <v>462426</v>
       </c>
       <c r="R139" t="n">
-        <v>6768784</v>
+        <v>6768812</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15095,10 +15092,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>125017138</v>
+        <v>125017266</v>
       </c>
       <c r="B140" t="n">
-        <v>78842</v>
+        <v>92293</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15107,38 +15104,47 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>462516</v>
+        <v>462462</v>
       </c>
       <c r="R140" t="n">
-        <v>6768902</v>
+        <v>6768863</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15197,10 +15203,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>125017210</v>
+        <v>125017268</v>
       </c>
       <c r="B141" t="n">
-        <v>8447</v>
+        <v>92293</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15213,27 +15219,31 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
@@ -15242,10 +15252,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>462636</v>
+        <v>462470</v>
       </c>
       <c r="R141" t="n">
-        <v>6769113</v>
+        <v>6768894</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15304,10 +15314,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>125004378</v>
+        <v>125017284</v>
       </c>
       <c r="B142" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15320,39 +15330,34 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Lädsån, Dlr</t>
+          <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>462261</v>
+        <v>462409</v>
       </c>
       <c r="R142" t="n">
-        <v>6768593</v>
+        <v>6768814</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15387,11 +15392,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD142" t="b">
         <v>0</v>
       </c>
@@ -15404,22 +15404,22 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>124999190</v>
+        <v>125017246</v>
       </c>
       <c r="B143" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15428,25 +15428,25 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15456,10 +15456,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>462672</v>
+        <v>462868</v>
       </c>
       <c r="R143" t="n">
-        <v>6769113</v>
+        <v>6769325</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15506,22 +15506,22 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>124999088</v>
+        <v>125017261</v>
       </c>
       <c r="B144" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15534,21 +15534,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15558,10 +15558,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>462698</v>
+        <v>462696</v>
       </c>
       <c r="R144" t="n">
-        <v>6769146</v>
+        <v>6769144</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15596,11 +15596,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC144" t="inlineStr">
-        <is>
-          <t>Miljöbilder. Sannoligt spillkråka, hackhål/bohål.</t>
-        </is>
-      </c>
       <c r="AD144" t="b">
         <v>0</v>
       </c>
@@ -15613,22 +15608,22 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>125017123</v>
+        <v>125017207</v>
       </c>
       <c r="B145" t="n">
-        <v>79428</v>
+        <v>8447</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15637,38 +15632,43 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>462680</v>
+        <v>462840</v>
       </c>
       <c r="R145" t="n">
-        <v>6769027</v>
+        <v>6769309</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15727,10 +15727,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>125017116</v>
+        <v>125017273</v>
       </c>
       <c r="B146" t="n">
-        <v>79428</v>
+        <v>78455</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15743,21 +15743,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15767,10 +15767,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>462460</v>
+        <v>462642</v>
       </c>
       <c r="R146" t="n">
-        <v>6768868</v>
+        <v>6769092</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15829,10 +15829,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125017162</v>
+        <v>125017171</v>
       </c>
       <c r="B147" t="n">
-        <v>79428</v>
+        <v>91012</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15845,21 +15845,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15869,10 +15869,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>462763</v>
+        <v>462425</v>
       </c>
       <c r="R147" t="n">
-        <v>6769126</v>
+        <v>6768807</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15931,10 +15931,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125017175</v>
+        <v>125017236</v>
       </c>
       <c r="B148" t="n">
-        <v>56722</v>
+        <v>78546</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15943,43 +15943,38 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P148" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>462419</v>
+        <v>462688</v>
       </c>
       <c r="R148" t="n">
-        <v>6768798</v>
+        <v>6769019</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16038,10 +16033,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125017114</v>
+        <v>125017186</v>
       </c>
       <c r="B149" t="n">
-        <v>79428</v>
+        <v>57529</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16054,34 +16049,43 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>462451</v>
+        <v>462647</v>
       </c>
       <c r="R149" t="n">
-        <v>6768820</v>
+        <v>6769118</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16140,10 +16144,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125017108</v>
+        <v>125017175</v>
       </c>
       <c r="B150" t="n">
-        <v>79428</v>
+        <v>56722</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16152,38 +16156,43 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>462569</v>
+        <v>462419</v>
       </c>
       <c r="R150" t="n">
-        <v>6769031</v>
+        <v>6768798</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16242,7 +16251,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>125017261</v>
+        <v>125017254</v>
       </c>
       <c r="B151" t="n">
         <v>78810</v>
@@ -16282,10 +16291,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>462696</v>
+        <v>462424</v>
       </c>
       <c r="R151" t="n">
-        <v>6769144</v>
+        <v>6768802</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16344,10 +16353,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>124999027</v>
+        <v>125017250</v>
       </c>
       <c r="B152" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16360,21 +16369,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16384,10 +16393,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>462741</v>
+        <v>462364</v>
       </c>
       <c r="R152" t="n">
-        <v>6769142</v>
+        <v>6768755</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16422,11 +16431,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>Miljöbilder. Sannoligt bohål/hackhål efter spillkråka.</t>
-        </is>
-      </c>
       <c r="AD152" t="b">
         <v>0</v>
       </c>
@@ -16439,22 +16443,22 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>125017207</v>
+        <v>125017228</v>
       </c>
       <c r="B153" t="n">
-        <v>8447</v>
+        <v>94766</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16467,39 +16471,34 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>106545</v>
+        <v>2412</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Philonotis fontana</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P153" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>462840</v>
+        <v>462418</v>
       </c>
       <c r="R153" t="n">
-        <v>6769309</v>
+        <v>6768790</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16532,6 +16531,11 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>I kallkälla</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16558,10 +16562,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>125017271</v>
+        <v>125017114</v>
       </c>
       <c r="B154" t="n">
-        <v>78455</v>
+        <v>79428</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16574,21 +16578,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16598,10 +16602,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>462755</v>
+        <v>462451</v>
       </c>
       <c r="R154" t="n">
-        <v>6769176</v>
+        <v>6768820</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16660,10 +16664,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>125017219</v>
+        <v>125017130</v>
       </c>
       <c r="B155" t="n">
-        <v>8447</v>
+        <v>79428</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16672,43 +16676,38 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P155" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>462585</v>
+        <v>462444</v>
       </c>
       <c r="R155" t="n">
-        <v>6769050</v>
+        <v>6768840</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16767,10 +16766,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>125017190</v>
+        <v>125007547</v>
       </c>
       <c r="B156" t="n">
-        <v>57529</v>
+        <v>79428</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16783,39 +16782,34 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P156" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>462791</v>
+        <v>462441</v>
       </c>
       <c r="R156" t="n">
-        <v>6769257</v>
+        <v>6768886</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16850,6 +16844,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD156" t="b">
         <v>0</v>
       </c>
@@ -16862,22 +16861,22 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>125017265</v>
+        <v>125017156</v>
       </c>
       <c r="B157" t="n">
-        <v>78810</v>
+        <v>96354</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16890,21 +16889,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16914,10 +16913,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>462762</v>
+        <v>462418</v>
       </c>
       <c r="R157" t="n">
-        <v>6769125</v>
+        <v>6768776</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16976,10 +16975,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>125017117</v>
+        <v>125017278</v>
       </c>
       <c r="B158" t="n">
-        <v>79428</v>
+        <v>78455</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16992,21 +16991,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17016,10 +17015,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>462501</v>
+        <v>462544</v>
       </c>
       <c r="R158" t="n">
-        <v>6768895</v>
+        <v>6768928</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17078,10 +17077,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>125017256</v>
+        <v>125017188</v>
       </c>
       <c r="B159" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -17094,34 +17093,39 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P159" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>462409</v>
+        <v>462760</v>
       </c>
       <c r="R159" t="n">
-        <v>6768798</v>
+        <v>6769122</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17180,10 +17184,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>125017268</v>
+        <v>124999142</v>
       </c>
       <c r="B160" t="n">
-        <v>92293</v>
+        <v>78842</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17192,47 +17196,38 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J160" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>462470</v>
+        <v>462684</v>
       </c>
       <c r="R160" t="n">
-        <v>6768894</v>
+        <v>6769117</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17279,22 +17274,22 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>125017280</v>
+        <v>125017220</v>
       </c>
       <c r="B161" t="n">
-        <v>96227</v>
+        <v>8447</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17307,34 +17302,39 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>2869</v>
+        <v>106545</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P161" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>462403</v>
+        <v>462472</v>
       </c>
       <c r="R161" t="n">
-        <v>6768799</v>
+        <v>6768856</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17393,7 +17393,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>125017264</v>
+        <v>125017260</v>
       </c>
       <c r="B162" t="n">
         <v>78810</v>
@@ -17433,10 +17433,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>462713</v>
+        <v>462575</v>
       </c>
       <c r="R162" t="n">
-        <v>6769148</v>
+        <v>6768974</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17495,10 +17495,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>125017285</v>
+        <v>125017199</v>
       </c>
       <c r="B163" t="n">
-        <v>91065</v>
+        <v>96345</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17507,25 +17507,25 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>5321</v>
+        <v>54</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Skogstrappmossa</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Anastrophyllum michauxii</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(F.Weber.) H.Buch</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17535,10 +17535,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>462561</v>
+        <v>462249</v>
       </c>
       <c r="R163" t="n">
-        <v>6768949</v>
+        <v>6768580</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17571,11 +17571,6 @@
       <c r="AA163" t="inlineStr">
         <is>
           <t>2025-05-12</t>
-        </is>
-      </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17603,7 +17598,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>125007648</v>
+        <v>125017108</v>
       </c>
       <c r="B164" t="n">
         <v>79428</v>
@@ -17643,10 +17638,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>462431</v>
+        <v>462569</v>
       </c>
       <c r="R164" t="n">
-        <v>6768885</v>
+        <v>6769031</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17681,11 +17676,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC164" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD164" t="b">
         <v>0</v>
       </c>
@@ -17698,22 +17688,22 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>125017232</v>
+        <v>125017115</v>
       </c>
       <c r="B165" t="n">
-        <v>80763</v>
+        <v>79428</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -17726,21 +17716,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17750,10 +17740,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>462456</v>
+        <v>462449</v>
       </c>
       <c r="R165" t="n">
-        <v>6768781</v>
+        <v>6768835</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17812,10 +17802,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>125017209</v>
+        <v>125001637</v>
       </c>
       <c r="B166" t="n">
-        <v>8447</v>
+        <v>56722</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -17828,27 +17818,27 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
       <c r="M166" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P166" t="inlineStr">
@@ -17857,10 +17847,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>462777</v>
+        <v>462376</v>
       </c>
       <c r="R166" t="n">
-        <v>6769237</v>
+        <v>6768807</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17907,22 +17897,22 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>125017140</v>
+        <v>124999088</v>
       </c>
       <c r="B167" t="n">
-        <v>78842</v>
+        <v>57529</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -17935,21 +17925,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17959,10 +17949,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>462575</v>
+        <v>462698</v>
       </c>
       <c r="R167" t="n">
-        <v>6768972</v>
+        <v>6769146</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17997,6 +17987,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>Miljöbilder. Sannoligt spillkråka, hackhål/bohål.</t>
+        </is>
+      </c>
       <c r="AD167" t="b">
         <v>0</v>
       </c>
@@ -18009,12 +18004,12 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>

--- a/artfynd/A 18527-2025 artfynd.xlsx
+++ b/artfynd/A 18527-2025 artfynd.xlsx
@@ -6047,10 +6047,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125017279</v>
+        <v>125017185</v>
       </c>
       <c r="B53" t="n">
-        <v>78455</v>
+        <v>98122</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6059,25 +6059,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>221952</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6087,10 +6087,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>462581</v>
+        <v>462417</v>
       </c>
       <c r="R53" t="n">
-        <v>6768944</v>
+        <v>6768771</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6149,10 +6149,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125017255</v>
+        <v>125017279</v>
       </c>
       <c r="B54" t="n">
-        <v>78810</v>
+        <v>78455</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6165,21 +6165,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6189,10 +6189,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>462419</v>
+        <v>462581</v>
       </c>
       <c r="R54" t="n">
-        <v>6768798</v>
+        <v>6768944</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6251,10 +6251,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125017185</v>
+        <v>125017255</v>
       </c>
       <c r="B55" t="n">
-        <v>98122</v>
+        <v>78810</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6263,25 +6263,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6291,10 +6291,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>462417</v>
+        <v>462419</v>
       </c>
       <c r="R55" t="n">
-        <v>6768771</v>
+        <v>6768798</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -8657,10 +8657,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125017123</v>
+        <v>125017259</v>
       </c>
       <c r="B78" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8673,21 +8673,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8697,10 +8697,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>462680</v>
+        <v>462444</v>
       </c>
       <c r="R78" t="n">
-        <v>6769027</v>
+        <v>6768832</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8759,10 +8759,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125007648</v>
+        <v>125017270</v>
       </c>
       <c r="B79" t="n">
-        <v>79428</v>
+        <v>78455</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8775,21 +8775,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8799,10 +8799,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>462431</v>
+        <v>462777</v>
       </c>
       <c r="R79" t="n">
-        <v>6768885</v>
+        <v>6769237</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8837,11 +8837,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -8854,22 +8849,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125017259</v>
+        <v>125017123</v>
       </c>
       <c r="B80" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8882,21 +8877,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8906,10 +8901,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>462444</v>
+        <v>462680</v>
       </c>
       <c r="R80" t="n">
-        <v>6768832</v>
+        <v>6769027</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8968,10 +8963,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125017270</v>
+        <v>125007648</v>
       </c>
       <c r="B81" t="n">
-        <v>78455</v>
+        <v>79428</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8984,21 +8979,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9008,10 +9003,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>462777</v>
+        <v>462431</v>
       </c>
       <c r="R81" t="n">
-        <v>6769237</v>
+        <v>6768885</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9046,6 +9041,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -9058,12 +9058,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -9284,10 +9284,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125017251</v>
+        <v>125001339</v>
       </c>
       <c r="B84" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9300,34 +9300,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>462357</v>
+        <v>462456</v>
       </c>
       <c r="R84" t="n">
-        <v>6768775</v>
+        <v>6768778</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9362,6 +9367,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -9374,22 +9384,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125001145</v>
+        <v>125017251</v>
       </c>
       <c r="B85" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9402,21 +9412,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9426,10 +9436,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>462456</v>
+        <v>462357</v>
       </c>
       <c r="R85" t="n">
-        <v>6768778</v>
+        <v>6768775</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9464,11 +9474,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -9481,19 +9486,19 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125017128</v>
+        <v>125001145</v>
       </c>
       <c r="B86" t="n">
         <v>79428</v>
@@ -9533,10 +9538,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>462680</v>
+        <v>462456</v>
       </c>
       <c r="R86" t="n">
-        <v>6769078</v>
+        <v>6768778</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9571,6 +9576,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -9583,22 +9593,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125001339</v>
+        <v>125017128</v>
       </c>
       <c r="B87" t="n">
-        <v>57529</v>
+        <v>79428</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9611,39 +9621,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>462456</v>
+        <v>462680</v>
       </c>
       <c r="R87" t="n">
-        <v>6768778</v>
+        <v>6769078</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9678,11 +9683,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
@@ -9695,12 +9695,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -13022,10 +13022,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125017280</v>
+        <v>125017282</v>
       </c>
       <c r="B120" t="n">
-        <v>96227</v>
+        <v>78194</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13034,25 +13034,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>2869</v>
+        <v>6437</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13062,10 +13062,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>462403</v>
+        <v>462759</v>
       </c>
       <c r="R120" t="n">
-        <v>6768799</v>
+        <v>6769121</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13124,10 +13124,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125017181</v>
+        <v>125017277</v>
       </c>
       <c r="B121" t="n">
-        <v>79920</v>
+        <v>78455</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13136,25 +13136,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6462</v>
+        <v>353</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13164,10 +13164,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>462422</v>
+        <v>462478</v>
       </c>
       <c r="R121" t="n">
-        <v>6768816</v>
+        <v>6768887</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13200,11 +13200,6 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-05-12</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13231,10 +13226,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125017282</v>
+        <v>125017135</v>
       </c>
       <c r="B122" t="n">
-        <v>78194</v>
+        <v>78842</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13247,21 +13242,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6437</v>
+        <v>185</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13271,10 +13266,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>462759</v>
+        <v>462439</v>
       </c>
       <c r="R122" t="n">
-        <v>6769121</v>
+        <v>6768813</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13333,10 +13328,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125017277</v>
+        <v>125017134</v>
       </c>
       <c r="B123" t="n">
-        <v>78455</v>
+        <v>78842</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13349,21 +13344,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13373,10 +13368,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>462478</v>
+        <v>462385</v>
       </c>
       <c r="R123" t="n">
-        <v>6768887</v>
+        <v>6768840</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13435,10 +13430,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125017135</v>
+        <v>125017198</v>
       </c>
       <c r="B124" t="n">
-        <v>78842</v>
+        <v>57529</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13451,34 +13446,39 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>462439</v>
+        <v>462452</v>
       </c>
       <c r="R124" t="n">
-        <v>6768813</v>
+        <v>6768897</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13537,10 +13537,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125017134</v>
+        <v>125017280</v>
       </c>
       <c r="B125" t="n">
-        <v>78842</v>
+        <v>96227</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13549,25 +13549,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>185</v>
+        <v>2869</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13577,10 +13577,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>462385</v>
+        <v>462403</v>
       </c>
       <c r="R125" t="n">
-        <v>6768840</v>
+        <v>6768799</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13639,10 +13639,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125017234</v>
+        <v>125017181</v>
       </c>
       <c r="B126" t="n">
-        <v>78546</v>
+        <v>79920</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13651,25 +13651,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13679,10 +13679,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>462501</v>
+        <v>462422</v>
       </c>
       <c r="R126" t="n">
-        <v>6768890</v>
+        <v>6768816</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13715,6 +13715,11 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13741,10 +13746,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125017198</v>
+        <v>125017234</v>
       </c>
       <c r="B127" t="n">
-        <v>57529</v>
+        <v>78546</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13757,39 +13762,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>462452</v>
+        <v>462501</v>
       </c>
       <c r="R127" t="n">
-        <v>6768897</v>
+        <v>6768890</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13950,10 +13950,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125000794</v>
+        <v>125017271</v>
       </c>
       <c r="B129" t="n">
-        <v>78810</v>
+        <v>78455</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13966,21 +13966,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13990,10 +13990,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>462420</v>
+        <v>462755</v>
       </c>
       <c r="R129" t="n">
-        <v>6768785</v>
+        <v>6769176</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14028,11 +14028,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD129" t="b">
         <v>0</v>
       </c>
@@ -14045,19 +14040,19 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>125017257</v>
+        <v>125000794</v>
       </c>
       <c r="B130" t="n">
         <v>78810</v>
@@ -14097,10 +14092,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>462417</v>
+        <v>462420</v>
       </c>
       <c r="R130" t="n">
-        <v>6768771</v>
+        <v>6768785</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14135,6 +14130,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD130" t="b">
         <v>0</v>
       </c>
@@ -14147,19 +14147,19 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125017265</v>
+        <v>125017257</v>
       </c>
       <c r="B131" t="n">
         <v>78810</v>
@@ -14199,10 +14199,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>462762</v>
+        <v>462417</v>
       </c>
       <c r="R131" t="n">
-        <v>6769125</v>
+        <v>6768771</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14261,10 +14261,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125017124</v>
+        <v>125017265</v>
       </c>
       <c r="B132" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14277,21 +14277,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14301,10 +14301,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>462679</v>
+        <v>462762</v>
       </c>
       <c r="R132" t="n">
-        <v>6769045</v>
+        <v>6769125</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14363,10 +14363,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125017237</v>
+        <v>125017124</v>
       </c>
       <c r="B133" t="n">
-        <v>78546</v>
+        <v>79428</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14379,21 +14379,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14403,10 +14403,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>462684</v>
+        <v>462679</v>
       </c>
       <c r="R133" t="n">
-        <v>6769060</v>
+        <v>6769045</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14465,10 +14465,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125017116</v>
+        <v>125017237</v>
       </c>
       <c r="B134" t="n">
-        <v>79428</v>
+        <v>78546</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14481,21 +14481,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14505,10 +14505,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>462460</v>
+        <v>462684</v>
       </c>
       <c r="R134" t="n">
-        <v>6768868</v>
+        <v>6769060</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14567,10 +14567,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125017271</v>
+        <v>125017116</v>
       </c>
       <c r="B135" t="n">
-        <v>78455</v>
+        <v>79428</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14583,21 +14583,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14607,10 +14607,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>462755</v>
+        <v>462460</v>
       </c>
       <c r="R135" t="n">
-        <v>6769176</v>
+        <v>6768868</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>

--- a/artfynd/A 18527-2025 artfynd.xlsx
+++ b/artfynd/A 18527-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124774494</v>
+        <v>124774975</v>
       </c>
       <c r="B2" t="n">
         <v>8447</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>462257</v>
+        <v>462275</v>
       </c>
       <c r="R2" t="n">
-        <v>6768691</v>
+        <v>6768714</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124777178</v>
+        <v>124772023</v>
       </c>
       <c r="B3" t="n">
-        <v>74901</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +798,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>462340</v>
+        <v>462234</v>
       </c>
       <c r="R3" t="n">
-        <v>6768649</v>
+        <v>6768605</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +863,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124772894</v>
+        <v>124774056</v>
       </c>
       <c r="B4" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462230</v>
+        <v>462291</v>
       </c>
       <c r="R4" t="n">
-        <v>6768556</v>
+        <v>6768602</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124778690</v>
+        <v>124782461</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,31 +1008,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1026,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462388</v>
+        <v>462374</v>
       </c>
       <c r="R5" t="n">
-        <v>6768696</v>
+        <v>6768823</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,11 +1077,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124775446</v>
+        <v>124774494</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1115,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>462341</v>
+        <v>462257</v>
       </c>
       <c r="R6" t="n">
-        <v>6768708</v>
+        <v>6768691</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124776376</v>
+        <v>124782138</v>
       </c>
       <c r="B7" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>462311</v>
+        <v>462447</v>
       </c>
       <c r="R7" t="n">
-        <v>6768690</v>
+        <v>6768805</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,7 +1307,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124774558</v>
+        <v>124775556</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1337,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>462257</v>
+        <v>462341</v>
       </c>
       <c r="R8" t="n">
-        <v>6768691</v>
+        <v>6768708</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124781784</v>
+        <v>124782169</v>
       </c>
       <c r="B9" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,39 +1425,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462362</v>
+        <v>462456</v>
       </c>
       <c r="R9" t="n">
-        <v>6768766</v>
+        <v>6768800</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124774922</v>
+        <v>124776534</v>
       </c>
       <c r="B10" t="n">
-        <v>57529</v>
+        <v>74901</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,39 +1527,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462275</v>
+        <v>462302</v>
       </c>
       <c r="R10" t="n">
-        <v>6768714</v>
+        <v>6768675</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1587,6 +1587,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1613,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124773032</v>
+        <v>124770579</v>
       </c>
       <c r="B11" t="n">
-        <v>57529</v>
+        <v>74901</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1629,39 +1634,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>462235</v>
+        <v>462182</v>
       </c>
       <c r="R11" t="n">
-        <v>6768533</v>
+        <v>6768583</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124777762</v>
+        <v>124777178</v>
       </c>
       <c r="B12" t="n">
-        <v>57529</v>
+        <v>74901</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1736,39 +1736,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>462331</v>
+        <v>462340</v>
       </c>
       <c r="R12" t="n">
-        <v>6768680</v>
+        <v>6768649</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1801,11 +1796,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Miljöbilder på bland annat angränsande hygge.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1832,7 +1822,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124782169</v>
+        <v>124771180</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -1872,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>462456</v>
+        <v>462198</v>
       </c>
       <c r="R13" t="n">
-        <v>6768800</v>
+        <v>6768579</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1934,7 +1924,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124776291</v>
+        <v>124770632</v>
       </c>
       <c r="B14" t="n">
         <v>57529</v>
@@ -1979,10 +1969,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>462311</v>
+        <v>462182</v>
       </c>
       <c r="R14" t="n">
-        <v>6768690</v>
+        <v>6768583</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2015,6 +2005,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2041,10 +2036,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124774056</v>
+        <v>124777762</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2057,34 +2052,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>462291</v>
+        <v>462331</v>
       </c>
       <c r="R15" t="n">
-        <v>6768602</v>
+        <v>6768680</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2117,6 +2117,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Miljöbilder på bland annat angränsande hygge.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2143,10 +2148,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124782461</v>
+        <v>124772894</v>
       </c>
       <c r="B16" t="n">
-        <v>56722</v>
+        <v>74901</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2155,43 +2160,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>462374</v>
+        <v>462230</v>
       </c>
       <c r="R16" t="n">
-        <v>6768823</v>
+        <v>6768556</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2250,10 +2250,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124774845</v>
+        <v>124781784</v>
       </c>
       <c r="B17" t="n">
-        <v>8447</v>
+        <v>57529</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2262,38 +2262,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>462271</v>
+        <v>462362</v>
       </c>
       <c r="R17" t="n">
-        <v>6768703</v>
+        <v>6768766</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2352,7 +2357,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124772212</v>
+        <v>124775405</v>
       </c>
       <c r="B18" t="n">
         <v>57529</v>
@@ -2397,10 +2402,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>462184</v>
+        <v>462322</v>
       </c>
       <c r="R18" t="n">
-        <v>6768538</v>
+        <v>6768707</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2464,10 +2469,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124781915</v>
+        <v>124781860</v>
       </c>
       <c r="B19" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2480,39 +2485,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>462389</v>
+        <v>462362</v>
       </c>
       <c r="R19" t="n">
-        <v>6768770</v>
+        <v>6768766</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2545,6 +2545,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2571,7 +2576,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124777471</v>
+        <v>124774189</v>
       </c>
       <c r="B20" t="n">
         <v>78810</v>
@@ -2611,10 +2616,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>462331</v>
+        <v>462287</v>
       </c>
       <c r="R20" t="n">
-        <v>6768680</v>
+        <v>6768630</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2673,7 +2678,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124776534</v>
+        <v>124776376</v>
       </c>
       <c r="B21" t="n">
         <v>74901</v>
@@ -2713,10 +2718,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>462302</v>
+        <v>462311</v>
       </c>
       <c r="R21" t="n">
-        <v>6768675</v>
+        <v>6768690</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2749,11 +2754,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2780,10 +2780,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124774463</v>
+        <v>124772212</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2796,34 +2796,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>462264</v>
+        <v>462184</v>
       </c>
       <c r="R22" t="n">
-        <v>6768671</v>
+        <v>6768538</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2856,6 +2861,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2882,7 +2892,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124771180</v>
+        <v>124774558</v>
       </c>
       <c r="B23" t="n">
         <v>78810</v>
@@ -2922,10 +2932,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>462198</v>
+        <v>462257</v>
       </c>
       <c r="R23" t="n">
-        <v>6768579</v>
+        <v>6768691</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2984,7 +2994,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124770632</v>
+        <v>124778690</v>
       </c>
       <c r="B24" t="n">
         <v>57529</v>
@@ -3029,10 +3039,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>462182</v>
+        <v>462388</v>
       </c>
       <c r="R24" t="n">
-        <v>6768583</v>
+        <v>6768696</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3069,7 +3079,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Miljöbilder.</t>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3096,10 +3106,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124771314</v>
+        <v>124781915</v>
       </c>
       <c r="B25" t="n">
-        <v>57666</v>
+        <v>57529</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3112,27 +3122,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3141,13 +3151,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>462210</v>
+        <v>462389</v>
       </c>
       <c r="R25" t="n">
-        <v>6768591</v>
+        <v>6768770</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3203,10 +3213,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124775105</v>
+        <v>124776266</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3219,34 +3229,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>462281</v>
+        <v>462311</v>
       </c>
       <c r="R26" t="n">
-        <v>6768705</v>
+        <v>6768690</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3279,11 +3294,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3310,10 +3320,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124781969</v>
+        <v>124774814</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3326,34 +3336,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>462389</v>
+        <v>462257</v>
       </c>
       <c r="R27" t="n">
-        <v>6768770</v>
+        <v>6768691</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3412,10 +3427,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124774814</v>
+        <v>124774463</v>
       </c>
       <c r="B28" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3428,39 +3443,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>462257</v>
+        <v>462264</v>
       </c>
       <c r="R28" t="n">
-        <v>6768691</v>
+        <v>6768671</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3519,10 +3529,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124775405</v>
+        <v>124778521</v>
       </c>
       <c r="B29" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3535,39 +3545,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>462322</v>
+        <v>462386</v>
       </c>
       <c r="R29" t="n">
-        <v>6768707</v>
+        <v>6768724</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3604,7 +3609,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Miljöbilder</t>
+          <t>Miljöbilder för närområdet. Hygget börjar bakom lågorna</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3631,7 +3636,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124774189</v>
+        <v>124777471</v>
       </c>
       <c r="B30" t="n">
         <v>78810</v>
@@ -3671,10 +3676,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>462287</v>
+        <v>462331</v>
       </c>
       <c r="R30" t="n">
-        <v>6768630</v>
+        <v>6768680</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3733,10 +3738,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124774975</v>
+        <v>124781969</v>
       </c>
       <c r="B31" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3745,25 +3750,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3773,10 +3778,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>462275</v>
+        <v>462389</v>
       </c>
       <c r="R31" t="n">
-        <v>6768714</v>
+        <v>6768770</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3809,11 +3814,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3840,7 +3840,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124781860</v>
+        <v>124775105</v>
       </c>
       <c r="B32" t="n">
         <v>78810</v>
@@ -3880,10 +3880,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>462362</v>
+        <v>462281</v>
       </c>
       <c r="R32" t="n">
-        <v>6768766</v>
+        <v>6768705</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3947,10 +3947,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124782138</v>
+        <v>124774922</v>
       </c>
       <c r="B33" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3963,34 +3963,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>462447</v>
+        <v>462275</v>
       </c>
       <c r="R33" t="n">
-        <v>6768805</v>
+        <v>6768714</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4049,10 +4054,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124770579</v>
+        <v>124773032</v>
       </c>
       <c r="B34" t="n">
-        <v>74901</v>
+        <v>57529</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4065,34 +4070,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>462182</v>
+        <v>462235</v>
       </c>
       <c r="R34" t="n">
-        <v>6768583</v>
+        <v>6768533</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4151,10 +4161,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124772023</v>
+        <v>124774845</v>
       </c>
       <c r="B35" t="n">
-        <v>57529</v>
+        <v>8447</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4163,43 +4173,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>462234</v>
+        <v>462271</v>
       </c>
       <c r="R35" t="n">
-        <v>6768605</v>
+        <v>6768703</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4232,11 +4237,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4263,10 +4263,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124778521</v>
+        <v>124771314</v>
       </c>
       <c r="B36" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4279,37 +4279,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>462386</v>
+        <v>462210</v>
       </c>
       <c r="R36" t="n">
-        <v>6768724</v>
+        <v>6768591</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4339,11 +4344,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Miljöbilder för närområdet. Hygget börjar bakom lågorna</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4370,7 +4370,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124833451</v>
+        <v>124835908</v>
       </c>
       <c r="B37" t="n">
         <v>8447</v>
@@ -4410,10 +4410,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>462818</v>
+        <v>462741</v>
       </c>
       <c r="R37" t="n">
-        <v>6769164</v>
+        <v>6769142</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4446,6 +4446,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Miljöbilder för närområdet.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4472,7 +4477,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124835245</v>
+        <v>124834205</v>
       </c>
       <c r="B38" t="n">
         <v>78546</v>
@@ -4579,10 +4584,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124834191</v>
+        <v>124838423</v>
       </c>
       <c r="B39" t="n">
-        <v>79428</v>
+        <v>57529</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4595,34 +4600,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Salutjärnen, Dlr</t>
+          <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>462814</v>
+        <v>462456</v>
       </c>
       <c r="R39" t="n">
-        <v>6769220</v>
+        <v>6768914</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4655,6 +4660,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4681,10 +4691,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124838423</v>
+        <v>124835714</v>
       </c>
       <c r="B40" t="n">
-        <v>57529</v>
+        <v>8447</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4693,38 +4703,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lädsån, Dlr</t>
+          <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>462456</v>
+        <v>462814</v>
       </c>
       <c r="R40" t="n">
-        <v>6768914</v>
+        <v>6769220</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4788,7 +4798,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124835908</v>
+        <v>124833941</v>
       </c>
       <c r="B41" t="n">
         <v>8447</v>
@@ -4828,10 +4838,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>462741</v>
+        <v>462816</v>
       </c>
       <c r="R41" t="n">
-        <v>6769142</v>
+        <v>6769191</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4895,10 +4905,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124836527</v>
+        <v>124834191</v>
       </c>
       <c r="B42" t="n">
-        <v>79399</v>
+        <v>79428</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4911,21 +4921,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4935,10 +4945,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>462712</v>
+        <v>462814</v>
       </c>
       <c r="R42" t="n">
-        <v>6769143</v>
+        <v>6769220</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4971,11 +4981,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5002,10 +5007,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124836354</v>
+        <v>124833451</v>
       </c>
       <c r="B43" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5014,25 +5019,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5042,10 +5047,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>462712</v>
+        <v>462818</v>
       </c>
       <c r="R43" t="n">
-        <v>6769143</v>
+        <v>6769164</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5078,11 +5083,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Miljöbild, garnlav i äldre tall.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5109,10 +5109,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124836445</v>
+        <v>124825418</v>
       </c>
       <c r="B44" t="n">
-        <v>78546</v>
+        <v>8447</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5121,25 +5121,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5149,10 +5149,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>462712</v>
+        <v>462844</v>
       </c>
       <c r="R44" t="n">
-        <v>6769143</v>
+        <v>6769302</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5185,11 +5185,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5216,10 +5211,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124835714</v>
+        <v>124836271</v>
       </c>
       <c r="B45" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5228,25 +5223,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5256,10 +5251,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>462814</v>
+        <v>462712</v>
       </c>
       <c r="R45" t="n">
-        <v>6769220</v>
+        <v>6769143</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5296,7 +5291,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Miljöbild</t>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5323,10 +5318,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124833941</v>
+        <v>124836445</v>
       </c>
       <c r="B46" t="n">
-        <v>8447</v>
+        <v>78546</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5335,25 +5330,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5363,10 +5358,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>462816</v>
+        <v>462712</v>
       </c>
       <c r="R46" t="n">
-        <v>6769191</v>
+        <v>6769143</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5403,7 +5398,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Miljöbilder för närområdet.</t>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5430,10 +5425,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124836148</v>
+        <v>124836527</v>
       </c>
       <c r="B47" t="n">
-        <v>78546</v>
+        <v>79399</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5446,21 +5441,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5470,10 +5465,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>462741</v>
+        <v>462712</v>
       </c>
       <c r="R47" t="n">
-        <v>6769142</v>
+        <v>6769143</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5537,10 +5532,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124825418</v>
+        <v>124836148</v>
       </c>
       <c r="B48" t="n">
-        <v>8447</v>
+        <v>78546</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5549,25 +5544,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5577,10 +5572,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>462844</v>
+        <v>462741</v>
       </c>
       <c r="R48" t="n">
-        <v>6769302</v>
+        <v>6769142</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5613,6 +5608,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5639,10 +5639,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125000045</v>
+        <v>125017162</v>
       </c>
       <c r="B49" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5655,34 +5655,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lädsån, Dlr</t>
+          <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>462482</v>
+        <v>462763</v>
       </c>
       <c r="R49" t="n">
-        <v>6768845</v>
+        <v>6769126</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5729,22 +5729,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125017245</v>
+        <v>125017227</v>
       </c>
       <c r="B50" t="n">
-        <v>78810</v>
+        <v>94959</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5753,25 +5753,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>2387</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5781,10 +5781,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>462867</v>
+        <v>462424</v>
       </c>
       <c r="R50" t="n">
-        <v>6769346</v>
+        <v>6768787</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5817,6 +5817,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>I kallkälla</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5843,10 +5848,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125017162</v>
+        <v>125017205</v>
       </c>
       <c r="B51" t="n">
-        <v>79428</v>
+        <v>8447</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5855,38 +5860,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>462763</v>
+        <v>462864</v>
       </c>
       <c r="R51" t="n">
-        <v>6769126</v>
+        <v>6769317</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5945,10 +5955,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125017140</v>
+        <v>125017204</v>
       </c>
       <c r="B52" t="n">
-        <v>78842</v>
+        <v>96979</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5957,25 +5967,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>185</v>
+        <v>221945</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5985,10 +5995,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>462575</v>
+        <v>462438</v>
       </c>
       <c r="R52" t="n">
-        <v>6768972</v>
+        <v>6768787</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6047,10 +6057,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125017185</v>
+        <v>124999177</v>
       </c>
       <c r="B53" t="n">
-        <v>98122</v>
+        <v>57529</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6059,38 +6069,43 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221952</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>462417</v>
+        <v>462684</v>
       </c>
       <c r="R53" t="n">
-        <v>6768771</v>
+        <v>6769117</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6137,22 +6152,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125017279</v>
+        <v>124999088</v>
       </c>
       <c r="B54" t="n">
-        <v>78455</v>
+        <v>57529</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6165,21 +6180,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6189,10 +6204,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>462581</v>
+        <v>462698</v>
       </c>
       <c r="R54" t="n">
-        <v>6768944</v>
+        <v>6769146</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6227,6 +6242,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Miljöbilder. Sannoligt spillkråka, hackhål/bohål.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6239,19 +6259,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125017255</v>
+        <v>125000045</v>
       </c>
       <c r="B55" t="n">
         <v>78810</v>
@@ -6287,14 +6307,14 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Salutjärnen, Dlr</t>
+          <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>462419</v>
+        <v>462482</v>
       </c>
       <c r="R55" t="n">
-        <v>6768798</v>
+        <v>6768845</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6341,19 +6361,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125017127</v>
+        <v>125017114</v>
       </c>
       <c r="B56" t="n">
         <v>79428</v>
@@ -6393,10 +6413,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>462685</v>
+        <v>462451</v>
       </c>
       <c r="R56" t="n">
-        <v>6769071</v>
+        <v>6768820</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6455,7 +6475,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125017112</v>
+        <v>125007719</v>
       </c>
       <c r="B57" t="n">
         <v>79428</v>
@@ -6491,14 +6511,14 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Salutjärnen, Dlr</t>
+          <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>462453</v>
+        <v>462456</v>
       </c>
       <c r="R57" t="n">
-        <v>6768876</v>
+        <v>6768884</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6533,6 +6553,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6545,22 +6570,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125017122</v>
+        <v>125017193</v>
       </c>
       <c r="B58" t="n">
-        <v>79428</v>
+        <v>57529</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6573,34 +6598,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>462688</v>
+        <v>462585</v>
       </c>
       <c r="R58" t="n">
-        <v>6769019</v>
+        <v>6769050</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6659,10 +6689,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125017232</v>
+        <v>125017219</v>
       </c>
       <c r="B59" t="n">
-        <v>80763</v>
+        <v>8447</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6671,38 +6701,43 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1049</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>462456</v>
+        <v>462585</v>
       </c>
       <c r="R59" t="n">
-        <v>6768781</v>
+        <v>6769050</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6761,10 +6796,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125017142</v>
+        <v>125017270</v>
       </c>
       <c r="B60" t="n">
-        <v>78842</v>
+        <v>78455</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6777,21 +6812,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6801,10 +6836,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>462682</v>
+        <v>462777</v>
       </c>
       <c r="R60" t="n">
-        <v>6769024</v>
+        <v>6769237</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6863,10 +6898,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125017154</v>
+        <v>125017171</v>
       </c>
       <c r="B61" t="n">
-        <v>96354</v>
+        <v>91012</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6879,21 +6914,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6903,10 +6938,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>462433</v>
+        <v>462425</v>
       </c>
       <c r="R61" t="n">
-        <v>6768784</v>
+        <v>6768807</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6965,10 +7000,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125001616</v>
+        <v>125017105</v>
       </c>
       <c r="B62" t="n">
-        <v>56722</v>
+        <v>79428</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6977,43 +7012,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>462456</v>
+        <v>462811</v>
       </c>
       <c r="R62" t="n">
-        <v>6768778</v>
+        <v>6769258</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7048,11 +7078,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Miljöbilder. Så kallad tjädertall</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -7065,22 +7090,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124999190</v>
+        <v>125017122</v>
       </c>
       <c r="B63" t="n">
-        <v>8447</v>
+        <v>79428</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7089,25 +7114,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7117,10 +7142,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>462672</v>
+        <v>462688</v>
       </c>
       <c r="R63" t="n">
-        <v>6769113</v>
+        <v>6769019</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7167,22 +7192,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125017258</v>
+        <v>125017128</v>
       </c>
       <c r="B64" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7195,21 +7220,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7219,10 +7244,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>462449</v>
+        <v>462680</v>
       </c>
       <c r="R64" t="n">
-        <v>6768783</v>
+        <v>6769078</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7281,10 +7306,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125017238</v>
+        <v>125017212</v>
       </c>
       <c r="B65" t="n">
-        <v>78546</v>
+        <v>8447</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7293,38 +7318,43 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>462685</v>
+        <v>462295</v>
       </c>
       <c r="R65" t="n">
-        <v>6769071</v>
+        <v>6768622</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7383,10 +7413,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125008171</v>
+        <v>124999027</v>
       </c>
       <c r="B66" t="n">
-        <v>79428</v>
+        <v>57529</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7399,34 +7429,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Lädsån, Dlr</t>
+          <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>462456</v>
+        <v>462741</v>
       </c>
       <c r="R66" t="n">
-        <v>6768884</v>
+        <v>6769142</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7463,7 +7493,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Miljöbilder</t>
+          <t>Miljöbilder. Sannoligt bohål/hackhål efter spillkråka.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7490,10 +7520,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125017202</v>
+        <v>125017282</v>
       </c>
       <c r="B67" t="n">
-        <v>91299</v>
+        <v>78194</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7506,21 +7536,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>658</v>
+        <v>6437</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7530,10 +7560,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>462414</v>
+        <v>462759</v>
       </c>
       <c r="R67" t="n">
-        <v>6768758</v>
+        <v>6769121</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7592,10 +7622,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125017136</v>
+        <v>125001637</v>
       </c>
       <c r="B68" t="n">
-        <v>78842</v>
+        <v>56722</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7604,38 +7634,43 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>185</v>
+        <v>100138</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>462449</v>
+        <v>462376</v>
       </c>
       <c r="R68" t="n">
-        <v>6768898</v>
+        <v>6768807</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7682,22 +7717,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125017141</v>
+        <v>125007547</v>
       </c>
       <c r="B69" t="n">
-        <v>78842</v>
+        <v>79428</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7710,21 +7745,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7734,10 +7769,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>462579</v>
+        <v>462441</v>
       </c>
       <c r="R69" t="n">
-        <v>6768990</v>
+        <v>6768886</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7772,6 +7807,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -7784,12 +7824,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -7908,10 +7948,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125017190</v>
+        <v>124999240</v>
       </c>
       <c r="B71" t="n">
-        <v>57529</v>
+        <v>79428</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7924,39 +7964,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>462791</v>
+        <v>462658</v>
       </c>
       <c r="R71" t="n">
-        <v>6769257</v>
+        <v>6769079</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8003,22 +8038,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124999027</v>
+        <v>125001616</v>
       </c>
       <c r="B72" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8027,38 +8062,43 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>462741</v>
+        <v>462456</v>
       </c>
       <c r="R72" t="n">
-        <v>6769142</v>
+        <v>6768778</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8095,7 +8135,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Miljöbilder. Sannoligt bohål/hackhål efter spillkråka.</t>
+          <t>Miljöbilder. Så kallad tjädertall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8122,7 +8162,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125017262</v>
+        <v>125017255</v>
       </c>
       <c r="B73" t="n">
         <v>78810</v>
@@ -8162,10 +8202,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>462703</v>
+        <v>462419</v>
       </c>
       <c r="R73" t="n">
-        <v>6769146</v>
+        <v>6768798</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8224,7 +8264,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125001767</v>
+        <v>125017198</v>
       </c>
       <c r="B74" t="n">
         <v>57529</v>
@@ -8260,19 +8300,19 @@
       <c r="I74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Lädsån, Dlr</t>
+          <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>462346</v>
+        <v>462452</v>
       </c>
       <c r="R74" t="n">
-        <v>6768794</v>
+        <v>6768897</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8307,11 +8347,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -8324,19 +8359,19 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125017193</v>
+        <v>125001339</v>
       </c>
       <c r="B75" t="n">
         <v>57529</v>
@@ -8372,7 +8407,7 @@
       <c r="I75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -8381,10 +8416,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>462585</v>
+        <v>462456</v>
       </c>
       <c r="R75" t="n">
-        <v>6769050</v>
+        <v>6768778</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8419,6 +8454,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -8431,22 +8471,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125017173</v>
+        <v>125017190</v>
       </c>
       <c r="B76" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8455,31 +8495,31 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -8488,10 +8528,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>462440</v>
+        <v>462791</v>
       </c>
       <c r="R76" t="n">
-        <v>6768764</v>
+        <v>6769257</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8550,10 +8590,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125017225</v>
+        <v>125017127</v>
       </c>
       <c r="B77" t="n">
-        <v>8447</v>
+        <v>79428</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8562,43 +8602,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>462449</v>
+        <v>462685</v>
       </c>
       <c r="R77" t="n">
-        <v>6768765</v>
+        <v>6769071</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8657,10 +8692,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125017259</v>
+        <v>125017119</v>
       </c>
       <c r="B78" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8673,21 +8708,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8697,10 +8732,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>462444</v>
+        <v>462543</v>
       </c>
       <c r="R78" t="n">
-        <v>6768832</v>
+        <v>6768929</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8759,10 +8794,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125017270</v>
+        <v>125017112</v>
       </c>
       <c r="B79" t="n">
-        <v>78455</v>
+        <v>79428</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8775,21 +8810,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8799,10 +8834,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>462777</v>
+        <v>462453</v>
       </c>
       <c r="R79" t="n">
-        <v>6769237</v>
+        <v>6768876</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8861,10 +8896,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125017123</v>
+        <v>125001767</v>
       </c>
       <c r="B80" t="n">
-        <v>79428</v>
+        <v>57529</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8877,34 +8912,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Salutjärnen, Dlr</t>
+          <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>462680</v>
+        <v>462346</v>
       </c>
       <c r="R80" t="n">
-        <v>6769027</v>
+        <v>6768794</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8939,6 +8979,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -8951,22 +8996,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125007648</v>
+        <v>125017138</v>
       </c>
       <c r="B81" t="n">
-        <v>79428</v>
+        <v>78842</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8979,21 +9024,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9003,10 +9048,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>462431</v>
+        <v>462516</v>
       </c>
       <c r="R81" t="n">
-        <v>6768885</v>
+        <v>6768902</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9041,11 +9086,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -9058,22 +9098,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125000666</v>
+        <v>125017245</v>
       </c>
       <c r="B82" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9086,39 +9126,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>462422</v>
+        <v>462867</v>
       </c>
       <c r="R82" t="n">
-        <v>6768811</v>
+        <v>6769346</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9165,22 +9200,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125017212</v>
+        <v>125017115</v>
       </c>
       <c r="B83" t="n">
-        <v>8447</v>
+        <v>79428</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9189,43 +9224,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>462295</v>
+        <v>462449</v>
       </c>
       <c r="R83" t="n">
-        <v>6768622</v>
+        <v>6768835</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9284,10 +9314,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125001339</v>
+        <v>125017260</v>
       </c>
       <c r="B84" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9300,39 +9330,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>462456</v>
+        <v>462575</v>
       </c>
       <c r="R84" t="n">
-        <v>6768778</v>
+        <v>6768974</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9367,11 +9392,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -9384,22 +9404,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125017251</v>
+        <v>125017117</v>
       </c>
       <c r="B85" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9412,21 +9432,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9436,10 +9456,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>462357</v>
+        <v>462501</v>
       </c>
       <c r="R85" t="n">
-        <v>6768775</v>
+        <v>6768895</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9498,10 +9518,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125001145</v>
+        <v>125017240</v>
       </c>
       <c r="B86" t="n">
-        <v>79428</v>
+        <v>58191</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9510,25 +9530,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>103044</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9538,10 +9558,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>462456</v>
+        <v>462248</v>
       </c>
       <c r="R86" t="n">
-        <v>6768778</v>
+        <v>6768584</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9576,11 +9596,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -9593,22 +9608,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125017128</v>
+        <v>125017232</v>
       </c>
       <c r="B87" t="n">
-        <v>79428</v>
+        <v>80763</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9621,21 +9636,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9645,10 +9660,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>462680</v>
+        <v>462456</v>
       </c>
       <c r="R87" t="n">
-        <v>6769078</v>
+        <v>6768781</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9707,10 +9722,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125017113</v>
+        <v>125017252</v>
       </c>
       <c r="B88" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9723,21 +9738,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9747,10 +9762,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>462356</v>
+        <v>462426</v>
       </c>
       <c r="R88" t="n">
-        <v>6768753</v>
+        <v>6768812</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9809,7 +9824,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125017105</v>
+        <v>125001145</v>
       </c>
       <c r="B89" t="n">
         <v>79428</v>
@@ -9849,10 +9864,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>462811</v>
+        <v>462456</v>
       </c>
       <c r="R89" t="n">
-        <v>6769258</v>
+        <v>6768778</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9887,6 +9902,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
@@ -9899,22 +9919,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125000745</v>
+        <v>125000666</v>
       </c>
       <c r="B90" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9927,16 +9947,16 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -9947,7 +9967,7 @@
       <c r="I90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -9956,10 +9976,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>462414</v>
+        <v>462422</v>
       </c>
       <c r="R90" t="n">
-        <v>6768796</v>
+        <v>6768811</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9992,11 +10012,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-05-12</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10023,10 +10038,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125017240</v>
+        <v>125017228</v>
       </c>
       <c r="B91" t="n">
-        <v>58191</v>
+        <v>94766</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10039,21 +10054,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>103044</v>
+        <v>2412</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Philonotis fontana</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10063,10 +10078,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>462248</v>
+        <v>462418</v>
       </c>
       <c r="R91" t="n">
-        <v>6768584</v>
+        <v>6768790</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10099,6 +10114,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>I kallkälla</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10125,10 +10145,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124999240</v>
+        <v>125017264</v>
       </c>
       <c r="B92" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10141,21 +10161,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10165,10 +10185,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>462658</v>
+        <v>462713</v>
       </c>
       <c r="R92" t="n">
-        <v>6769079</v>
+        <v>6769148</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10215,22 +10235,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125017155</v>
+        <v>125017285</v>
       </c>
       <c r="B93" t="n">
-        <v>96354</v>
+        <v>91065</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10239,25 +10259,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>53</v>
+        <v>5321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10267,10 +10287,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>462427</v>
+        <v>462561</v>
       </c>
       <c r="R93" t="n">
-        <v>6768776</v>
+        <v>6768949</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10305,12 +10325,18 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>På asp</t>
+        </is>
+      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10329,10 +10355,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125017205</v>
+        <v>125017261</v>
       </c>
       <c r="B94" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10341,43 +10367,38 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>462864</v>
+        <v>462696</v>
       </c>
       <c r="R94" t="n">
-        <v>6769317</v>
+        <v>6769144</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10436,10 +10457,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125017263</v>
+        <v>125017210</v>
       </c>
       <c r="B95" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10448,38 +10469,43 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>462712</v>
+        <v>462636</v>
       </c>
       <c r="R95" t="n">
-        <v>6769149</v>
+        <v>6769113</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10538,10 +10564,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125017264</v>
+        <v>125017142</v>
       </c>
       <c r="B96" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10554,21 +10580,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10578,10 +10604,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>462713</v>
+        <v>462682</v>
       </c>
       <c r="R96" t="n">
-        <v>6769148</v>
+        <v>6769024</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10640,10 +10666,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125017138</v>
+        <v>125017241</v>
       </c>
       <c r="B97" t="n">
-        <v>78842</v>
+        <v>91026</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10656,21 +10682,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>185</v>
+        <v>1204</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10680,10 +10706,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>462516</v>
+        <v>462418</v>
       </c>
       <c r="R97" t="n">
-        <v>6768902</v>
+        <v>6768776</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10742,10 +10768,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125017227</v>
+        <v>125017262</v>
       </c>
       <c r="B98" t="n">
-        <v>94959</v>
+        <v>78810</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10754,25 +10780,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2387</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10782,10 +10808,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>462424</v>
+        <v>462703</v>
       </c>
       <c r="R98" t="n">
-        <v>6768787</v>
+        <v>6769146</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10818,11 +10844,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-05-12</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>I kallkälla</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10849,7 +10870,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125017125</v>
+        <v>125017106</v>
       </c>
       <c r="B99" t="n">
         <v>79428</v>
@@ -10889,10 +10910,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>462683</v>
+        <v>462755</v>
       </c>
       <c r="R99" t="n">
-        <v>6769060</v>
+        <v>6769176</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10951,10 +10972,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125000074</v>
+        <v>125017125</v>
       </c>
       <c r="B100" t="n">
-        <v>57529</v>
+        <v>79428</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10967,39 +10988,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Lädsån, Dlr</t>
+          <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>462482</v>
+        <v>462683</v>
       </c>
       <c r="R100" t="n">
-        <v>6768845</v>
+        <v>6769060</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11046,19 +11062,19 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124999177</v>
+        <v>125000024</v>
       </c>
       <c r="B101" t="n">
         <v>57529</v>
@@ -11094,19 +11110,19 @@
       <c r="I101" t="inlineStr"/>
       <c r="M101" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Salutjärnen, Dlr</t>
+          <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>462684</v>
+        <v>462482</v>
       </c>
       <c r="R101" t="n">
-        <v>6769117</v>
+        <v>6768845</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11139,6 +11155,11 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11165,10 +11186,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125017118</v>
+        <v>125017166</v>
       </c>
       <c r="B102" t="n">
-        <v>79428</v>
+        <v>91361</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11177,25 +11198,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>2062</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11205,10 +11226,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>462542</v>
+        <v>462312</v>
       </c>
       <c r="R102" t="n">
-        <v>6768916</v>
+        <v>6768750</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11267,10 +11288,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125017106</v>
+        <v>125017238</v>
       </c>
       <c r="B103" t="n">
-        <v>79428</v>
+        <v>78546</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11283,21 +11304,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11307,10 +11328,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>462755</v>
+        <v>462685</v>
       </c>
       <c r="R103" t="n">
-        <v>6769176</v>
+        <v>6769071</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11369,10 +11390,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125017247</v>
+        <v>124999142</v>
       </c>
       <c r="B104" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11385,21 +11406,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11409,10 +11430,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>462756</v>
+        <v>462684</v>
       </c>
       <c r="R104" t="n">
-        <v>6769225</v>
+        <v>6769117</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11459,22 +11480,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125017166</v>
+        <v>125017156</v>
       </c>
       <c r="B105" t="n">
-        <v>91361</v>
+        <v>96354</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11483,25 +11504,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>2062</v>
+        <v>53</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11511,10 +11532,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>462312</v>
+        <v>462418</v>
       </c>
       <c r="R105" t="n">
-        <v>6768750</v>
+        <v>6768776</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11573,10 +11594,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125017285</v>
+        <v>125017141</v>
       </c>
       <c r="B106" t="n">
-        <v>91065</v>
+        <v>78842</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11585,25 +11606,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>5321</v>
+        <v>185</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11613,10 +11634,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>462561</v>
+        <v>462579</v>
       </c>
       <c r="R106" t="n">
-        <v>6768949</v>
+        <v>6768990</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11651,18 +11672,12 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>På asp</t>
-        </is>
-      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -11681,10 +11696,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124999607</v>
+        <v>125017258</v>
       </c>
       <c r="B107" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11697,21 +11712,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11721,10 +11736,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>462598</v>
+        <v>462449</v>
       </c>
       <c r="R107" t="n">
-        <v>6769000</v>
+        <v>6768783</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11759,11 +11774,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
-        </is>
-      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
@@ -11776,22 +11786,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125017253</v>
+        <v>125017118</v>
       </c>
       <c r="B108" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11804,21 +11814,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11828,10 +11838,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>462425</v>
+        <v>462542</v>
       </c>
       <c r="R108" t="n">
-        <v>6768806</v>
+        <v>6768916</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11890,10 +11900,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125017119</v>
+        <v>125017207</v>
       </c>
       <c r="B109" t="n">
-        <v>79428</v>
+        <v>8447</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11902,38 +11912,43 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>462543</v>
+        <v>462840</v>
       </c>
       <c r="R109" t="n">
-        <v>6768929</v>
+        <v>6769309</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11992,10 +12007,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125017157</v>
+        <v>125000794</v>
       </c>
       <c r="B110" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12004,25 +12019,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12032,10 +12047,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>462431</v>
+        <v>462420</v>
       </c>
       <c r="R110" t="n">
-        <v>6768769</v>
+        <v>6768785</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12070,6 +12085,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
@@ -12082,22 +12102,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125017219</v>
+        <v>125017277</v>
       </c>
       <c r="B111" t="n">
-        <v>8447</v>
+        <v>78455</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12106,43 +12126,38 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>462585</v>
+        <v>462478</v>
       </c>
       <c r="R111" t="n">
-        <v>6769050</v>
+        <v>6768887</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12201,10 +12216,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125017204</v>
+        <v>125017280</v>
       </c>
       <c r="B112" t="n">
-        <v>96979</v>
+        <v>96227</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12217,21 +12232,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>221945</v>
+        <v>2869</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12241,10 +12256,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>462438</v>
+        <v>462403</v>
       </c>
       <c r="R112" t="n">
-        <v>6768787</v>
+        <v>6768799</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12303,7 +12318,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125000267</v>
+        <v>124999425</v>
       </c>
       <c r="B113" t="n">
         <v>8447</v>
@@ -12339,14 +12354,14 @@
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Lädsån, Dlr</t>
+          <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>462482</v>
+        <v>462616</v>
       </c>
       <c r="R113" t="n">
-        <v>6768845</v>
+        <v>6769046</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12383,7 +12398,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>Miljöbilder</t>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12410,10 +12425,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125017241</v>
+        <v>125017268</v>
       </c>
       <c r="B114" t="n">
-        <v>91026</v>
+        <v>92293</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12422,38 +12437,47 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1204</v>
+        <v>4364</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>462418</v>
+        <v>462470</v>
       </c>
       <c r="R114" t="n">
-        <v>6768776</v>
+        <v>6768894</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12512,10 +12536,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125017170</v>
+        <v>125000745</v>
       </c>
       <c r="B115" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12528,34 +12552,39 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>462313</v>
+        <v>462414</v>
       </c>
       <c r="R115" t="n">
-        <v>6768749</v>
+        <v>6768796</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12590,6 +12619,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
+        </is>
+      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
@@ -12602,22 +12636,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125017137</v>
+        <v>125017186</v>
       </c>
       <c r="B116" t="n">
-        <v>78842</v>
+        <v>57529</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12630,34 +12664,43 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>462506</v>
+        <v>462647</v>
       </c>
       <c r="R116" t="n">
-        <v>6768894</v>
+        <v>6769118</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12716,10 +12759,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125017139</v>
+        <v>125017188</v>
       </c>
       <c r="B117" t="n">
-        <v>78842</v>
+        <v>57529</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12732,34 +12775,39 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>462539</v>
+        <v>462760</v>
       </c>
       <c r="R117" t="n">
-        <v>6768915</v>
+        <v>6769122</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12818,10 +12866,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125017117</v>
+        <v>125017273</v>
       </c>
       <c r="B118" t="n">
-        <v>79428</v>
+        <v>78455</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12834,21 +12882,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12858,10 +12906,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>462501</v>
+        <v>462642</v>
       </c>
       <c r="R118" t="n">
-        <v>6768895</v>
+        <v>6769092</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12920,10 +12968,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125017256</v>
+        <v>125017284</v>
       </c>
       <c r="B119" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12936,21 +12984,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12963,7 +13011,7 @@
         <v>462409</v>
       </c>
       <c r="R119" t="n">
-        <v>6768798</v>
+        <v>6768814</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13022,10 +13070,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125017282</v>
+        <v>125017123</v>
       </c>
       <c r="B120" t="n">
-        <v>78194</v>
+        <v>79428</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13038,21 +13086,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13062,10 +13110,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>462759</v>
+        <v>462680</v>
       </c>
       <c r="R120" t="n">
-        <v>6769121</v>
+        <v>6769027</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13124,10 +13172,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125017277</v>
+        <v>125017173</v>
       </c>
       <c r="B121" t="n">
-        <v>78455</v>
+        <v>56722</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13136,38 +13184,43 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>462478</v>
+        <v>462440</v>
       </c>
       <c r="R121" t="n">
-        <v>6768887</v>
+        <v>6768764</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13226,10 +13279,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125017135</v>
+        <v>125017254</v>
       </c>
       <c r="B122" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13242,21 +13295,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13266,10 +13319,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>462439</v>
+        <v>462424</v>
       </c>
       <c r="R122" t="n">
-        <v>6768813</v>
+        <v>6768802</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13328,10 +13381,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125017134</v>
+        <v>125017155</v>
       </c>
       <c r="B123" t="n">
-        <v>78842</v>
+        <v>96354</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13344,21 +13397,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>185</v>
+        <v>53</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13368,10 +13421,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>462385</v>
+        <v>462427</v>
       </c>
       <c r="R123" t="n">
-        <v>6768840</v>
+        <v>6768776</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13430,10 +13483,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125017198</v>
+        <v>125017116</v>
       </c>
       <c r="B124" t="n">
-        <v>57529</v>
+        <v>79428</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13446,39 +13499,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>462452</v>
+        <v>462460</v>
       </c>
       <c r="R124" t="n">
-        <v>6768897</v>
+        <v>6768868</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13537,10 +13585,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125017280</v>
+        <v>125017181</v>
       </c>
       <c r="B125" t="n">
-        <v>96227</v>
+        <v>79920</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13553,21 +13601,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>2869</v>
+        <v>6462</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13577,10 +13625,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>462403</v>
+        <v>462422</v>
       </c>
       <c r="R125" t="n">
-        <v>6768799</v>
+        <v>6768816</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13613,6 +13661,11 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13639,10 +13692,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125017181</v>
+        <v>125017108</v>
       </c>
       <c r="B126" t="n">
-        <v>79920</v>
+        <v>79428</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13651,25 +13704,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13679,10 +13732,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>462422</v>
+        <v>462569</v>
       </c>
       <c r="R126" t="n">
-        <v>6768816</v>
+        <v>6769031</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13715,11 +13768,6 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-05-12</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13746,10 +13794,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125017234</v>
+        <v>124999607</v>
       </c>
       <c r="B127" t="n">
-        <v>78546</v>
+        <v>79428</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13762,21 +13810,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13786,10 +13834,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>462501</v>
+        <v>462598</v>
       </c>
       <c r="R127" t="n">
-        <v>6768890</v>
+        <v>6769000</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13824,6 +13872,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
+        </is>
+      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
@@ -13836,22 +13889,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125017224</v>
+        <v>125017278</v>
       </c>
       <c r="B128" t="n">
-        <v>78547</v>
+        <v>78455</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13864,21 +13917,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13888,10 +13941,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>462683</v>
+        <v>462544</v>
       </c>
       <c r="R128" t="n">
-        <v>6769060</v>
+        <v>6768928</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13950,10 +14003,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125017271</v>
+        <v>125017253</v>
       </c>
       <c r="B129" t="n">
-        <v>78455</v>
+        <v>78810</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13966,21 +14019,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13990,10 +14043,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>462755</v>
+        <v>462425</v>
       </c>
       <c r="R129" t="n">
-        <v>6769176</v>
+        <v>6768806</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14052,7 +14105,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>125000794</v>
+        <v>125017251</v>
       </c>
       <c r="B130" t="n">
         <v>78810</v>
@@ -14092,10 +14145,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>462420</v>
+        <v>462357</v>
       </c>
       <c r="R130" t="n">
-        <v>6768785</v>
+        <v>6768775</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14130,11 +14183,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD130" t="b">
         <v>0</v>
       </c>
@@ -14147,22 +14195,22 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125017257</v>
+        <v>125017236</v>
       </c>
       <c r="B131" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14175,21 +14223,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14199,10 +14247,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>462417</v>
+        <v>462688</v>
       </c>
       <c r="R131" t="n">
-        <v>6768771</v>
+        <v>6769019</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14261,10 +14309,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125017265</v>
+        <v>125017224</v>
       </c>
       <c r="B132" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14277,21 +14325,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14301,10 +14349,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>462762</v>
+        <v>462683</v>
       </c>
       <c r="R132" t="n">
-        <v>6769125</v>
+        <v>6769060</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14363,10 +14411,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125017124</v>
+        <v>125017247</v>
       </c>
       <c r="B133" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14379,21 +14427,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14403,10 +14451,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>462679</v>
+        <v>462756</v>
       </c>
       <c r="R133" t="n">
-        <v>6769045</v>
+        <v>6769225</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14465,10 +14513,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125017237</v>
+        <v>125017113</v>
       </c>
       <c r="B134" t="n">
-        <v>78546</v>
+        <v>79428</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14481,21 +14529,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14505,10 +14553,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>462684</v>
+        <v>462356</v>
       </c>
       <c r="R134" t="n">
-        <v>6769060</v>
+        <v>6768753</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14567,7 +14615,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125017116</v>
+        <v>125007648</v>
       </c>
       <c r="B135" t="n">
         <v>79428</v>
@@ -14607,10 +14655,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>462460</v>
+        <v>462431</v>
       </c>
       <c r="R135" t="n">
-        <v>6768868</v>
+        <v>6768885</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14645,6 +14693,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD135" t="b">
         <v>0</v>
       </c>
@@ -14657,12 +14710,12 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
@@ -14776,10 +14829,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125017210</v>
+        <v>125017136</v>
       </c>
       <c r="B137" t="n">
-        <v>8447</v>
+        <v>78842</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -14788,43 +14841,38 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>462636</v>
+        <v>462449</v>
       </c>
       <c r="R137" t="n">
-        <v>6769113</v>
+        <v>6768898</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14883,10 +14931,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>124999425</v>
+        <v>125017279</v>
       </c>
       <c r="B138" t="n">
-        <v>8447</v>
+        <v>78455</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -14895,25 +14943,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14923,10 +14971,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>462616</v>
+        <v>462581</v>
       </c>
       <c r="R138" t="n">
-        <v>6769046</v>
+        <v>6768944</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14961,11 +15009,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
-        </is>
-      </c>
       <c r="AD138" t="b">
         <v>0</v>
       </c>
@@ -14978,22 +15021,22 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>125017252</v>
+        <v>125017137</v>
       </c>
       <c r="B139" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15006,21 +15049,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15030,10 +15073,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>462426</v>
+        <v>462506</v>
       </c>
       <c r="R139" t="n">
-        <v>6768812</v>
+        <v>6768894</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15092,10 +15135,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>125017266</v>
+        <v>125017263</v>
       </c>
       <c r="B140" t="n">
-        <v>92293</v>
+        <v>78810</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15104,47 +15147,38 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>462462</v>
+        <v>462712</v>
       </c>
       <c r="R140" t="n">
-        <v>6768863</v>
+        <v>6769149</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15203,10 +15237,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>125017268</v>
+        <v>125017259</v>
       </c>
       <c r="B141" t="n">
-        <v>92293</v>
+        <v>78810</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15215,47 +15249,38 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>462470</v>
+        <v>462444</v>
       </c>
       <c r="R141" t="n">
-        <v>6768894</v>
+        <v>6768832</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15314,10 +15339,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>125017284</v>
+        <v>125017257</v>
       </c>
       <c r="B142" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15330,21 +15355,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15354,10 +15379,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>462409</v>
+        <v>462417</v>
       </c>
       <c r="R142" t="n">
-        <v>6768814</v>
+        <v>6768771</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15416,10 +15441,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>125017246</v>
+        <v>125017234</v>
       </c>
       <c r="B143" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15432,21 +15457,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15456,10 +15481,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>462868</v>
+        <v>462501</v>
       </c>
       <c r="R143" t="n">
-        <v>6769325</v>
+        <v>6768890</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15518,10 +15543,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>125017261</v>
+        <v>124999190</v>
       </c>
       <c r="B144" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15530,25 +15555,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15558,10 +15583,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>462696</v>
+        <v>462672</v>
       </c>
       <c r="R144" t="n">
-        <v>6769144</v>
+        <v>6769113</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15608,22 +15633,22 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>125017207</v>
+        <v>125017202</v>
       </c>
       <c r="B145" t="n">
-        <v>8447</v>
+        <v>91299</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15632,43 +15657,38 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>106545</v>
+        <v>658</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>462840</v>
+        <v>462414</v>
       </c>
       <c r="R145" t="n">
-        <v>6769309</v>
+        <v>6768758</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15727,10 +15747,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>125017273</v>
+        <v>125017139</v>
       </c>
       <c r="B146" t="n">
-        <v>78455</v>
+        <v>78842</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15743,21 +15763,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15767,10 +15787,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>462642</v>
+        <v>462539</v>
       </c>
       <c r="R146" t="n">
-        <v>6769092</v>
+        <v>6768915</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15829,10 +15849,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125017171</v>
+        <v>125017271</v>
       </c>
       <c r="B147" t="n">
-        <v>91012</v>
+        <v>78455</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15845,21 +15865,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1202</v>
+        <v>353</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15869,10 +15889,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>462425</v>
+        <v>462755</v>
       </c>
       <c r="R147" t="n">
-        <v>6768807</v>
+        <v>6769176</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15931,10 +15951,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125017236</v>
+        <v>125017170</v>
       </c>
       <c r="B148" t="n">
-        <v>78546</v>
+        <v>91012</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15947,21 +15967,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15971,10 +15991,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>462688</v>
+        <v>462313</v>
       </c>
       <c r="R148" t="n">
-        <v>6769019</v>
+        <v>6768749</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16033,10 +16053,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125017186</v>
+        <v>125017256</v>
       </c>
       <c r="B149" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16049,43 +16069,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>462647</v>
+        <v>462409</v>
       </c>
       <c r="R149" t="n">
-        <v>6769118</v>
+        <v>6768798</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16144,10 +16155,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125017175</v>
+        <v>125017265</v>
       </c>
       <c r="B150" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16156,43 +16167,38 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>462419</v>
+        <v>462762</v>
       </c>
       <c r="R150" t="n">
-        <v>6768798</v>
+        <v>6769125</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16251,10 +16257,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>125017254</v>
+        <v>125000267</v>
       </c>
       <c r="B151" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16263,38 +16269,38 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Salutjärnen, Dlr</t>
+          <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>462424</v>
+        <v>462482</v>
       </c>
       <c r="R151" t="n">
-        <v>6768802</v>
+        <v>6768845</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16329,6 +16335,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
+        </is>
+      </c>
       <c r="AD151" t="b">
         <v>0</v>
       </c>
@@ -16341,22 +16352,22 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>125017250</v>
+        <v>125017225</v>
       </c>
       <c r="B152" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16365,38 +16376,43 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P152" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>462364</v>
+        <v>462449</v>
       </c>
       <c r="R152" t="n">
-        <v>6768755</v>
+        <v>6768765</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16455,10 +16471,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>125017228</v>
+        <v>125017220</v>
       </c>
       <c r="B153" t="n">
-        <v>94766</v>
+        <v>8447</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16471,34 +16487,39 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>2412</v>
+        <v>106545</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Philonotis fontana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P153" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>462418</v>
+        <v>462472</v>
       </c>
       <c r="R153" t="n">
-        <v>6768790</v>
+        <v>6768856</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16531,11 +16552,6 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-05-12</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>I kallkälla</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16562,10 +16578,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>125017114</v>
+        <v>125017135</v>
       </c>
       <c r="B154" t="n">
-        <v>79428</v>
+        <v>78842</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16578,21 +16594,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16602,10 +16618,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>462451</v>
+        <v>462439</v>
       </c>
       <c r="R154" t="n">
-        <v>6768820</v>
+        <v>6768813</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16664,10 +16680,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>125017130</v>
+        <v>125017140</v>
       </c>
       <c r="B155" t="n">
-        <v>79428</v>
+        <v>78842</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16680,21 +16696,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16704,10 +16720,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>462444</v>
+        <v>462575</v>
       </c>
       <c r="R155" t="n">
-        <v>6768840</v>
+        <v>6768972</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16766,7 +16782,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>125007547</v>
+        <v>125017130</v>
       </c>
       <c r="B156" t="n">
         <v>79428</v>
@@ -16806,10 +16822,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>462441</v>
+        <v>462444</v>
       </c>
       <c r="R156" t="n">
-        <v>6768886</v>
+        <v>6768840</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16844,11 +16860,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD156" t="b">
         <v>0</v>
       </c>
@@ -16861,22 +16872,22 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>125017156</v>
+        <v>125017157</v>
       </c>
       <c r="B157" t="n">
-        <v>96354</v>
+        <v>90977</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16885,25 +16896,25 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16913,10 +16924,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>462418</v>
+        <v>462431</v>
       </c>
       <c r="R157" t="n">
-        <v>6768776</v>
+        <v>6768769</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16975,10 +16986,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>125017278</v>
+        <v>125017199</v>
       </c>
       <c r="B158" t="n">
-        <v>78455</v>
+        <v>96345</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16991,21 +17002,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>353</v>
+        <v>54</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skogstrappmossa</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anastrophyllum michauxii</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(F.Weber.) H.Buch</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17015,10 +17026,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>462544</v>
+        <v>462249</v>
       </c>
       <c r="R158" t="n">
-        <v>6768928</v>
+        <v>6768580</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17059,6 +17070,7 @@
       <c r="AE158" t="b">
         <v>0</v>
       </c>
+      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
@@ -17077,10 +17089,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>125017188</v>
+        <v>125017154</v>
       </c>
       <c r="B159" t="n">
-        <v>57529</v>
+        <v>96354</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -17093,39 +17105,34 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P159" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>462760</v>
+        <v>462433</v>
       </c>
       <c r="R159" t="n">
-        <v>6769122</v>
+        <v>6768784</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17184,7 +17191,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>124999142</v>
+        <v>125017134</v>
       </c>
       <c r="B160" t="n">
         <v>78842</v>
@@ -17224,10 +17231,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>462684</v>
+        <v>462385</v>
       </c>
       <c r="R160" t="n">
-        <v>6769117</v>
+        <v>6768840</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17274,22 +17281,22 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>125017220</v>
+        <v>125017124</v>
       </c>
       <c r="B161" t="n">
-        <v>8447</v>
+        <v>79428</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17298,43 +17305,38 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P161" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>462472</v>
+        <v>462679</v>
       </c>
       <c r="R161" t="n">
-        <v>6768856</v>
+        <v>6769045</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17393,10 +17395,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>125017260</v>
+        <v>125017266</v>
       </c>
       <c r="B162" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17405,38 +17407,47 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P162" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>462575</v>
+        <v>462462</v>
       </c>
       <c r="R162" t="n">
-        <v>6768974</v>
+        <v>6768863</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17495,10 +17506,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>125017199</v>
+        <v>125017246</v>
       </c>
       <c r="B163" t="n">
-        <v>96345</v>
+        <v>78810</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17511,21 +17522,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>54</v>
+        <v>6425</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Skogstrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Anastrophyllum michauxii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(F.Weber.) H.Buch</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17535,10 +17546,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>462249</v>
+        <v>462868</v>
       </c>
       <c r="R163" t="n">
-        <v>6768580</v>
+        <v>6769325</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17579,7 +17590,6 @@
       <c r="AE163" t="b">
         <v>0</v>
       </c>
-      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
@@ -17598,10 +17608,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>125017108</v>
+        <v>125017250</v>
       </c>
       <c r="B164" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17614,21 +17624,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17638,10 +17648,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>462569</v>
+        <v>462364</v>
       </c>
       <c r="R164" t="n">
-        <v>6769031</v>
+        <v>6768755</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17700,10 +17710,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>125017115</v>
+        <v>125017237</v>
       </c>
       <c r="B165" t="n">
-        <v>79428</v>
+        <v>78546</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -17716,21 +17726,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17740,10 +17750,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>462449</v>
+        <v>462684</v>
       </c>
       <c r="R165" t="n">
-        <v>6768835</v>
+        <v>6769060</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17802,7 +17812,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>125001637</v>
+        <v>125017175</v>
       </c>
       <c r="B166" t="n">
         <v>56722</v>
@@ -17847,10 +17857,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>462376</v>
+        <v>462419</v>
       </c>
       <c r="R166" t="n">
-        <v>6768807</v>
+        <v>6768798</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17897,22 +17907,22 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>124999088</v>
+        <v>125017185</v>
       </c>
       <c r="B167" t="n">
-        <v>57529</v>
+        <v>98122</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -17921,25 +17931,25 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>100049</v>
+        <v>221952</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17949,10 +17959,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>462698</v>
+        <v>462417</v>
       </c>
       <c r="R167" t="n">
-        <v>6769146</v>
+        <v>6768771</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17987,11 +17997,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC167" t="inlineStr">
-        <is>
-          <t>Miljöbilder. Sannoligt spillkråka, hackhål/bohål.</t>
-        </is>
-      </c>
       <c r="AD167" t="b">
         <v>0</v>
       </c>
@@ -18004,12 +18009,12 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>

--- a/artfynd/A 18527-2025 artfynd.xlsx
+++ b/artfynd/A 18527-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124770579</v>
+        <v>124781784</v>
       </c>
       <c r="B2" t="n">
-        <v>74901</v>
+        <v>57529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>462182</v>
+        <v>462362</v>
       </c>
       <c r="R2" t="n">
-        <v>6768583</v>
+        <v>6768766</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124774463</v>
+        <v>124778690</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +798,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>462264</v>
+        <v>462388</v>
       </c>
       <c r="R3" t="n">
-        <v>6768671</v>
+        <v>6768696</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +863,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124774845</v>
+        <v>124782461</v>
       </c>
       <c r="B4" t="n">
-        <v>8447</v>
+        <v>56722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,34 +910,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462271</v>
+        <v>462374</v>
       </c>
       <c r="R4" t="n">
-        <v>6768703</v>
+        <v>6768823</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124781784</v>
+        <v>124770579</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>74901</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,39 +1017,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462362</v>
+        <v>462182</v>
       </c>
       <c r="R5" t="n">
-        <v>6768766</v>
+        <v>6768583</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124778690</v>
+        <v>124774463</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,39 +1119,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>462388</v>
+        <v>462264</v>
       </c>
       <c r="R6" t="n">
-        <v>6768696</v>
+        <v>6768671</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,11 +1179,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124782461</v>
+        <v>124774845</v>
       </c>
       <c r="B7" t="n">
-        <v>56722</v>
+        <v>8447</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,39 +1221,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>462374</v>
+        <v>462271</v>
       </c>
       <c r="R7" t="n">
-        <v>6768823</v>
+        <v>6768703</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1934,10 +1934,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124781860</v>
+        <v>124776291</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1950,34 +1950,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>462362</v>
+        <v>462311</v>
       </c>
       <c r="R14" t="n">
-        <v>6768766</v>
+        <v>6768690</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2010,11 +2015,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2041,10 +2041,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124776291</v>
+        <v>124781860</v>
       </c>
       <c r="B15" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2057,39 +2057,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>462311</v>
+        <v>462362</v>
       </c>
       <c r="R15" t="n">
-        <v>6768690</v>
+        <v>6768766</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2122,6 +2117,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -4049,10 +4049,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124774494</v>
+        <v>124772212</v>
       </c>
       <c r="B34" t="n">
-        <v>8447</v>
+        <v>57529</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4061,38 +4061,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>462257</v>
+        <v>462184</v>
       </c>
       <c r="R34" t="n">
-        <v>6768691</v>
+        <v>6768538</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4125,6 +4130,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4151,10 +4161,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124772212</v>
+        <v>124774494</v>
       </c>
       <c r="B35" t="n">
-        <v>57529</v>
+        <v>8447</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4163,43 +4173,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>462184</v>
+        <v>462257</v>
       </c>
       <c r="R35" t="n">
-        <v>6768538</v>
+        <v>6768691</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4232,11 +4237,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5954,10 +5954,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125017199</v>
+        <v>125017127</v>
       </c>
       <c r="B52" t="n">
-        <v>96345</v>
+        <v>79428</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5970,21 +5970,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>54</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skogstrappmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Anastrophyllum michauxii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(F.Weber.) H.Buch</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5994,10 +5994,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>462249</v>
+        <v>462685</v>
       </c>
       <c r="R52" t="n">
-        <v>6768580</v>
+        <v>6769071</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6038,7 +6038,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6057,7 +6056,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125017127</v>
+        <v>125017112</v>
       </c>
       <c r="B53" t="n">
         <v>79428</v>
@@ -6097,10 +6096,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>462685</v>
+        <v>462453</v>
       </c>
       <c r="R53" t="n">
-        <v>6769071</v>
+        <v>6768876</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6159,10 +6158,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125017112</v>
+        <v>124999088</v>
       </c>
       <c r="B54" t="n">
-        <v>79428</v>
+        <v>57529</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6175,21 +6174,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6199,10 +6198,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>462453</v>
+        <v>462698</v>
       </c>
       <c r="R54" t="n">
-        <v>6768876</v>
+        <v>6769146</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6237,6 +6236,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Miljöbilder. Sannoligt spillkråka, hackhål/bohål.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6249,22 +6253,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124999088</v>
+        <v>125017225</v>
       </c>
       <c r="B55" t="n">
-        <v>57529</v>
+        <v>8447</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6273,38 +6277,43 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>462698</v>
+        <v>462449</v>
       </c>
       <c r="R55" t="n">
-        <v>6769146</v>
+        <v>6768765</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6339,11 +6348,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Miljöbilder. Sannoligt spillkråka, hackhål/bohål.</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6356,22 +6360,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125017224</v>
+        <v>125017220</v>
       </c>
       <c r="B56" t="n">
-        <v>78547</v>
+        <v>8447</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6380,38 +6384,43 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>462683</v>
+        <v>462472</v>
       </c>
       <c r="R56" t="n">
-        <v>6769060</v>
+        <v>6768856</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6470,10 +6479,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125017225</v>
+        <v>125017224</v>
       </c>
       <c r="B57" t="n">
-        <v>8447</v>
+        <v>78547</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6482,43 +6491,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>462449</v>
+        <v>462683</v>
       </c>
       <c r="R57" t="n">
-        <v>6768765</v>
+        <v>6769060</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6577,10 +6581,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125017220</v>
+        <v>125017199</v>
       </c>
       <c r="B58" t="n">
-        <v>8447</v>
+        <v>96345</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6589,43 +6593,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>54</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skogstrappmossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Anastrophyllum michauxii</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(F.Weber.) H.Buch</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>462472</v>
+        <v>462249</v>
       </c>
       <c r="R58" t="n">
-        <v>6768856</v>
+        <v>6768580</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6666,6 +6665,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6684,10 +6684,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125017140</v>
+        <v>125017210</v>
       </c>
       <c r="B59" t="n">
-        <v>78842</v>
+        <v>8447</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6696,38 +6696,43 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>462575</v>
+        <v>462636</v>
       </c>
       <c r="R59" t="n">
-        <v>6768972</v>
+        <v>6769113</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6995,10 +7000,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125017210</v>
+        <v>125017140</v>
       </c>
       <c r="B62" t="n">
-        <v>8447</v>
+        <v>78842</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7007,43 +7012,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>462636</v>
+        <v>462575</v>
       </c>
       <c r="R62" t="n">
-        <v>6769113</v>
+        <v>6768972</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -9065,10 +9065,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125017263</v>
+        <v>125017219</v>
       </c>
       <c r="B82" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9077,38 +9077,43 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>462712</v>
+        <v>462585</v>
       </c>
       <c r="R82" t="n">
-        <v>6769149</v>
+        <v>6769050</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9167,10 +9172,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125017219</v>
+        <v>125017263</v>
       </c>
       <c r="B83" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9179,43 +9184,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>462585</v>
+        <v>462712</v>
       </c>
       <c r="R83" t="n">
-        <v>6769050</v>
+        <v>6769149</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9381,10 +9381,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125017236</v>
+        <v>125017166</v>
       </c>
       <c r="B85" t="n">
-        <v>78546</v>
+        <v>91361</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9393,25 +9393,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6446</v>
+        <v>2062</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9421,10 +9421,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>462688</v>
+        <v>462312</v>
       </c>
       <c r="R85" t="n">
-        <v>6769019</v>
+        <v>6768750</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9483,10 +9483,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125017105</v>
+        <v>125017142</v>
       </c>
       <c r="B86" t="n">
-        <v>79428</v>
+        <v>78842</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9499,21 +9499,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9523,10 +9523,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>462811</v>
+        <v>462682</v>
       </c>
       <c r="R86" t="n">
-        <v>6769258</v>
+        <v>6769024</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9585,10 +9585,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125017166</v>
+        <v>125017236</v>
       </c>
       <c r="B87" t="n">
-        <v>91361</v>
+        <v>78546</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9597,25 +9597,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2062</v>
+        <v>6446</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9625,10 +9625,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>462312</v>
+        <v>462688</v>
       </c>
       <c r="R87" t="n">
-        <v>6768750</v>
+        <v>6769019</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9687,10 +9687,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125017142</v>
+        <v>125017105</v>
       </c>
       <c r="B88" t="n">
-        <v>78842</v>
+        <v>79428</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9703,21 +9703,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9727,10 +9727,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>462682</v>
+        <v>462811</v>
       </c>
       <c r="R88" t="n">
-        <v>6769024</v>
+        <v>6769258</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9789,10 +9789,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124999332</v>
+        <v>125017240</v>
       </c>
       <c r="B89" t="n">
-        <v>79428</v>
+        <v>58191</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9801,25 +9801,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6453</v>
+        <v>103044</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9829,10 +9829,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>462658</v>
+        <v>462248</v>
       </c>
       <c r="R89" t="n">
-        <v>6769079</v>
+        <v>6768584</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9879,19 +9879,19 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125001392</v>
+        <v>124999332</v>
       </c>
       <c r="B90" t="n">
         <v>79428</v>
@@ -9931,10 +9931,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>462456</v>
+        <v>462658</v>
       </c>
       <c r="R90" t="n">
-        <v>6768778</v>
+        <v>6769079</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9967,11 +9967,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-05-12</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9998,10 +9993,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125000045</v>
+        <v>125001392</v>
       </c>
       <c r="B91" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10014,34 +10009,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Lädsån, Dlr</t>
+          <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>462482</v>
+        <v>462456</v>
       </c>
       <c r="R91" t="n">
-        <v>6768845</v>
+        <v>6768778</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10074,6 +10069,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10100,10 +10100,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125017240</v>
+        <v>125000045</v>
       </c>
       <c r="B92" t="n">
-        <v>58191</v>
+        <v>78810</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10112,38 +10112,38 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>103044</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Salutjärnen, Dlr</t>
+          <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>462248</v>
+        <v>462482</v>
       </c>
       <c r="R92" t="n">
-        <v>6768584</v>
+        <v>6768845</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10190,12 +10190,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -10309,10 +10309,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125000024</v>
+        <v>125017273</v>
       </c>
       <c r="B94" t="n">
-        <v>57529</v>
+        <v>78455</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10325,39 +10325,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Lädsån, Dlr</t>
+          <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>462482</v>
+        <v>462642</v>
       </c>
       <c r="R94" t="n">
-        <v>6768845</v>
+        <v>6769092</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10392,11 +10387,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
@@ -10409,22 +10399,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125017251</v>
+        <v>125017277</v>
       </c>
       <c r="B95" t="n">
-        <v>78810</v>
+        <v>78455</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10437,21 +10427,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10461,10 +10451,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>462357</v>
+        <v>462478</v>
       </c>
       <c r="R95" t="n">
-        <v>6768775</v>
+        <v>6768887</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10523,10 +10513,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125007547</v>
+        <v>125017139</v>
       </c>
       <c r="B96" t="n">
-        <v>79428</v>
+        <v>78842</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10539,21 +10529,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10563,10 +10553,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>462441</v>
+        <v>462539</v>
       </c>
       <c r="R96" t="n">
-        <v>6768886</v>
+        <v>6768915</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10601,11 +10591,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
@@ -10618,22 +10603,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125017265</v>
+        <v>125000024</v>
       </c>
       <c r="B97" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10646,34 +10631,39 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Salutjärnen, Dlr</t>
+          <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>462762</v>
+        <v>462482</v>
       </c>
       <c r="R97" t="n">
-        <v>6769125</v>
+        <v>6768845</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10708,6 +10698,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
@@ -10720,22 +10715,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125017273</v>
+        <v>125017251</v>
       </c>
       <c r="B98" t="n">
-        <v>78455</v>
+        <v>78810</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10748,21 +10743,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10772,10 +10767,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>462642</v>
+        <v>462357</v>
       </c>
       <c r="R98" t="n">
-        <v>6769092</v>
+        <v>6768775</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10834,10 +10829,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125017277</v>
+        <v>125007547</v>
       </c>
       <c r="B99" t="n">
-        <v>78455</v>
+        <v>79428</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10850,21 +10845,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10874,10 +10869,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>462478</v>
+        <v>462441</v>
       </c>
       <c r="R99" t="n">
-        <v>6768887</v>
+        <v>6768886</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10912,6 +10907,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
@@ -10924,22 +10924,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125017139</v>
+        <v>125017265</v>
       </c>
       <c r="B100" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10952,21 +10952,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10976,10 +10976,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>462539</v>
+        <v>462762</v>
       </c>
       <c r="R100" t="n">
-        <v>6768915</v>
+        <v>6769125</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11038,10 +11038,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125017135</v>
+        <v>125017113</v>
       </c>
       <c r="B101" t="n">
-        <v>78842</v>
+        <v>79428</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11054,21 +11054,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11078,10 +11078,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>462439</v>
+        <v>462356</v>
       </c>
       <c r="R101" t="n">
-        <v>6768813</v>
+        <v>6768753</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11140,10 +11140,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125017284</v>
+        <v>125017247</v>
       </c>
       <c r="B102" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11156,21 +11156,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11180,10 +11180,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>462409</v>
+        <v>462756</v>
       </c>
       <c r="R102" t="n">
-        <v>6768814</v>
+        <v>6769225</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11242,10 +11242,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125017113</v>
+        <v>125017262</v>
       </c>
       <c r="B103" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11258,21 +11258,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11282,10 +11282,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>462356</v>
+        <v>462703</v>
       </c>
       <c r="R103" t="n">
-        <v>6768753</v>
+        <v>6769146</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11344,10 +11344,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125017247</v>
+        <v>124999027</v>
       </c>
       <c r="B104" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11360,21 +11360,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11384,10 +11384,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>462756</v>
+        <v>462741</v>
       </c>
       <c r="R104" t="n">
-        <v>6769225</v>
+        <v>6769142</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11422,6 +11422,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Miljöbilder. Sannoligt bohål/hackhål efter spillkråka.</t>
+        </is>
+      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
@@ -11434,22 +11439,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125017262</v>
+        <v>125017135</v>
       </c>
       <c r="B105" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11462,21 +11467,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11486,10 +11491,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>462703</v>
+        <v>462439</v>
       </c>
       <c r="R105" t="n">
-        <v>6769146</v>
+        <v>6768813</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11548,10 +11553,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124999027</v>
+        <v>125017284</v>
       </c>
       <c r="B106" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11564,21 +11569,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11588,10 +11593,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>462741</v>
+        <v>462409</v>
       </c>
       <c r="R106" t="n">
-        <v>6769142</v>
+        <v>6768814</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11626,11 +11631,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Miljöbilder. Sannoligt bohål/hackhål efter spillkråka.</t>
-        </is>
-      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
@@ -11643,22 +11643,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125017254</v>
+        <v>125017156</v>
       </c>
       <c r="B107" t="n">
-        <v>78810</v>
+        <v>96354</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11671,21 +11671,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11695,10 +11695,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>462424</v>
+        <v>462418</v>
       </c>
       <c r="R107" t="n">
-        <v>6768802</v>
+        <v>6768776</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11757,10 +11757,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125000745</v>
+        <v>125017254</v>
       </c>
       <c r="B108" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11773,39 +11773,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>462414</v>
+        <v>462424</v>
       </c>
       <c r="R108" t="n">
-        <v>6768796</v>
+        <v>6768802</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11840,11 +11835,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
-        </is>
-      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
@@ -11857,22 +11847,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125017202</v>
+        <v>125000745</v>
       </c>
       <c r="B109" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11885,24 +11875,29 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
@@ -11912,7 +11907,7 @@
         <v>462414</v>
       </c>
       <c r="R109" t="n">
-        <v>6768758</v>
+        <v>6768796</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11947,6 +11942,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
+        </is>
+      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
@@ -11959,22 +11959,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125017156</v>
+        <v>125017202</v>
       </c>
       <c r="B110" t="n">
-        <v>96354</v>
+        <v>91299</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11987,21 +11987,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>53</v>
+        <v>658</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12011,10 +12011,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>462418</v>
+        <v>462414</v>
       </c>
       <c r="R110" t="n">
-        <v>6768776</v>
+        <v>6768758</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12287,10 +12287,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125017241</v>
+        <v>125017162</v>
       </c>
       <c r="B113" t="n">
-        <v>91026</v>
+        <v>79428</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12303,21 +12303,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1204</v>
+        <v>6453</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12327,10 +12327,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>462418</v>
+        <v>462763</v>
       </c>
       <c r="R113" t="n">
-        <v>6768776</v>
+        <v>6769126</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12389,10 +12389,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125017162</v>
+        <v>125017253</v>
       </c>
       <c r="B114" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12405,21 +12405,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12429,10 +12429,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>462763</v>
+        <v>462425</v>
       </c>
       <c r="R114" t="n">
-        <v>6769126</v>
+        <v>6768806</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12491,10 +12491,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125017253</v>
+        <v>125017241</v>
       </c>
       <c r="B115" t="n">
-        <v>78810</v>
+        <v>91026</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12507,21 +12507,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12531,10 +12531,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>462425</v>
+        <v>462418</v>
       </c>
       <c r="R115" t="n">
-        <v>6768806</v>
+        <v>6768776</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12593,10 +12593,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125017285</v>
+        <v>125017212</v>
       </c>
       <c r="B116" t="n">
-        <v>91065</v>
+        <v>8447</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12609,34 +12609,39 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5321</v>
+        <v>106545</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>462561</v>
+        <v>462295</v>
       </c>
       <c r="R116" t="n">
-        <v>6768949</v>
+        <v>6768622</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12671,18 +12676,12 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>På asp</t>
-        </is>
-      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12701,10 +12700,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125017154</v>
+        <v>125017123</v>
       </c>
       <c r="B117" t="n">
-        <v>96354</v>
+        <v>79428</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12717,21 +12716,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>53</v>
+        <v>6453</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12741,10 +12740,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>462433</v>
+        <v>462680</v>
       </c>
       <c r="R117" t="n">
-        <v>6768784</v>
+        <v>6769027</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12803,10 +12802,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125017134</v>
+        <v>125017118</v>
       </c>
       <c r="B118" t="n">
-        <v>78842</v>
+        <v>79428</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12819,21 +12818,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12843,10 +12842,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>462385</v>
+        <v>462542</v>
       </c>
       <c r="R118" t="n">
-        <v>6768840</v>
+        <v>6768916</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12905,10 +12904,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125017212</v>
+        <v>125017124</v>
       </c>
       <c r="B119" t="n">
-        <v>8447</v>
+        <v>79428</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12917,43 +12916,38 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>462295</v>
+        <v>462679</v>
       </c>
       <c r="R119" t="n">
-        <v>6768622</v>
+        <v>6769045</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13012,10 +13006,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125017123</v>
+        <v>125001616</v>
       </c>
       <c r="B120" t="n">
-        <v>79428</v>
+        <v>56722</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13024,38 +13018,43 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>462680</v>
+        <v>462456</v>
       </c>
       <c r="R120" t="n">
-        <v>6769027</v>
+        <v>6768778</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13090,6 +13089,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Miljöbilder. Så kallad tjädertall</t>
+        </is>
+      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
@@ -13102,22 +13106,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125017118</v>
+        <v>125017154</v>
       </c>
       <c r="B121" t="n">
-        <v>79428</v>
+        <v>96354</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13130,21 +13134,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6453</v>
+        <v>53</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13154,10 +13158,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>462542</v>
+        <v>462433</v>
       </c>
       <c r="R121" t="n">
-        <v>6768916</v>
+        <v>6768784</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13216,10 +13220,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125017124</v>
+        <v>125017134</v>
       </c>
       <c r="B122" t="n">
-        <v>79428</v>
+        <v>78842</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13232,21 +13236,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13256,10 +13260,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>462679</v>
+        <v>462385</v>
       </c>
       <c r="R122" t="n">
-        <v>6769045</v>
+        <v>6768840</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13318,10 +13322,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125001616</v>
+        <v>125017285</v>
       </c>
       <c r="B123" t="n">
-        <v>56722</v>
+        <v>91065</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13334,39 +13338,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100138</v>
+        <v>5321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>462456</v>
+        <v>462561</v>
       </c>
       <c r="R123" t="n">
-        <v>6768778</v>
+        <v>6768949</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13403,7 +13402,7 @@
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Miljöbilder. Så kallad tjädertall</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13412,18 +13411,19 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
@@ -14348,10 +14348,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125017125</v>
+        <v>125017155</v>
       </c>
       <c r="B133" t="n">
-        <v>79428</v>
+        <v>96354</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14364,21 +14364,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6453</v>
+        <v>53</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14388,10 +14388,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>462683</v>
+        <v>462427</v>
       </c>
       <c r="R133" t="n">
-        <v>6769060</v>
+        <v>6768776</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14552,10 +14552,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125017155</v>
+        <v>125017125</v>
       </c>
       <c r="B135" t="n">
-        <v>96354</v>
+        <v>79428</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14568,21 +14568,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>53</v>
+        <v>6453</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14592,10 +14592,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>462427</v>
+        <v>462683</v>
       </c>
       <c r="R135" t="n">
-        <v>6768776</v>
+        <v>6769060</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15286,10 +15286,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>125017256</v>
+        <v>124999177</v>
       </c>
       <c r="B142" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15302,34 +15302,39 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>462409</v>
+        <v>462684</v>
       </c>
       <c r="R142" t="n">
-        <v>6768798</v>
+        <v>6769117</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15376,22 +15381,22 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>125017266</v>
+        <v>125017205</v>
       </c>
       <c r="B143" t="n">
-        <v>92293</v>
+        <v>8447</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15404,31 +15409,27 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
@@ -15437,10 +15438,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>462462</v>
+        <v>462864</v>
       </c>
       <c r="R143" t="n">
-        <v>6768863</v>
+        <v>6769317</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15499,10 +15500,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>125017190</v>
+        <v>125017266</v>
       </c>
       <c r="B144" t="n">
-        <v>57529</v>
+        <v>92293</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15511,31 +15512,35 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
@@ -15544,10 +15549,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>462791</v>
+        <v>462462</v>
       </c>
       <c r="R144" t="n">
-        <v>6769257</v>
+        <v>6768863</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15606,7 +15611,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>125000666</v>
+        <v>125017190</v>
       </c>
       <c r="B145" t="n">
         <v>57529</v>
@@ -15651,10 +15656,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>462422</v>
+        <v>462791</v>
       </c>
       <c r="R145" t="n">
-        <v>6768811</v>
+        <v>6769257</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15701,19 +15706,19 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>124999177</v>
+        <v>125000666</v>
       </c>
       <c r="B146" t="n">
         <v>57529</v>
@@ -15758,10 +15763,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>462684</v>
+        <v>462422</v>
       </c>
       <c r="R146" t="n">
-        <v>6769117</v>
+        <v>6768811</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15820,10 +15825,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125017205</v>
+        <v>125017256</v>
       </c>
       <c r="B147" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15832,43 +15837,38 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>462864</v>
+        <v>462409</v>
       </c>
       <c r="R147" t="n">
-        <v>6769317</v>
+        <v>6768798</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17603,10 +17603,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>125017185</v>
+        <v>125017136</v>
       </c>
       <c r="B164" t="n">
-        <v>98122</v>
+        <v>78842</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17615,25 +17615,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>221952</v>
+        <v>185</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17643,10 +17643,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>462417</v>
+        <v>462449</v>
       </c>
       <c r="R164" t="n">
-        <v>6768771</v>
+        <v>6768898</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17705,10 +17705,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>125017136</v>
+        <v>125000794</v>
       </c>
       <c r="B165" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -17721,21 +17721,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17745,10 +17745,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>462449</v>
+        <v>462420</v>
       </c>
       <c r="R165" t="n">
-        <v>6768898</v>
+        <v>6768785</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17783,6 +17783,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD165" t="b">
         <v>0</v>
       </c>
@@ -17795,22 +17800,22 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>125000794</v>
+        <v>125007648</v>
       </c>
       <c r="B166" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -17823,21 +17828,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17847,10 +17852,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>462420</v>
+        <v>462431</v>
       </c>
       <c r="R166" t="n">
-        <v>6768785</v>
+        <v>6768885</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17914,10 +17919,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>125007648</v>
+        <v>125017185</v>
       </c>
       <c r="B167" t="n">
-        <v>79428</v>
+        <v>98122</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -17926,25 +17931,25 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6453</v>
+        <v>221952</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17954,10 +17959,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>462431</v>
+        <v>462417</v>
       </c>
       <c r="R167" t="n">
-        <v>6768885</v>
+        <v>6768771</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17992,11 +17997,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC167" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD167" t="b">
         <v>0</v>
       </c>
@@ -18009,12 +18009,12 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>

--- a/artfynd/A 18527-2025 artfynd.xlsx
+++ b/artfynd/A 18527-2025 artfynd.xlsx
@@ -1934,10 +1934,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124776291</v>
+        <v>124781860</v>
       </c>
       <c r="B14" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1950,39 +1950,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>462311</v>
+        <v>462362</v>
       </c>
       <c r="R14" t="n">
-        <v>6768690</v>
+        <v>6768766</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2015,6 +2010,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2041,10 +2041,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124781860</v>
+        <v>124776291</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2057,34 +2057,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>462362</v>
+        <v>462311</v>
       </c>
       <c r="R15" t="n">
-        <v>6768766</v>
+        <v>6768690</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2117,11 +2122,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -4049,10 +4049,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124772212</v>
+        <v>124774494</v>
       </c>
       <c r="B34" t="n">
-        <v>57529</v>
+        <v>8447</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4061,43 +4061,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>462184</v>
+        <v>462257</v>
       </c>
       <c r="R34" t="n">
-        <v>6768538</v>
+        <v>6768691</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4130,11 +4125,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4161,10 +4151,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124774494</v>
+        <v>124772212</v>
       </c>
       <c r="B35" t="n">
-        <v>8447</v>
+        <v>57529</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4173,38 +4163,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>462257</v>
+        <v>462184</v>
       </c>
       <c r="R35" t="n">
-        <v>6768691</v>
+        <v>6768538</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4237,6 +4232,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5430,10 +5430,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124836527</v>
+        <v>124833451</v>
       </c>
       <c r="B47" t="n">
-        <v>79399</v>
+        <v>8447</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5442,25 +5442,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5470,10 +5470,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>462712</v>
+        <v>462818</v>
       </c>
       <c r="R47" t="n">
-        <v>6769143</v>
+        <v>6769164</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5506,11 +5506,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5537,10 +5532,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124833451</v>
+        <v>124836527</v>
       </c>
       <c r="B48" t="n">
-        <v>8447</v>
+        <v>79399</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5549,25 +5544,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5577,10 +5572,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>462818</v>
+        <v>462712</v>
       </c>
       <c r="R48" t="n">
-        <v>6769164</v>
+        <v>6769143</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5613,6 +5608,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6684,10 +6684,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125017210</v>
+        <v>125001637</v>
       </c>
       <c r="B59" t="n">
-        <v>8447</v>
+        <v>56722</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6700,27 +6700,27 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6729,10 +6729,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>462636</v>
+        <v>462376</v>
       </c>
       <c r="R59" t="n">
-        <v>6769113</v>
+        <v>6768807</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6779,22 +6779,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125017117</v>
+        <v>125017140</v>
       </c>
       <c r="B60" t="n">
-        <v>79428</v>
+        <v>78842</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6807,21 +6807,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6831,10 +6831,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>462501</v>
+        <v>462575</v>
       </c>
       <c r="R60" t="n">
-        <v>6768895</v>
+        <v>6768972</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6893,10 +6893,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125001637</v>
+        <v>125017117</v>
       </c>
       <c r="B61" t="n">
-        <v>56722</v>
+        <v>79428</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6905,43 +6905,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>462376</v>
+        <v>462501</v>
       </c>
       <c r="R61" t="n">
-        <v>6768807</v>
+        <v>6768895</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6988,22 +6983,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125017140</v>
+        <v>125017210</v>
       </c>
       <c r="B62" t="n">
-        <v>78842</v>
+        <v>8447</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7012,38 +7007,43 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>462575</v>
+        <v>462636</v>
       </c>
       <c r="R62" t="n">
-        <v>6768972</v>
+        <v>6769113</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7209,10 +7209,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125001767</v>
+        <v>125017278</v>
       </c>
       <c r="B64" t="n">
-        <v>57529</v>
+        <v>78455</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7225,39 +7225,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Lädsån, Dlr</t>
+          <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>462346</v>
+        <v>462544</v>
       </c>
       <c r="R64" t="n">
-        <v>6768794</v>
+        <v>6768928</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7292,11 +7287,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -7309,22 +7299,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125017193</v>
+        <v>125017279</v>
       </c>
       <c r="B65" t="n">
-        <v>57529</v>
+        <v>78455</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7337,39 +7327,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>462585</v>
+        <v>462581</v>
       </c>
       <c r="R65" t="n">
-        <v>6769050</v>
+        <v>6768944</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7428,10 +7413,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125017252</v>
+        <v>125017270</v>
       </c>
       <c r="B66" t="n">
-        <v>78810</v>
+        <v>78455</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7444,21 +7429,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7468,10 +7453,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>462426</v>
+        <v>462777</v>
       </c>
       <c r="R66" t="n">
-        <v>6768812</v>
+        <v>6769237</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7530,10 +7515,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125017106</v>
+        <v>125001767</v>
       </c>
       <c r="B67" t="n">
-        <v>79428</v>
+        <v>57529</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7546,34 +7531,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Salutjärnen, Dlr</t>
+          <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>462755</v>
+        <v>462346</v>
       </c>
       <c r="R67" t="n">
-        <v>6769176</v>
+        <v>6768794</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7608,6 +7598,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -7620,22 +7615,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125017122</v>
+        <v>125017193</v>
       </c>
       <c r="B68" t="n">
-        <v>79428</v>
+        <v>57529</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7648,34 +7643,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>462688</v>
+        <v>462585</v>
       </c>
       <c r="R68" t="n">
-        <v>6769019</v>
+        <v>6769050</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7734,7 +7734,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125017259</v>
+        <v>125017252</v>
       </c>
       <c r="B69" t="n">
         <v>78810</v>
@@ -7774,10 +7774,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>462444</v>
+        <v>462426</v>
       </c>
       <c r="R69" t="n">
-        <v>6768832</v>
+        <v>6768812</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7836,10 +7836,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125017278</v>
+        <v>125017106</v>
       </c>
       <c r="B70" t="n">
-        <v>78455</v>
+        <v>79428</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7852,21 +7852,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7876,10 +7876,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>462544</v>
+        <v>462755</v>
       </c>
       <c r="R70" t="n">
-        <v>6768928</v>
+        <v>6769176</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7938,10 +7938,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125017279</v>
+        <v>125017122</v>
       </c>
       <c r="B71" t="n">
-        <v>78455</v>
+        <v>79428</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7954,21 +7954,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7978,10 +7978,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>462581</v>
+        <v>462688</v>
       </c>
       <c r="R71" t="n">
-        <v>6768944</v>
+        <v>6769019</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8040,10 +8040,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125017270</v>
+        <v>125017259</v>
       </c>
       <c r="B72" t="n">
-        <v>78455</v>
+        <v>78810</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8056,21 +8056,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8080,10 +8080,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>462777</v>
+        <v>462444</v>
       </c>
       <c r="R72" t="n">
-        <v>6769237</v>
+        <v>6768832</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9065,10 +9065,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125017219</v>
+        <v>125017263</v>
       </c>
       <c r="B82" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9077,43 +9077,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>462585</v>
+        <v>462712</v>
       </c>
       <c r="R82" t="n">
-        <v>6769050</v>
+        <v>6769149</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9172,10 +9167,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125017263</v>
+        <v>125017219</v>
       </c>
       <c r="B83" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9184,38 +9179,43 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>462712</v>
+        <v>462585</v>
       </c>
       <c r="R83" t="n">
-        <v>6769149</v>
+        <v>6769050</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11757,10 +11757,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125017254</v>
+        <v>125017227</v>
       </c>
       <c r="B108" t="n">
-        <v>78810</v>
+        <v>94959</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11769,25 +11769,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>2387</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11800,7 +11800,7 @@
         <v>462424</v>
       </c>
       <c r="R108" t="n">
-        <v>6768802</v>
+        <v>6768787</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11833,6 +11833,11 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>I kallkälla</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11859,10 +11864,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125000745</v>
+        <v>125000267</v>
       </c>
       <c r="B109" t="n">
-        <v>57513</v>
+        <v>8447</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11871,43 +11876,38 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Salutjärnen, Dlr</t>
+          <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>462414</v>
+        <v>462482</v>
       </c>
       <c r="R109" t="n">
-        <v>6768796</v>
+        <v>6768845</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11971,10 +11971,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125017202</v>
+        <v>125017254</v>
       </c>
       <c r="B110" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11987,21 +11987,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12011,10 +12011,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>462414</v>
+        <v>462424</v>
       </c>
       <c r="R110" t="n">
-        <v>6768758</v>
+        <v>6768802</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12073,10 +12073,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125017227</v>
+        <v>125000745</v>
       </c>
       <c r="B111" t="n">
-        <v>94959</v>
+        <v>57513</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12085,38 +12085,43 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>2387</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>462424</v>
+        <v>462414</v>
       </c>
       <c r="R111" t="n">
-        <v>6768787</v>
+        <v>6768796</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12153,7 +12158,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>I kallkälla</t>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12168,22 +12173,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125000267</v>
+        <v>125017202</v>
       </c>
       <c r="B112" t="n">
-        <v>8447</v>
+        <v>91299</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12192,38 +12197,38 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>106545</v>
+        <v>658</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Lädsån, Dlr</t>
+          <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>462482</v>
+        <v>462414</v>
       </c>
       <c r="R112" t="n">
-        <v>6768845</v>
+        <v>6768758</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12258,11 +12263,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
-        </is>
-      </c>
       <c r="AD112" t="b">
         <v>0</v>
       </c>
@@ -12275,12 +12275,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
@@ -12593,10 +12593,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125017212</v>
+        <v>125017123</v>
       </c>
       <c r="B116" t="n">
-        <v>8447</v>
+        <v>79428</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12605,43 +12605,38 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>462295</v>
+        <v>462680</v>
       </c>
       <c r="R116" t="n">
-        <v>6768622</v>
+        <v>6769027</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12700,7 +12695,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125017123</v>
+        <v>125017118</v>
       </c>
       <c r="B117" t="n">
         <v>79428</v>
@@ -12740,10 +12735,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>462680</v>
+        <v>462542</v>
       </c>
       <c r="R117" t="n">
-        <v>6769027</v>
+        <v>6768916</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12802,7 +12797,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125017118</v>
+        <v>125017124</v>
       </c>
       <c r="B118" t="n">
         <v>79428</v>
@@ -12842,10 +12837,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>462542</v>
+        <v>462679</v>
       </c>
       <c r="R118" t="n">
-        <v>6768916</v>
+        <v>6769045</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12904,10 +12899,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125017124</v>
+        <v>125001616</v>
       </c>
       <c r="B119" t="n">
-        <v>79428</v>
+        <v>56722</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12916,38 +12911,43 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>462679</v>
+        <v>462456</v>
       </c>
       <c r="R119" t="n">
-        <v>6769045</v>
+        <v>6768778</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12982,6 +12982,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Miljöbilder. Så kallad tjädertall</t>
+        </is>
+      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
@@ -12994,22 +12999,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125001616</v>
+        <v>125017285</v>
       </c>
       <c r="B120" t="n">
-        <v>56722</v>
+        <v>91065</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13022,39 +13027,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100138</v>
+        <v>5321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>462456</v>
+        <v>462561</v>
       </c>
       <c r="R120" t="n">
-        <v>6768778</v>
+        <v>6768949</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13091,7 +13091,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Miljöbilder. Så kallad tjädertall</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13100,18 +13100,19 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
@@ -13322,10 +13323,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125017285</v>
+        <v>125017212</v>
       </c>
       <c r="B123" t="n">
-        <v>91065</v>
+        <v>8447</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13338,34 +13339,39 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5321</v>
+        <v>106545</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>462561</v>
+        <v>462295</v>
       </c>
       <c r="R123" t="n">
-        <v>6768949</v>
+        <v>6768622</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13400,18 +13406,12 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>På asp</t>
-        </is>
-      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -13430,10 +13430,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>124999142</v>
+        <v>125017250</v>
       </c>
       <c r="B124" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13446,21 +13446,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13470,10 +13470,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>462684</v>
+        <v>462364</v>
       </c>
       <c r="R124" t="n">
-        <v>6769117</v>
+        <v>6768755</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13520,22 +13520,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125017250</v>
+        <v>124999142</v>
       </c>
       <c r="B125" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13548,21 +13548,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13572,10 +13572,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>462364</v>
+        <v>462684</v>
       </c>
       <c r="R125" t="n">
-        <v>6768755</v>
+        <v>6769117</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13622,12 +13622,12 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
@@ -14348,10 +14348,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125017155</v>
+        <v>125017125</v>
       </c>
       <c r="B133" t="n">
-        <v>96354</v>
+        <v>79428</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14364,21 +14364,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>53</v>
+        <v>6453</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14388,10 +14388,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>462427</v>
+        <v>462683</v>
       </c>
       <c r="R133" t="n">
-        <v>6768776</v>
+        <v>6769060</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14552,10 +14552,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125017125</v>
+        <v>125017155</v>
       </c>
       <c r="B135" t="n">
-        <v>79428</v>
+        <v>96354</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14568,21 +14568,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6453</v>
+        <v>53</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14592,10 +14592,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>462683</v>
+        <v>462427</v>
       </c>
       <c r="R135" t="n">
-        <v>6769060</v>
+        <v>6768776</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15286,10 +15286,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>124999177</v>
+        <v>125017256</v>
       </c>
       <c r="B142" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15302,39 +15302,34 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>462684</v>
+        <v>462409</v>
       </c>
       <c r="R142" t="n">
-        <v>6769117</v>
+        <v>6768798</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15381,22 +15376,22 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>125017205</v>
+        <v>125017266</v>
       </c>
       <c r="B143" t="n">
-        <v>8447</v>
+        <v>92293</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15409,27 +15404,31 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
@@ -15438,10 +15437,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>462864</v>
+        <v>462462</v>
       </c>
       <c r="R143" t="n">
-        <v>6769317</v>
+        <v>6768863</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15500,10 +15499,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>125017266</v>
+        <v>125017190</v>
       </c>
       <c r="B144" t="n">
-        <v>92293</v>
+        <v>57529</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15512,35 +15511,31 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
@@ -15549,10 +15544,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>462462</v>
+        <v>462791</v>
       </c>
       <c r="R144" t="n">
-        <v>6768863</v>
+        <v>6769257</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15611,7 +15606,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>125017190</v>
+        <v>125000666</v>
       </c>
       <c r="B145" t="n">
         <v>57529</v>
@@ -15656,10 +15651,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>462791</v>
+        <v>462422</v>
       </c>
       <c r="R145" t="n">
-        <v>6769257</v>
+        <v>6768811</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15706,19 +15701,19 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>125000666</v>
+        <v>124999177</v>
       </c>
       <c r="B146" t="n">
         <v>57529</v>
@@ -15763,10 +15758,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>462422</v>
+        <v>462684</v>
       </c>
       <c r="R146" t="n">
-        <v>6768811</v>
+        <v>6769117</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15825,10 +15820,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125017256</v>
+        <v>125017205</v>
       </c>
       <c r="B147" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15837,38 +15832,43 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>462409</v>
+        <v>462864</v>
       </c>
       <c r="R147" t="n">
-        <v>6768798</v>
+        <v>6769317</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>

--- a/artfynd/A 18527-2025 artfynd.xlsx
+++ b/artfynd/A 18527-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124773032</v>
+        <v>124782138</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>462235</v>
+        <v>462447</v>
       </c>
       <c r="R2" t="n">
-        <v>6768533</v>
+        <v>6768805</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124782138</v>
+        <v>124782461</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,38 +789,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>462447</v>
+        <v>462374</v>
       </c>
       <c r="R3" t="n">
-        <v>6768805</v>
+        <v>6768823</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124777598</v>
+        <v>124771314</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,37 +900,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462331</v>
+        <v>462210</v>
       </c>
       <c r="R4" t="n">
-        <v>6768680</v>
+        <v>6768591</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124782461</v>
+        <v>124774494</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
+        <v>8447</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,39 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462374</v>
+        <v>462257</v>
       </c>
       <c r="R5" t="n">
-        <v>6768823</v>
+        <v>6768691</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124771314</v>
+        <v>124777598</v>
       </c>
       <c r="B6" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,42 +1109,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>462210</v>
+        <v>462331</v>
       </c>
       <c r="R6" t="n">
-        <v>6768591</v>
+        <v>6768680</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1200,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124774494</v>
+        <v>124773032</v>
       </c>
       <c r="B7" t="n">
-        <v>8447</v>
+        <v>57529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,38 +1207,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>462257</v>
+        <v>462235</v>
       </c>
       <c r="R7" t="n">
-        <v>6768691</v>
+        <v>6768533</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1832,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124771180</v>
+        <v>124777762</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1848,34 +1848,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>462198</v>
+        <v>462331</v>
       </c>
       <c r="R13" t="n">
-        <v>6768579</v>
+        <v>6768680</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,6 +1913,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Miljöbilder på bland annat angränsande hygge.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1934,7 +1944,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124782169</v>
+        <v>124771180</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -1974,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>462456</v>
+        <v>462198</v>
       </c>
       <c r="R14" t="n">
-        <v>6768800</v>
+        <v>6768579</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2036,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124777762</v>
+        <v>124782169</v>
       </c>
       <c r="B15" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2052,39 +2062,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>462331</v>
+        <v>462456</v>
       </c>
       <c r="R15" t="n">
-        <v>6768680</v>
+        <v>6768800</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2117,11 +2122,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Miljöbilder på bland annat angränsande hygge.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -6057,10 +6057,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125017253</v>
+        <v>125017241</v>
       </c>
       <c r="B53" t="n">
-        <v>78810</v>
+        <v>91026</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6073,21 +6073,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6097,10 +6097,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>462425</v>
+        <v>462418</v>
       </c>
       <c r="R53" t="n">
-        <v>6768806</v>
+        <v>6768776</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6669,10 +6669,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125017241</v>
+        <v>125017253</v>
       </c>
       <c r="B59" t="n">
-        <v>91026</v>
+        <v>78810</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6685,21 +6685,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6709,10 +6709,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>462418</v>
+        <v>462425</v>
       </c>
       <c r="R59" t="n">
-        <v>6768776</v>
+        <v>6768806</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8151,10 +8151,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125017113</v>
+        <v>125017280</v>
       </c>
       <c r="B73" t="n">
-        <v>79428</v>
+        <v>96227</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8163,25 +8163,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>2869</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8191,10 +8191,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>462356</v>
+        <v>462403</v>
       </c>
       <c r="R73" t="n">
-        <v>6768753</v>
+        <v>6768799</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8253,7 +8253,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125001145</v>
+        <v>125017113</v>
       </c>
       <c r="B74" t="n">
         <v>79428</v>
@@ -8293,10 +8293,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>462456</v>
+        <v>462356</v>
       </c>
       <c r="R74" t="n">
-        <v>6768778</v>
+        <v>6768753</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8331,11 +8331,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -8348,22 +8343,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125000794</v>
+        <v>125001145</v>
       </c>
       <c r="B75" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8376,21 +8371,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8400,10 +8395,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>462420</v>
+        <v>462456</v>
       </c>
       <c r="R75" t="n">
-        <v>6768785</v>
+        <v>6768778</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8467,10 +8462,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125017280</v>
+        <v>125000794</v>
       </c>
       <c r="B76" t="n">
-        <v>96227</v>
+        <v>78810</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8479,25 +8474,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8507,10 +8502,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>462403</v>
+        <v>462420</v>
       </c>
       <c r="R76" t="n">
-        <v>6768799</v>
+        <v>6768785</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8545,6 +8540,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -8557,12 +8557,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -11067,10 +11067,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125017136</v>
+        <v>125017157</v>
       </c>
       <c r="B101" t="n">
-        <v>78842</v>
+        <v>90977</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11079,25 +11079,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11107,10 +11107,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>462449</v>
+        <v>462431</v>
       </c>
       <c r="R101" t="n">
-        <v>6768898</v>
+        <v>6768769</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11169,10 +11169,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125017157</v>
+        <v>125017136</v>
       </c>
       <c r="B102" t="n">
-        <v>90977</v>
+        <v>78842</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11181,25 +11181,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11209,10 +11209,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>462431</v>
+        <v>462449</v>
       </c>
       <c r="R102" t="n">
-        <v>6768769</v>
+        <v>6768898</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11271,10 +11271,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125017228</v>
+        <v>124999177</v>
       </c>
       <c r="B103" t="n">
-        <v>94766</v>
+        <v>57529</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11283,38 +11283,43 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2412</v>
+        <v>100049</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Philonotis fontana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>462418</v>
+        <v>462684</v>
       </c>
       <c r="R103" t="n">
-        <v>6768790</v>
+        <v>6769117</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11349,11 +11354,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>I kallkälla</t>
-        </is>
-      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
@@ -11366,22 +11366,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125017251</v>
+        <v>125017228</v>
       </c>
       <c r="B104" t="n">
-        <v>78810</v>
+        <v>94766</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11390,25 +11390,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>2412</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Philonotis fontana</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11418,10 +11418,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>462357</v>
+        <v>462418</v>
       </c>
       <c r="R104" t="n">
-        <v>6768775</v>
+        <v>6768790</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11454,6 +11454,11 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>I kallkälla</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11480,7 +11485,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125017250</v>
+        <v>125017251</v>
       </c>
       <c r="B105" t="n">
         <v>78810</v>
@@ -11520,10 +11525,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>462364</v>
+        <v>462357</v>
       </c>
       <c r="R105" t="n">
-        <v>6768755</v>
+        <v>6768775</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11582,7 +11587,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125017257</v>
+        <v>125017250</v>
       </c>
       <c r="B106" t="n">
         <v>78810</v>
@@ -11622,10 +11627,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>462417</v>
+        <v>462364</v>
       </c>
       <c r="R106" t="n">
-        <v>6768771</v>
+        <v>6768755</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11684,10 +11689,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124999142</v>
+        <v>125017257</v>
       </c>
       <c r="B107" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11700,21 +11705,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11724,10 +11729,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>462684</v>
+        <v>462417</v>
       </c>
       <c r="R107" t="n">
-        <v>6769117</v>
+        <v>6768771</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11774,19 +11779,19 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124999177</v>
+        <v>125004378</v>
       </c>
       <c r="B108" t="n">
         <v>57529</v>
@@ -11827,14 +11832,14 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Salutjärnen, Dlr</t>
+          <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>462684</v>
+        <v>462261</v>
       </c>
       <c r="R108" t="n">
-        <v>6769117</v>
+        <v>6768593</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11867,6 +11872,11 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11893,10 +11903,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125004378</v>
+        <v>124999142</v>
       </c>
       <c r="B109" t="n">
-        <v>57529</v>
+        <v>78842</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11909,39 +11919,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Lädsån, Dlr</t>
+          <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>462261</v>
+        <v>462684</v>
       </c>
       <c r="R109" t="n">
-        <v>6768593</v>
+        <v>6769117</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11974,11 +11979,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-05-12</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12005,10 +12005,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125017224</v>
+        <v>125017227</v>
       </c>
       <c r="B110" t="n">
-        <v>78547</v>
+        <v>94959</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12017,25 +12017,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>228912</v>
+        <v>2387</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12045,10 +12045,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>462683</v>
+        <v>462424</v>
       </c>
       <c r="R110" t="n">
-        <v>6769060</v>
+        <v>6768787</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12081,6 +12081,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>I kallkälla</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12107,10 +12112,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125017225</v>
+        <v>125017224</v>
       </c>
       <c r="B111" t="n">
-        <v>8447</v>
+        <v>78547</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12119,43 +12124,38 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>462449</v>
+        <v>462683</v>
       </c>
       <c r="R111" t="n">
-        <v>6768765</v>
+        <v>6769060</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12418,10 +12418,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125017227</v>
+        <v>125017188</v>
       </c>
       <c r="B114" t="n">
-        <v>94959</v>
+        <v>57529</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12430,38 +12430,43 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2387</v>
+        <v>100049</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>462424</v>
+        <v>462760</v>
       </c>
       <c r="R114" t="n">
-        <v>6768787</v>
+        <v>6769122</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12494,11 +12499,6 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-05-12</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>I kallkälla</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12525,10 +12525,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125017188</v>
+        <v>125017225</v>
       </c>
       <c r="B115" t="n">
-        <v>57529</v>
+        <v>8447</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12537,31 +12537,31 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -12570,10 +12570,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>462760</v>
+        <v>462449</v>
       </c>
       <c r="R115" t="n">
-        <v>6769122</v>
+        <v>6768765</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12632,10 +12632,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125017190</v>
+        <v>125017232</v>
       </c>
       <c r="B116" t="n">
-        <v>57529</v>
+        <v>80763</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12648,39 +12648,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>462791</v>
+        <v>462456</v>
       </c>
       <c r="R116" t="n">
-        <v>6769257</v>
+        <v>6768781</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12739,10 +12734,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125017232</v>
+        <v>125017273</v>
       </c>
       <c r="B117" t="n">
-        <v>80763</v>
+        <v>78455</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12755,21 +12750,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1049</v>
+        <v>353</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12779,10 +12774,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>462456</v>
+        <v>462642</v>
       </c>
       <c r="R117" t="n">
-        <v>6768781</v>
+        <v>6769092</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12841,7 +12836,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125017273</v>
+        <v>125017278</v>
       </c>
       <c r="B118" t="n">
         <v>78455</v>
@@ -12881,10 +12876,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>462642</v>
+        <v>462544</v>
       </c>
       <c r="R118" t="n">
-        <v>6769092</v>
+        <v>6768928</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12943,10 +12938,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125017278</v>
+        <v>125017237</v>
       </c>
       <c r="B119" t="n">
-        <v>78455</v>
+        <v>78546</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12959,21 +12954,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12983,10 +12978,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>462544</v>
+        <v>462684</v>
       </c>
       <c r="R119" t="n">
-        <v>6768928</v>
+        <v>6769060</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13045,10 +13040,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125017237</v>
+        <v>125017247</v>
       </c>
       <c r="B120" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13061,21 +13056,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13085,10 +13080,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>462684</v>
+        <v>462756</v>
       </c>
       <c r="R120" t="n">
-        <v>6769060</v>
+        <v>6769225</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13147,7 +13142,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125017247</v>
+        <v>125000045</v>
       </c>
       <c r="B121" t="n">
         <v>78810</v>
@@ -13183,14 +13178,14 @@
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Salutjärnen, Dlr</t>
+          <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>462756</v>
+        <v>462482</v>
       </c>
       <c r="R121" t="n">
-        <v>6769225</v>
+        <v>6768845</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13237,22 +13232,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125000045</v>
+        <v>125017190</v>
       </c>
       <c r="B122" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13265,34 +13260,39 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Lädsån, Dlr</t>
+          <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>462482</v>
+        <v>462791</v>
       </c>
       <c r="R122" t="n">
-        <v>6768845</v>
+        <v>6769257</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13339,12 +13339,12 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
@@ -16466,10 +16466,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>125017112</v>
+        <v>125017155</v>
       </c>
       <c r="B153" t="n">
-        <v>79428</v>
+        <v>96354</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16482,21 +16482,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6453</v>
+        <v>53</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16506,10 +16506,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>462453</v>
+        <v>462427</v>
       </c>
       <c r="R153" t="n">
-        <v>6768876</v>
+        <v>6768776</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16568,10 +16568,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>125017124</v>
+        <v>125017142</v>
       </c>
       <c r="B154" t="n">
-        <v>79428</v>
+        <v>78842</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16584,21 +16584,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16608,10 +16608,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>462679</v>
+        <v>462682</v>
       </c>
       <c r="R154" t="n">
-        <v>6769045</v>
+        <v>6769024</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16670,10 +16670,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>125017155</v>
+        <v>125017112</v>
       </c>
       <c r="B155" t="n">
-        <v>96354</v>
+        <v>79428</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16686,21 +16686,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>53</v>
+        <v>6453</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16710,10 +16710,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>462427</v>
+        <v>462453</v>
       </c>
       <c r="R155" t="n">
-        <v>6768776</v>
+        <v>6768876</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16772,10 +16772,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>125017142</v>
+        <v>125017124</v>
       </c>
       <c r="B156" t="n">
-        <v>78842</v>
+        <v>79428</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16788,21 +16788,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16812,10 +16812,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>462682</v>
+        <v>462679</v>
       </c>
       <c r="R156" t="n">
-        <v>6769024</v>
+        <v>6769045</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16874,10 +16874,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>125017199</v>
+        <v>125000267</v>
       </c>
       <c r="B157" t="n">
-        <v>96345</v>
+        <v>8447</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16886,38 +16886,38 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>54</v>
+        <v>106545</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Skogstrappmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Anastrophyllum michauxii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(F.Weber.) H.Buch</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Salutjärnen, Dlr</t>
+          <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>462249</v>
+        <v>462482</v>
       </c>
       <c r="R157" t="n">
-        <v>6768580</v>
+        <v>6768845</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16952,35 +16952,39 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
+        </is>
+      </c>
       <c r="AD157" t="b">
         <v>0</v>
       </c>
       <c r="AE157" t="b">
         <v>0</v>
       </c>
-      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>125017266</v>
+        <v>125017207</v>
       </c>
       <c r="B158" t="n">
-        <v>92293</v>
+        <v>8447</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16993,31 +16997,27 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
@@ -17026,10 +17026,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>462462</v>
+        <v>462840</v>
       </c>
       <c r="R158" t="n">
-        <v>6768863</v>
+        <v>6769309</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17190,10 +17190,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>125017246</v>
+        <v>125017175</v>
       </c>
       <c r="B160" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17202,38 +17202,43 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P160" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>462868</v>
+        <v>462419</v>
       </c>
       <c r="R160" t="n">
-        <v>6769325</v>
+        <v>6768798</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17292,10 +17297,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>125017175</v>
+        <v>125017198</v>
       </c>
       <c r="B161" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17304,31 +17309,31 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="M161" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
@@ -17337,10 +17342,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>462419</v>
+        <v>462452</v>
       </c>
       <c r="R161" t="n">
-        <v>6768798</v>
+        <v>6768897</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17399,10 +17404,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>125017198</v>
+        <v>125017199</v>
       </c>
       <c r="B162" t="n">
-        <v>57529</v>
+        <v>96345</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17415,39 +17420,34 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>100049</v>
+        <v>54</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogstrappmossa</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Anastrophyllum michauxii</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(F.Weber.) H.Buch</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P162" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>462452</v>
+        <v>462249</v>
       </c>
       <c r="R162" t="n">
-        <v>6768897</v>
+        <v>6768580</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17488,6 +17488,7 @@
       <c r="AE162" t="b">
         <v>0</v>
       </c>
+      <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="b">
         <v>0</v>
       </c>
@@ -17506,10 +17507,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>125000267</v>
+        <v>125017266</v>
       </c>
       <c r="B163" t="n">
-        <v>8447</v>
+        <v>92293</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17522,34 +17523,43 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Lädsån, Dlr</t>
+          <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>462482</v>
+        <v>462462</v>
       </c>
       <c r="R163" t="n">
-        <v>6768845</v>
+        <v>6768863</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17584,11 +17594,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
-        </is>
-      </c>
       <c r="AD163" t="b">
         <v>0</v>
       </c>
@@ -17601,22 +17606,22 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>125017207</v>
+        <v>125017246</v>
       </c>
       <c r="B164" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17625,43 +17630,38 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
-      <c r="M164" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P164" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>462840</v>
+        <v>462868</v>
       </c>
       <c r="R164" t="n">
-        <v>6769309</v>
+        <v>6769325</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18536,10 +18536,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>125300490</v>
+        <v>125302464</v>
       </c>
       <c r="B173" t="n">
-        <v>82597</v>
+        <v>74901</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -18552,21 +18552,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18576,10 +18576,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>462425</v>
+        <v>462289</v>
       </c>
       <c r="R173" t="n">
-        <v>6768760</v>
+        <v>6768660</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18638,10 +18638,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>125299865</v>
+        <v>125302321</v>
       </c>
       <c r="B174" t="n">
-        <v>56722</v>
+        <v>74901</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -18650,43 +18650,38 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>100138</v>
+        <v>6440</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
-      <c r="M174" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Salutjärnen, Dlr</t>
+          <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>462462</v>
+        <v>462310</v>
       </c>
       <c r="R174" t="n">
-        <v>6768859</v>
+        <v>6768674</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18745,10 +18740,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>125302464</v>
+        <v>125300490</v>
       </c>
       <c r="B175" t="n">
-        <v>74901</v>
+        <v>82597</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -18761,21 +18756,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18785,10 +18780,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>462289</v>
+        <v>462425</v>
       </c>
       <c r="R175" t="n">
-        <v>6768660</v>
+        <v>6768760</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18847,10 +18842,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>125302321</v>
+        <v>125299865</v>
       </c>
       <c r="B176" t="n">
-        <v>74901</v>
+        <v>56722</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -18859,38 +18854,43 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6440</v>
+        <v>100138</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Lädsån, Dlr</t>
+          <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>462310</v>
+        <v>462462</v>
       </c>
       <c r="R176" t="n">
-        <v>6768674</v>
+        <v>6768859</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -20173,10 +20173,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>125300260</v>
+        <v>125303298</v>
       </c>
       <c r="B189" t="n">
-        <v>96227</v>
+        <v>74901</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -20185,25 +20185,25 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>2869</v>
+        <v>6440</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -20213,10 +20213,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>462418</v>
+        <v>462263</v>
       </c>
       <c r="R189" t="n">
-        <v>6768801</v>
+        <v>6768595</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20275,10 +20275,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>125299647</v>
+        <v>125300260</v>
       </c>
       <c r="B190" t="n">
-        <v>78810</v>
+        <v>96227</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -20287,38 +20287,38 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Salutjärnen, Dlr</t>
+          <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>462563</v>
+        <v>462418</v>
       </c>
       <c r="R190" t="n">
-        <v>6768994</v>
+        <v>6768801</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20377,10 +20377,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>125303298</v>
+        <v>125299647</v>
       </c>
       <c r="B191" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -20393,34 +20393,34 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Lädsån, Dlr</t>
+          <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>462263</v>
+        <v>462563</v>
       </c>
       <c r="R191" t="n">
-        <v>6768595</v>
+        <v>6768994</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>

--- a/artfynd/A 18527-2025 artfynd.xlsx
+++ b/artfynd/A 18527-2025 artfynd.xlsx
@@ -6576,10 +6576,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125017268</v>
+        <v>125017219</v>
       </c>
       <c r="B58" t="n">
-        <v>92293</v>
+        <v>8447</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6592,31 +6592,27 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -6625,10 +6621,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>462470</v>
+        <v>462585</v>
       </c>
       <c r="R58" t="n">
-        <v>6768894</v>
+        <v>6769050</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6687,10 +6683,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125017236</v>
+        <v>124999142</v>
       </c>
       <c r="B59" t="n">
-        <v>78546</v>
+        <v>78842</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6703,21 +6699,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6727,10 +6723,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>462688</v>
+        <v>462684</v>
       </c>
       <c r="R59" t="n">
-        <v>6769019</v>
+        <v>6769117</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6777,22 +6773,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125017106</v>
+        <v>125017268</v>
       </c>
       <c r="B60" t="n">
-        <v>79428</v>
+        <v>92293</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6801,38 +6797,47 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>462755</v>
+        <v>462470</v>
       </c>
       <c r="R60" t="n">
-        <v>6769176</v>
+        <v>6768894</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6891,10 +6896,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125017118</v>
+        <v>125017142</v>
       </c>
       <c r="B61" t="n">
-        <v>79428</v>
+        <v>78842</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6907,21 +6912,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6931,10 +6936,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>462542</v>
+        <v>462682</v>
       </c>
       <c r="R61" t="n">
-        <v>6768916</v>
+        <v>6769024</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6993,10 +6998,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125017142</v>
+        <v>125017236</v>
       </c>
       <c r="B62" t="n">
-        <v>78842</v>
+        <v>78546</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7009,21 +7014,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7033,10 +7038,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>462682</v>
+        <v>462688</v>
       </c>
       <c r="R62" t="n">
-        <v>6769024</v>
+        <v>6769019</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7095,7 +7100,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125017125</v>
+        <v>125017106</v>
       </c>
       <c r="B63" t="n">
         <v>79428</v>
@@ -7135,10 +7140,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>462683</v>
+        <v>462755</v>
       </c>
       <c r="R63" t="n">
-        <v>6769060</v>
+        <v>6769176</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7197,10 +7202,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125017262</v>
+        <v>125017125</v>
       </c>
       <c r="B64" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7213,21 +7218,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7237,10 +7242,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>462703</v>
+        <v>462683</v>
       </c>
       <c r="R64" t="n">
-        <v>6769146</v>
+        <v>6769060</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7299,10 +7304,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125017219</v>
+        <v>125017118</v>
       </c>
       <c r="B65" t="n">
-        <v>8447</v>
+        <v>79428</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7311,43 +7316,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>462585</v>
+        <v>462542</v>
       </c>
       <c r="R65" t="n">
-        <v>6769050</v>
+        <v>6768916</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7406,10 +7406,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124999142</v>
+        <v>125017262</v>
       </c>
       <c r="B66" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7422,21 +7422,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7446,10 +7446,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>462684</v>
+        <v>462703</v>
       </c>
       <c r="R66" t="n">
-        <v>6769117</v>
+        <v>6769146</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7496,12 +7496,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -10313,10 +10313,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124999027</v>
+        <v>125017122</v>
       </c>
       <c r="B94" t="n">
-        <v>57529</v>
+        <v>79428</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10329,21 +10329,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10353,10 +10353,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>462741</v>
+        <v>462688</v>
       </c>
       <c r="R94" t="n">
-        <v>6769142</v>
+        <v>6769019</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10391,11 +10391,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Miljöbilder. Sannoligt bohål/hackhål efter spillkråka.</t>
-        </is>
-      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
@@ -10408,19 +10403,19 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124999088</v>
+        <v>124999027</v>
       </c>
       <c r="B95" t="n">
         <v>57529</v>
@@ -10460,10 +10455,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>462698</v>
+        <v>462741</v>
       </c>
       <c r="R95" t="n">
-        <v>6769146</v>
+        <v>6769142</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10500,7 +10495,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Miljöbilder. Sannoligt spillkråka, hackhål/bohål.</t>
+          <t>Miljöbilder. Sannoligt bohål/hackhål efter spillkråka.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10527,10 +10522,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125017122</v>
+        <v>124999088</v>
       </c>
       <c r="B96" t="n">
-        <v>79428</v>
+        <v>57529</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10543,21 +10538,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10567,10 +10562,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>462688</v>
+        <v>462698</v>
       </c>
       <c r="R96" t="n">
-        <v>6769019</v>
+        <v>6769146</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10605,6 +10600,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Miljöbilder. Sannoligt spillkråka, hackhål/bohål.</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
@@ -10617,22 +10617,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125017282</v>
+        <v>125007547</v>
       </c>
       <c r="B97" t="n">
-        <v>78194</v>
+        <v>79428</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10645,21 +10645,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10669,10 +10669,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>462759</v>
+        <v>462441</v>
       </c>
       <c r="R97" t="n">
-        <v>6769121</v>
+        <v>6768886</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10707,6 +10707,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
@@ -10719,22 +10724,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125007547</v>
+        <v>125017251</v>
       </c>
       <c r="B98" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10747,21 +10752,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10771,10 +10776,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>462441</v>
+        <v>462357</v>
       </c>
       <c r="R98" t="n">
-        <v>6768886</v>
+        <v>6768775</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10809,11 +10814,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
@@ -10826,22 +10826,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125017251</v>
+        <v>125017157</v>
       </c>
       <c r="B99" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10850,25 +10850,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10878,10 +10878,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>462357</v>
+        <v>462431</v>
       </c>
       <c r="R99" t="n">
-        <v>6768775</v>
+        <v>6768769</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10940,10 +10940,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125017157</v>
+        <v>125017261</v>
       </c>
       <c r="B100" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10952,25 +10952,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10980,10 +10980,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>462431</v>
+        <v>462696</v>
       </c>
       <c r="R100" t="n">
-        <v>6768769</v>
+        <v>6769144</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11042,10 +11042,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125017261</v>
+        <v>125000074</v>
       </c>
       <c r="B101" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11058,34 +11058,39 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Salutjärnen, Dlr</t>
+          <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>462696</v>
+        <v>462482</v>
       </c>
       <c r="R101" t="n">
-        <v>6769144</v>
+        <v>6768845</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11132,22 +11137,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125000074</v>
+        <v>125017207</v>
       </c>
       <c r="B102" t="n">
-        <v>57529</v>
+        <v>8447</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11156,43 +11161,43 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Lädsån, Dlr</t>
+          <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>462482</v>
+        <v>462840</v>
       </c>
       <c r="R102" t="n">
-        <v>6768845</v>
+        <v>6769309</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11239,19 +11244,19 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125017207</v>
+        <v>125017209</v>
       </c>
       <c r="B103" t="n">
         <v>8447</v>
@@ -11296,10 +11301,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>462840</v>
+        <v>462777</v>
       </c>
       <c r="R103" t="n">
-        <v>6769309</v>
+        <v>6769237</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11358,10 +11363,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125017209</v>
+        <v>125017282</v>
       </c>
       <c r="B104" t="n">
-        <v>8447</v>
+        <v>78194</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11370,43 +11375,38 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>106545</v>
+        <v>6437</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>462777</v>
+        <v>462759</v>
       </c>
       <c r="R104" t="n">
-        <v>6769237</v>
+        <v>6769121</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11567,10 +11567,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125007648</v>
+        <v>125017255</v>
       </c>
       <c r="B106" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11583,21 +11583,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11607,10 +11607,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>462431</v>
+        <v>462419</v>
       </c>
       <c r="R106" t="n">
-        <v>6768885</v>
+        <v>6768798</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11645,11 +11645,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
@@ -11662,22 +11657,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125017255</v>
+        <v>125007648</v>
       </c>
       <c r="B107" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11690,21 +11685,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11714,10 +11709,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>462419</v>
+        <v>462431</v>
       </c>
       <c r="R107" t="n">
-        <v>6768798</v>
+        <v>6768885</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11752,6 +11747,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
@@ -11764,12 +11764,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
@@ -13335,10 +13335,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125001767</v>
+        <v>125017279</v>
       </c>
       <c r="B123" t="n">
-        <v>57529</v>
+        <v>78455</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13351,39 +13351,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Lädsån, Dlr</t>
+          <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>462346</v>
+        <v>462581</v>
       </c>
       <c r="R123" t="n">
-        <v>6768794</v>
+        <v>6768944</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13418,11 +13413,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
@@ -13435,19 +13425,19 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125001339</v>
+        <v>125001767</v>
       </c>
       <c r="B124" t="n">
         <v>57529</v>
@@ -13488,14 +13478,14 @@
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Salutjärnen, Dlr</t>
+          <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>462456</v>
+        <v>462346</v>
       </c>
       <c r="R124" t="n">
-        <v>6768778</v>
+        <v>6768794</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13559,10 +13549,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125017279</v>
+        <v>125001339</v>
       </c>
       <c r="B125" t="n">
-        <v>78455</v>
+        <v>57529</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13575,34 +13565,39 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>353</v>
+        <v>100049</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>462581</v>
+        <v>462456</v>
       </c>
       <c r="R125" t="n">
-        <v>6768944</v>
+        <v>6768778</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13637,6 +13632,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD125" t="b">
         <v>0</v>
       </c>
@@ -13649,12 +13649,12 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
@@ -16169,10 +16169,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125017238</v>
+        <v>125017166</v>
       </c>
       <c r="B150" t="n">
-        <v>78546</v>
+        <v>91361</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16181,25 +16181,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6446</v>
+        <v>2062</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16209,10 +16209,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>462685</v>
+        <v>462312</v>
       </c>
       <c r="R150" t="n">
-        <v>6769071</v>
+        <v>6768750</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16271,10 +16271,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>125017166</v>
+        <v>125017136</v>
       </c>
       <c r="B151" t="n">
-        <v>91361</v>
+        <v>78842</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16283,25 +16283,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>2062</v>
+        <v>185</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16311,10 +16311,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>462312</v>
+        <v>462449</v>
       </c>
       <c r="R151" t="n">
-        <v>6768750</v>
+        <v>6768898</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16373,7 +16373,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>125017136</v>
+        <v>125017138</v>
       </c>
       <c r="B152" t="n">
         <v>78842</v>
@@ -16413,10 +16413,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>462449</v>
+        <v>462516</v>
       </c>
       <c r="R152" t="n">
-        <v>6768898</v>
+        <v>6768902</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16475,10 +16475,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>125017138</v>
+        <v>125017238</v>
       </c>
       <c r="B153" t="n">
-        <v>78842</v>
+        <v>78546</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16491,21 +16491,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16515,10 +16515,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>462516</v>
+        <v>462685</v>
       </c>
       <c r="R153" t="n">
-        <v>6768902</v>
+        <v>6769071</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>

--- a/artfynd/A 18527-2025 artfynd.xlsx
+++ b/artfynd/A 18527-2025 artfynd.xlsx
@@ -1613,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124774056</v>
+        <v>124776266</v>
       </c>
       <c r="B11" t="n">
-        <v>78947</v>
+        <v>57632</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1629,34 +1629,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>462291</v>
+        <v>462311</v>
       </c>
       <c r="R11" t="n">
-        <v>6768602</v>
+        <v>6768690</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124776266</v>
+        <v>124774056</v>
       </c>
       <c r="B12" t="n">
-        <v>57632</v>
+        <v>78947</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1731,39 +1736,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>462311</v>
+        <v>462291</v>
       </c>
       <c r="R12" t="n">
-        <v>6768690</v>
+        <v>6768602</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -5746,10 +5746,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125017220</v>
+        <v>125017266</v>
       </c>
       <c r="B50" t="n">
-        <v>8447</v>
+        <v>92448</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5762,27 +5762,31 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5791,10 +5795,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>462472</v>
+        <v>462462</v>
       </c>
       <c r="R50" t="n">
-        <v>6768856</v>
+        <v>6768863</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5853,10 +5857,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125017266</v>
+        <v>125017128</v>
       </c>
       <c r="B51" t="n">
-        <v>92448</v>
+        <v>79565</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5865,47 +5869,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>462462</v>
+        <v>462680</v>
       </c>
       <c r="R51" t="n">
-        <v>6768863</v>
+        <v>6769078</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5964,7 +5959,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125017128</v>
+        <v>125017108</v>
       </c>
       <c r="B52" t="n">
         <v>79565</v>
@@ -6004,10 +5999,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>462680</v>
+        <v>462569</v>
       </c>
       <c r="R52" t="n">
-        <v>6769078</v>
+        <v>6769031</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6066,10 +6061,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125017108</v>
+        <v>125017220</v>
       </c>
       <c r="B53" t="n">
-        <v>79565</v>
+        <v>8447</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6078,38 +6073,43 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>462569</v>
+        <v>462472</v>
       </c>
       <c r="R53" t="n">
-        <v>6769031</v>
+        <v>6768856</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -10206,10 +10206,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125017252</v>
+        <v>125017280</v>
       </c>
       <c r="B93" t="n">
-        <v>78947</v>
+        <v>96395</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10218,25 +10218,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10246,10 +10246,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>462426</v>
+        <v>462403</v>
       </c>
       <c r="R93" t="n">
-        <v>6768812</v>
+        <v>6768799</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10308,10 +10308,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125008171</v>
+        <v>125017227</v>
       </c>
       <c r="B94" t="n">
-        <v>79565</v>
+        <v>95127</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10320,38 +10320,38 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>2387</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Lädsån, Dlr</t>
+          <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>462456</v>
+        <v>462424</v>
       </c>
       <c r="R94" t="n">
-        <v>6768884</v>
+        <v>6768787</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10388,7 +10388,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Miljöbilder</t>
+          <t>I kallkälla</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10403,22 +10403,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125007648</v>
+        <v>125017252</v>
       </c>
       <c r="B95" t="n">
-        <v>79565</v>
+        <v>78947</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10431,21 +10431,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10455,10 +10455,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>462431</v>
+        <v>462426</v>
       </c>
       <c r="R95" t="n">
-        <v>6768885</v>
+        <v>6768812</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10493,11 +10493,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
@@ -10510,22 +10505,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125000745</v>
+        <v>125008171</v>
       </c>
       <c r="B96" t="n">
-        <v>57635</v>
+        <v>79565</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10538,39 +10533,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Salutjärnen, Dlr</t>
+          <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>462414</v>
+        <v>462456</v>
       </c>
       <c r="R96" t="n">
-        <v>6768796</v>
+        <v>6768884</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10634,10 +10624,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125017280</v>
+        <v>125007648</v>
       </c>
       <c r="B97" t="n">
-        <v>96395</v>
+        <v>79565</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10646,25 +10636,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2869</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10674,10 +10664,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>462403</v>
+        <v>462431</v>
       </c>
       <c r="R97" t="n">
-        <v>6768799</v>
+        <v>6768885</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10712,6 +10702,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
@@ -10724,22 +10719,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125017227</v>
+        <v>125000745</v>
       </c>
       <c r="B98" t="n">
-        <v>95127</v>
+        <v>57635</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10748,38 +10743,43 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2387</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>462424</v>
+        <v>462414</v>
       </c>
       <c r="R98" t="n">
-        <v>6768787</v>
+        <v>6768796</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10816,7 +10816,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>I kallkälla</t>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10831,12 +10831,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -12301,10 +12301,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125017202</v>
+        <v>125017234</v>
       </c>
       <c r="B113" t="n">
-        <v>91459</v>
+        <v>78683</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12317,21 +12317,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12341,10 +12341,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>462414</v>
+        <v>462501</v>
       </c>
       <c r="R113" t="n">
-        <v>6768758</v>
+        <v>6768890</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12403,10 +12403,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125017138</v>
+        <v>125017190</v>
       </c>
       <c r="B114" t="n">
-        <v>78979</v>
+        <v>57632</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12419,34 +12419,39 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>462516</v>
+        <v>462791</v>
       </c>
       <c r="R114" t="n">
-        <v>6768902</v>
+        <v>6769257</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12505,10 +12510,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125017234</v>
+        <v>125017202</v>
       </c>
       <c r="B115" t="n">
-        <v>78683</v>
+        <v>91459</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12521,21 +12526,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12545,10 +12550,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>462501</v>
+        <v>462414</v>
       </c>
       <c r="R115" t="n">
-        <v>6768890</v>
+        <v>6768758</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12607,10 +12612,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125017247</v>
+        <v>125017138</v>
       </c>
       <c r="B116" t="n">
-        <v>78947</v>
+        <v>78979</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12623,21 +12628,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12647,10 +12652,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>462756</v>
+        <v>462516</v>
       </c>
       <c r="R116" t="n">
-        <v>6769225</v>
+        <v>6768902</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12709,7 +12714,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125017261</v>
+        <v>125017247</v>
       </c>
       <c r="B117" t="n">
         <v>78947</v>
@@ -12749,10 +12754,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>462696</v>
+        <v>462756</v>
       </c>
       <c r="R117" t="n">
-        <v>6769144</v>
+        <v>6769225</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12811,10 +12816,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125017190</v>
+        <v>125017261</v>
       </c>
       <c r="B118" t="n">
-        <v>57632</v>
+        <v>78947</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12827,39 +12832,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>462791</v>
+        <v>462696</v>
       </c>
       <c r="R118" t="n">
-        <v>6769257</v>
+        <v>6769144</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12918,10 +12918,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125017114</v>
+        <v>125017198</v>
       </c>
       <c r="B119" t="n">
-        <v>79565</v>
+        <v>57632</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12934,34 +12934,39 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>462451</v>
+        <v>462452</v>
       </c>
       <c r="R119" t="n">
-        <v>6768820</v>
+        <v>6768897</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13020,10 +13025,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125017124</v>
+        <v>125017173</v>
       </c>
       <c r="B120" t="n">
-        <v>79565</v>
+        <v>56836</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13032,38 +13037,43 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>462679</v>
+        <v>462440</v>
       </c>
       <c r="R120" t="n">
-        <v>6769045</v>
+        <v>6768764</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13122,10 +13132,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125017264</v>
+        <v>125017240</v>
       </c>
       <c r="B121" t="n">
-        <v>78947</v>
+        <v>58305</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13134,25 +13144,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>103044</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13162,10 +13172,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>462713</v>
+        <v>462248</v>
       </c>
       <c r="R121" t="n">
-        <v>6769148</v>
+        <v>6768584</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13224,10 +13234,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125017198</v>
+        <v>125017114</v>
       </c>
       <c r="B122" t="n">
-        <v>57632</v>
+        <v>79565</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13240,39 +13250,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>462452</v>
+        <v>462451</v>
       </c>
       <c r="R122" t="n">
-        <v>6768897</v>
+        <v>6768820</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13331,10 +13336,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125017173</v>
+        <v>125017124</v>
       </c>
       <c r="B123" t="n">
-        <v>56836</v>
+        <v>79565</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13343,43 +13348,38 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>462440</v>
+        <v>462679</v>
       </c>
       <c r="R123" t="n">
-        <v>6768764</v>
+        <v>6769045</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13438,10 +13438,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125017240</v>
+        <v>125017264</v>
       </c>
       <c r="B124" t="n">
-        <v>58305</v>
+        <v>78947</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13450,25 +13450,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>103044</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13478,10 +13478,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>462248</v>
+        <v>462713</v>
       </c>
       <c r="R124" t="n">
-        <v>6768584</v>
+        <v>6769148</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14274,10 +14274,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125000794</v>
+        <v>125017270</v>
       </c>
       <c r="B132" t="n">
-        <v>78947</v>
+        <v>78592</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14290,21 +14290,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14314,10 +14314,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>462420</v>
+        <v>462777</v>
       </c>
       <c r="R132" t="n">
-        <v>6768785</v>
+        <v>6769237</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14352,11 +14352,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD132" t="b">
         <v>0</v>
       </c>
@@ -14369,22 +14364,22 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125017254</v>
+        <v>125017228</v>
       </c>
       <c r="B133" t="n">
-        <v>78947</v>
+        <v>94934</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14393,25 +14388,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>2412</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Philonotis fontana</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14421,10 +14416,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>462424</v>
+        <v>462418</v>
       </c>
       <c r="R133" t="n">
-        <v>6768802</v>
+        <v>6768790</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14457,6 +14452,11 @@
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>I kallkälla</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14483,7 +14483,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125017260</v>
+        <v>125000794</v>
       </c>
       <c r="B134" t="n">
         <v>78947</v>
@@ -14523,10 +14523,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>462575</v>
+        <v>462420</v>
       </c>
       <c r="R134" t="n">
-        <v>6768974</v>
+        <v>6768785</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14561,6 +14561,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD134" t="b">
         <v>0</v>
       </c>
@@ -14573,22 +14578,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125017228</v>
+        <v>125017254</v>
       </c>
       <c r="B135" t="n">
-        <v>94934</v>
+        <v>78947</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14597,25 +14602,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>2412</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Philonotis fontana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14625,10 +14630,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>462418</v>
+        <v>462424</v>
       </c>
       <c r="R135" t="n">
-        <v>6768790</v>
+        <v>6768802</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14661,11 +14666,6 @@
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-05-12</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>I kallkälla</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14692,10 +14692,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125017270</v>
+        <v>125017260</v>
       </c>
       <c r="B136" t="n">
-        <v>78592</v>
+        <v>78947</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14708,21 +14708,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14732,10 +14732,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>462777</v>
+        <v>462575</v>
       </c>
       <c r="R136" t="n">
-        <v>6769237</v>
+        <v>6768974</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15936,10 +15936,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125017246</v>
+        <v>125004378</v>
       </c>
       <c r="B148" t="n">
-        <v>78947</v>
+        <v>57632</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15952,34 +15952,39 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Salutjärnen, Dlr</t>
+          <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>462868</v>
+        <v>462261</v>
       </c>
       <c r="R148" t="n">
-        <v>6769325</v>
+        <v>6768593</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16014,6 +16019,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD148" t="b">
         <v>0</v>
       </c>
@@ -16026,12 +16036,12 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
@@ -16757,10 +16767,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>125004378</v>
+        <v>125017246</v>
       </c>
       <c r="B156" t="n">
-        <v>57632</v>
+        <v>78947</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16773,39 +16783,34 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Lädsån, Dlr</t>
+          <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>462261</v>
+        <v>462868</v>
       </c>
       <c r="R156" t="n">
-        <v>6768593</v>
+        <v>6769325</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16840,11 +16845,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD156" t="b">
         <v>0</v>
       </c>
@@ -16857,22 +16857,22 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>125017186</v>
+        <v>125017106</v>
       </c>
       <c r="B157" t="n">
-        <v>57632</v>
+        <v>79565</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16885,43 +16885,34 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>462647</v>
+        <v>462755</v>
       </c>
       <c r="R157" t="n">
-        <v>6769118</v>
+        <v>6769176</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16980,10 +16971,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>125017204</v>
+        <v>125017130</v>
       </c>
       <c r="B158" t="n">
-        <v>97147</v>
+        <v>79565</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16992,25 +16983,25 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17020,10 +17011,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>462438</v>
+        <v>462444</v>
       </c>
       <c r="R158" t="n">
-        <v>6768787</v>
+        <v>6768840</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17184,10 +17175,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>125017106</v>
+        <v>125017186</v>
       </c>
       <c r="B160" t="n">
-        <v>79565</v>
+        <v>57632</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17200,34 +17191,43 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P160" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>462755</v>
+        <v>462647</v>
       </c>
       <c r="R160" t="n">
-        <v>6769176</v>
+        <v>6769118</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17286,10 +17286,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>125017130</v>
+        <v>125017204</v>
       </c>
       <c r="B161" t="n">
-        <v>79565</v>
+        <v>97147</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17298,25 +17298,25 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6453</v>
+        <v>221945</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17326,10 +17326,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>462444</v>
+        <v>462438</v>
       </c>
       <c r="R161" t="n">
-        <v>6768840</v>
+        <v>6768787</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17918,10 +17918,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>125300490</v>
+        <v>125299886</v>
       </c>
       <c r="B167" t="n">
-        <v>82737</v>
+        <v>92448</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -17930,38 +17930,38 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Lädsån, Dlr</t>
+          <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>462425</v>
+        <v>462462</v>
       </c>
       <c r="R167" t="n">
-        <v>6768760</v>
+        <v>6768859</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18020,10 +18020,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>125299886</v>
+        <v>125300490</v>
       </c>
       <c r="B168" t="n">
-        <v>92448</v>
+        <v>82737</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -18032,38 +18032,38 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Salutjärnen, Dlr</t>
+          <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>462462</v>
+        <v>462425</v>
       </c>
       <c r="R168" t="n">
-        <v>6768859</v>
+        <v>6768760</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>

--- a/artfynd/A 18527-2025 artfynd.xlsx
+++ b/artfynd/A 18527-2025 artfynd.xlsx
@@ -1322,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124777598</v>
+        <v>124774814</v>
       </c>
       <c r="B8" t="n">
-        <v>78947</v>
+        <v>57632</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1338,34 +1338,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>462331</v>
+        <v>462257</v>
       </c>
       <c r="R8" t="n">
-        <v>6768680</v>
+        <v>6768691</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124774814</v>
+        <v>124777598</v>
       </c>
       <c r="B9" t="n">
-        <v>57632</v>
+        <v>78947</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1440,39 +1445,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462257</v>
+        <v>462331</v>
       </c>
       <c r="R9" t="n">
-        <v>6768691</v>
+        <v>6768680</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -3845,10 +3845,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124774845</v>
+        <v>124781860</v>
       </c>
       <c r="B32" t="n">
-        <v>8447</v>
+        <v>78947</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3857,25 +3857,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>462271</v>
+        <v>462362</v>
       </c>
       <c r="R32" t="n">
-        <v>6768703</v>
+        <v>6768766</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3921,6 +3921,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3947,10 +3952,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124781860</v>
+        <v>124774845</v>
       </c>
       <c r="B33" t="n">
-        <v>78947</v>
+        <v>8447</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3959,25 +3964,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3987,10 +3992,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>462362</v>
+        <v>462271</v>
       </c>
       <c r="R33" t="n">
-        <v>6768766</v>
+        <v>6768703</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4023,11 +4028,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4793,10 +4793,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124836527</v>
+        <v>124833941</v>
       </c>
       <c r="B41" t="n">
-        <v>79536</v>
+        <v>8447</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4805,25 +4805,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4833,10 +4833,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>462712</v>
+        <v>462816</v>
       </c>
       <c r="R41" t="n">
-        <v>6769143</v>
+        <v>6769191</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4873,7 +4873,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Miljöbild</t>
+          <t>Miljöbilder för närområdet.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4900,10 +4900,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124833941</v>
+        <v>124836527</v>
       </c>
       <c r="B42" t="n">
-        <v>8447</v>
+        <v>79536</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4912,25 +4912,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4940,10 +4940,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>462816</v>
+        <v>462712</v>
       </c>
       <c r="R42" t="n">
-        <v>6769191</v>
+        <v>6769143</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Miljöbilder för närområdet.</t>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6384,10 +6384,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125017139</v>
+        <v>125017258</v>
       </c>
       <c r="B56" t="n">
-        <v>78979</v>
+        <v>78947</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6400,21 +6400,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6424,10 +6424,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>462539</v>
+        <v>462449</v>
       </c>
       <c r="R56" t="n">
-        <v>6768915</v>
+        <v>6768783</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6486,10 +6486,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125017258</v>
+        <v>125004378</v>
       </c>
       <c r="B57" t="n">
-        <v>78947</v>
+        <v>57632</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6502,34 +6502,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Salutjärnen, Dlr</t>
+          <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>462449</v>
+        <v>462261</v>
       </c>
       <c r="R57" t="n">
-        <v>6768783</v>
+        <v>6768593</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6564,6 +6569,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6576,22 +6586,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125017188</v>
+        <v>125017232</v>
       </c>
       <c r="B58" t="n">
-        <v>57632</v>
+        <v>80900</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6604,39 +6614,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>462760</v>
+        <v>462456</v>
       </c>
       <c r="R58" t="n">
-        <v>6769122</v>
+        <v>6768781</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6695,10 +6700,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125004378</v>
+        <v>125017171</v>
       </c>
       <c r="B59" t="n">
-        <v>57632</v>
+        <v>91166</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6711,39 +6716,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lädsån, Dlr</t>
+          <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>462261</v>
+        <v>462425</v>
       </c>
       <c r="R59" t="n">
-        <v>6768593</v>
+        <v>6768807</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6778,11 +6778,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -6795,22 +6790,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125017173</v>
+        <v>125017139</v>
       </c>
       <c r="B60" t="n">
-        <v>56836</v>
+        <v>78979</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6819,43 +6814,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100138</v>
+        <v>185</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>462440</v>
+        <v>462539</v>
       </c>
       <c r="R60" t="n">
-        <v>6768764</v>
+        <v>6768915</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6914,10 +6904,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125001616</v>
+        <v>125017188</v>
       </c>
       <c r="B61" t="n">
-        <v>56836</v>
+        <v>57632</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6926,31 +6916,31 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -6959,10 +6949,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>462456</v>
+        <v>462760</v>
       </c>
       <c r="R61" t="n">
-        <v>6768778</v>
+        <v>6769122</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6997,11 +6987,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Miljöbilder. Så kallad tjädertall</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -7014,22 +6999,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125017232</v>
+        <v>125017173</v>
       </c>
       <c r="B62" t="n">
-        <v>80900</v>
+        <v>56836</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7038,38 +7023,43 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1049</v>
+        <v>100138</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>462456</v>
+        <v>462440</v>
       </c>
       <c r="R62" t="n">
-        <v>6768781</v>
+        <v>6768764</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7128,10 +7118,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125017171</v>
+        <v>125001616</v>
       </c>
       <c r="B63" t="n">
-        <v>91166</v>
+        <v>56836</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7140,38 +7130,43 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>462425</v>
+        <v>462456</v>
       </c>
       <c r="R63" t="n">
-        <v>6768807</v>
+        <v>6768778</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7206,6 +7201,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Miljöbilder. Så kallad tjädertall</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -7218,12 +7218,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -9528,10 +9528,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125017108</v>
+        <v>125017212</v>
       </c>
       <c r="B86" t="n">
-        <v>79565</v>
+        <v>8447</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9540,38 +9540,43 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>462569</v>
+        <v>462295</v>
       </c>
       <c r="R86" t="n">
-        <v>6769031</v>
+        <v>6768622</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9630,10 +9635,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125007719</v>
+        <v>125017166</v>
       </c>
       <c r="B87" t="n">
-        <v>79565</v>
+        <v>91521</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9642,38 +9647,38 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>2062</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Lädsån, Dlr</t>
+          <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>462456</v>
+        <v>462312</v>
       </c>
       <c r="R87" t="n">
-        <v>6768884</v>
+        <v>6768750</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9708,11 +9713,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
@@ -9725,22 +9725,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125017166</v>
+        <v>125017245</v>
       </c>
       <c r="B88" t="n">
-        <v>91521</v>
+        <v>78947</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9749,25 +9749,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9777,10 +9777,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>462312</v>
+        <v>462867</v>
       </c>
       <c r="R88" t="n">
-        <v>6768750</v>
+        <v>6769346</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9839,10 +9839,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125017245</v>
+        <v>125017108</v>
       </c>
       <c r="B89" t="n">
-        <v>78947</v>
+        <v>79565</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9855,21 +9855,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9879,10 +9879,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>462867</v>
+        <v>462569</v>
       </c>
       <c r="R89" t="n">
-        <v>6769346</v>
+        <v>6769031</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9941,10 +9941,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125017212</v>
+        <v>125007719</v>
       </c>
       <c r="B90" t="n">
-        <v>8447</v>
+        <v>79565</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9953,43 +9953,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Salutjärnen, Dlr</t>
+          <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>462295</v>
+        <v>462456</v>
       </c>
       <c r="R90" t="n">
-        <v>6768622</v>
+        <v>6768884</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10024,6 +10019,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
@@ -10036,12 +10036,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -10573,7 +10573,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124999425</v>
+        <v>125017220</v>
       </c>
       <c r="B96" t="n">
         <v>8447</v>
@@ -10607,16 +10607,21 @@
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>462616</v>
+        <v>462472</v>
       </c>
       <c r="R96" t="n">
-        <v>6769046</v>
+        <v>6768856</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10651,11 +10656,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
@@ -10668,22 +10668,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125017202</v>
+        <v>125017114</v>
       </c>
       <c r="B97" t="n">
-        <v>91459</v>
+        <v>79565</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10696,21 +10696,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>658</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10720,10 +10720,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>462414</v>
+        <v>462451</v>
       </c>
       <c r="R97" t="n">
-        <v>6768758</v>
+        <v>6768820</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10782,7 +10782,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125017270</v>
+        <v>125017277</v>
       </c>
       <c r="B98" t="n">
         <v>78592</v>
@@ -10822,10 +10822,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>462777</v>
+        <v>462478</v>
       </c>
       <c r="R98" t="n">
-        <v>6769237</v>
+        <v>6768887</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10884,7 +10884,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125017220</v>
+        <v>124999425</v>
       </c>
       <c r="B99" t="n">
         <v>8447</v>
@@ -10918,21 +10918,16 @@
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>462472</v>
+        <v>462616</v>
       </c>
       <c r="R99" t="n">
-        <v>6768856</v>
+        <v>6769046</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10967,6 +10962,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
+        </is>
+      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
@@ -10979,22 +10979,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125017114</v>
+        <v>125017202</v>
       </c>
       <c r="B100" t="n">
-        <v>79565</v>
+        <v>91459</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11007,21 +11007,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>658</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11031,10 +11031,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>462451</v>
+        <v>462414</v>
       </c>
       <c r="R100" t="n">
-        <v>6768820</v>
+        <v>6768758</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11093,7 +11093,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125017277</v>
+        <v>125017270</v>
       </c>
       <c r="B101" t="n">
         <v>78592</v>
@@ -11133,10 +11133,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>462478</v>
+        <v>462777</v>
       </c>
       <c r="R101" t="n">
-        <v>6768887</v>
+        <v>6769237</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11714,10 +11714,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125017279</v>
+        <v>124999027</v>
       </c>
       <c r="B107" t="n">
-        <v>78592</v>
+        <v>57632</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11730,21 +11730,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>353</v>
+        <v>100049</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11754,10 +11754,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>462581</v>
+        <v>462741</v>
       </c>
       <c r="R107" t="n">
-        <v>6768944</v>
+        <v>6769142</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11792,6 +11792,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Miljöbilder. Sannoligt bohål/hackhål efter spillkråka.</t>
+        </is>
+      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
@@ -11804,22 +11809,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125017113</v>
+        <v>125017279</v>
       </c>
       <c r="B108" t="n">
-        <v>79565</v>
+        <v>78592</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11832,21 +11837,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11856,10 +11861,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>462356</v>
+        <v>462581</v>
       </c>
       <c r="R108" t="n">
-        <v>6768753</v>
+        <v>6768944</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11918,10 +11923,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125017251</v>
+        <v>125017113</v>
       </c>
       <c r="B109" t="n">
-        <v>78947</v>
+        <v>79565</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11934,21 +11939,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11958,10 +11963,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>462357</v>
+        <v>462356</v>
       </c>
       <c r="R109" t="n">
-        <v>6768775</v>
+        <v>6768753</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12020,7 +12025,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125017256</v>
+        <v>125017251</v>
       </c>
       <c r="B110" t="n">
         <v>78947</v>
@@ -12060,10 +12065,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>462409</v>
+        <v>462357</v>
       </c>
       <c r="R110" t="n">
-        <v>6768798</v>
+        <v>6768775</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12122,10 +12127,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>124999027</v>
+        <v>125017256</v>
       </c>
       <c r="B111" t="n">
-        <v>57632</v>
+        <v>78947</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12138,21 +12143,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12162,10 +12167,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>462741</v>
+        <v>462409</v>
       </c>
       <c r="R111" t="n">
-        <v>6769142</v>
+        <v>6768798</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12200,11 +12205,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Miljöbilder. Sannoligt bohål/hackhål efter spillkråka.</t>
-        </is>
-      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
@@ -12217,12 +12217,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
@@ -13050,10 +13050,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125017117</v>
+        <v>125017228</v>
       </c>
       <c r="B120" t="n">
-        <v>79565</v>
+        <v>94934</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13062,25 +13062,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6453</v>
+        <v>2412</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Philonotis fontana</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13090,10 +13090,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>462501</v>
+        <v>462418</v>
       </c>
       <c r="R120" t="n">
-        <v>6768895</v>
+        <v>6768790</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13126,6 +13126,11 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>I kallkälla</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13152,10 +13157,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125017228</v>
+        <v>125017253</v>
       </c>
       <c r="B121" t="n">
-        <v>94934</v>
+        <v>78947</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13164,25 +13169,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>2412</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Philonotis fontana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13192,10 +13197,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>462418</v>
+        <v>462425</v>
       </c>
       <c r="R121" t="n">
-        <v>6768790</v>
+        <v>6768806</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13228,11 +13233,6 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-05-12</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>I kallkälla</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13259,10 +13259,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125017253</v>
+        <v>125017117</v>
       </c>
       <c r="B122" t="n">
-        <v>78947</v>
+        <v>79565</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13275,21 +13275,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13299,10 +13299,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>462425</v>
+        <v>462501</v>
       </c>
       <c r="R122" t="n">
-        <v>6768806</v>
+        <v>6768895</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -16252,10 +16252,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>125017284</v>
+        <v>124999190</v>
       </c>
       <c r="B151" t="n">
-        <v>91166</v>
+        <v>8447</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16264,25 +16264,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16292,10 +16292,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>462409</v>
+        <v>462672</v>
       </c>
       <c r="R151" t="n">
-        <v>6768814</v>
+        <v>6769113</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16342,12 +16342,12 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
@@ -16660,10 +16660,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>125001339</v>
+        <v>125017284</v>
       </c>
       <c r="B155" t="n">
-        <v>57632</v>
+        <v>91166</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16676,39 +16676,34 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P155" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>462456</v>
+        <v>462409</v>
       </c>
       <c r="R155" t="n">
-        <v>6768778</v>
+        <v>6768814</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16743,11 +16738,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC155" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD155" t="b">
         <v>0</v>
       </c>
@@ -16760,22 +16750,22 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>124999190</v>
+        <v>125001339</v>
       </c>
       <c r="B156" t="n">
-        <v>8447</v>
+        <v>57632</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16784,38 +16774,43 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P156" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>462672</v>
+        <v>462456</v>
       </c>
       <c r="R156" t="n">
-        <v>6769113</v>
+        <v>6768778</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16848,6 +16843,11 @@
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -19045,10 +19045,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>125300481</v>
+        <v>125300260</v>
       </c>
       <c r="B178" t="n">
-        <v>75025</v>
+        <v>96395</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -19057,25 +19057,25 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6440</v>
+        <v>2869</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -19085,10 +19085,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>462425</v>
+        <v>462418</v>
       </c>
       <c r="R178" t="n">
-        <v>6768760</v>
+        <v>6768801</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19147,10 +19147,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>125300260</v>
+        <v>125300481</v>
       </c>
       <c r="B179" t="n">
-        <v>96395</v>
+        <v>75025</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -19159,25 +19159,25 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>2869</v>
+        <v>6440</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -19187,10 +19187,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>462418</v>
+        <v>462425</v>
       </c>
       <c r="R179" t="n">
-        <v>6768801</v>
+        <v>6768760</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>

--- a/artfynd/A 18527-2025 artfynd.xlsx
+++ b/artfynd/A 18527-2025 artfynd.xlsx
@@ -7750,10 +7750,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125017265</v>
+        <v>125017154</v>
       </c>
       <c r="B69" t="n">
-        <v>78947</v>
+        <v>96522</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7766,21 +7766,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7790,10 +7790,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>462762</v>
+        <v>462433</v>
       </c>
       <c r="R69" t="n">
-        <v>6769125</v>
+        <v>6768784</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7852,10 +7852,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125017205</v>
+        <v>125017134</v>
       </c>
       <c r="B70" t="n">
-        <v>8447</v>
+        <v>78979</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7864,43 +7864,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>462864</v>
+        <v>462385</v>
       </c>
       <c r="R70" t="n">
-        <v>6769317</v>
+        <v>6768840</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7959,10 +7954,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125017225</v>
+        <v>125017236</v>
       </c>
       <c r="B71" t="n">
-        <v>8447</v>
+        <v>78683</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7971,43 +7966,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>462449</v>
+        <v>462688</v>
       </c>
       <c r="R71" t="n">
-        <v>6768765</v>
+        <v>6769019</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8066,10 +8056,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125017154</v>
+        <v>125017265</v>
       </c>
       <c r="B72" t="n">
-        <v>96522</v>
+        <v>78947</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8082,21 +8072,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8106,10 +8096,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>462433</v>
+        <v>462762</v>
       </c>
       <c r="R72" t="n">
-        <v>6768784</v>
+        <v>6769125</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8168,10 +8158,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125017134</v>
+        <v>125017205</v>
       </c>
       <c r="B73" t="n">
-        <v>78979</v>
+        <v>8447</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8180,38 +8170,43 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>462385</v>
+        <v>462864</v>
       </c>
       <c r="R73" t="n">
-        <v>6768840</v>
+        <v>6769317</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8270,10 +8265,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125017236</v>
+        <v>125017225</v>
       </c>
       <c r="B74" t="n">
-        <v>78683</v>
+        <v>8447</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8282,38 +8277,43 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>462688</v>
+        <v>462449</v>
       </c>
       <c r="R74" t="n">
-        <v>6769019</v>
+        <v>6768765</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8372,10 +8372,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125000074</v>
+        <v>125017162</v>
       </c>
       <c r="B75" t="n">
-        <v>57632</v>
+        <v>79565</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8388,39 +8388,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Lädsån, Dlr</t>
+          <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>462482</v>
+        <v>462763</v>
       </c>
       <c r="R75" t="n">
-        <v>6768845</v>
+        <v>6769126</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8467,19 +8462,19 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125017162</v>
+        <v>125017122</v>
       </c>
       <c r="B76" t="n">
         <v>79565</v>
@@ -8519,10 +8514,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>462763</v>
+        <v>462688</v>
       </c>
       <c r="R76" t="n">
-        <v>6769126</v>
+        <v>6769019</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8581,7 +8576,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125017122</v>
+        <v>125001392</v>
       </c>
       <c r="B77" t="n">
         <v>79565</v>
@@ -8621,10 +8616,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>462688</v>
+        <v>462456</v>
       </c>
       <c r="R77" t="n">
-        <v>6769019</v>
+        <v>6768778</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8659,6 +8654,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -8671,19 +8671,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125001392</v>
+        <v>125017115</v>
       </c>
       <c r="B78" t="n">
         <v>79565</v>
@@ -8723,10 +8723,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>462456</v>
+        <v>462449</v>
       </c>
       <c r="R78" t="n">
-        <v>6768778</v>
+        <v>6768835</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8761,11 +8761,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -8778,19 +8773,19 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125017115</v>
+        <v>125017124</v>
       </c>
       <c r="B79" t="n">
         <v>79565</v>
@@ -8830,10 +8825,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>462449</v>
+        <v>462679</v>
       </c>
       <c r="R79" t="n">
-        <v>6768835</v>
+        <v>6769045</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8892,10 +8887,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125017124</v>
+        <v>125017268</v>
       </c>
       <c r="B80" t="n">
-        <v>79565</v>
+        <v>92448</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8904,38 +8899,47 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>462679</v>
+        <v>462470</v>
       </c>
       <c r="R80" t="n">
-        <v>6769045</v>
+        <v>6768894</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8994,10 +8998,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125017268</v>
+        <v>125017190</v>
       </c>
       <c r="B81" t="n">
-        <v>92448</v>
+        <v>57632</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9006,35 +9010,31 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -9043,10 +9043,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>462470</v>
+        <v>462791</v>
       </c>
       <c r="R81" t="n">
-        <v>6768894</v>
+        <v>6769257</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9207,7 +9207,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125017190</v>
+        <v>125000074</v>
       </c>
       <c r="B83" t="n">
         <v>57632</v>
@@ -9243,19 +9243,19 @@
       <c r="I83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Salutjärnen, Dlr</t>
+          <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>462791</v>
+        <v>462482</v>
       </c>
       <c r="R83" t="n">
-        <v>6769257</v>
+        <v>6768845</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9302,12 +9302,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -10048,10 +10048,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125017130</v>
+        <v>125017234</v>
       </c>
       <c r="B91" t="n">
-        <v>79565</v>
+        <v>78683</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10064,21 +10064,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10088,10 +10088,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>462444</v>
+        <v>462501</v>
       </c>
       <c r="R91" t="n">
-        <v>6768840</v>
+        <v>6768890</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10150,10 +10150,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125017234</v>
+        <v>125017130</v>
       </c>
       <c r="B92" t="n">
-        <v>78683</v>
+        <v>79565</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10166,21 +10166,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10190,10 +10190,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>462501</v>
+        <v>462444</v>
       </c>
       <c r="R92" t="n">
-        <v>6768890</v>
+        <v>6768840</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10252,10 +10252,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125000045</v>
+        <v>125001767</v>
       </c>
       <c r="B93" t="n">
-        <v>78947</v>
+        <v>57632</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10268,34 +10268,39 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>462482</v>
+        <v>462346</v>
       </c>
       <c r="R93" t="n">
-        <v>6768845</v>
+        <v>6768794</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10328,6 +10333,11 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10354,7 +10364,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125001767</v>
+        <v>125017193</v>
       </c>
       <c r="B94" t="n">
         <v>57632</v>
@@ -10390,19 +10400,19 @@
       <c r="I94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Lädsån, Dlr</t>
+          <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>462346</v>
+        <v>462585</v>
       </c>
       <c r="R94" t="n">
-        <v>6768794</v>
+        <v>6769050</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10437,11 +10447,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
@@ -10454,22 +10459,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125017193</v>
+        <v>125000045</v>
       </c>
       <c r="B95" t="n">
-        <v>57632</v>
+        <v>78947</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10482,39 +10487,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Salutjärnen, Dlr</t>
+          <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>462585</v>
+        <v>462482</v>
       </c>
       <c r="R95" t="n">
-        <v>6769050</v>
+        <v>6768845</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10561,12 +10561,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
@@ -11195,10 +11195,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125017123</v>
+        <v>125017246</v>
       </c>
       <c r="B102" t="n">
-        <v>79565</v>
+        <v>78947</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11211,21 +11211,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11235,10 +11235,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>462680</v>
+        <v>462868</v>
       </c>
       <c r="R102" t="n">
-        <v>6769027</v>
+        <v>6769325</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11297,10 +11297,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125017112</v>
+        <v>125017186</v>
       </c>
       <c r="B103" t="n">
-        <v>79565</v>
+        <v>57632</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11313,34 +11313,43 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>462453</v>
+        <v>462647</v>
       </c>
       <c r="R103" t="n">
-        <v>6768876</v>
+        <v>6769118</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11399,10 +11408,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125017141</v>
+        <v>125017123</v>
       </c>
       <c r="B104" t="n">
-        <v>78979</v>
+        <v>79565</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11415,21 +11424,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11439,10 +11448,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>462579</v>
+        <v>462680</v>
       </c>
       <c r="R104" t="n">
-        <v>6768990</v>
+        <v>6769027</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11501,10 +11510,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125017246</v>
+        <v>125017112</v>
       </c>
       <c r="B105" t="n">
-        <v>78947</v>
+        <v>79565</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11517,21 +11526,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11541,10 +11550,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>462868</v>
+        <v>462453</v>
       </c>
       <c r="R105" t="n">
-        <v>6769325</v>
+        <v>6768876</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11603,10 +11612,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125017186</v>
+        <v>125017141</v>
       </c>
       <c r="B106" t="n">
-        <v>57632</v>
+        <v>78979</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11619,43 +11628,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>462647</v>
+        <v>462579</v>
       </c>
       <c r="R106" t="n">
-        <v>6769118</v>
+        <v>6768990</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -13463,10 +13463,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125017210</v>
+        <v>125017155</v>
       </c>
       <c r="B124" t="n">
-        <v>8447</v>
+        <v>96522</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13475,43 +13475,38 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>462636</v>
+        <v>462427</v>
       </c>
       <c r="R124" t="n">
-        <v>6769113</v>
+        <v>6768776</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13570,10 +13565,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>124999142</v>
+        <v>125017278</v>
       </c>
       <c r="B125" t="n">
-        <v>78979</v>
+        <v>78592</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13586,21 +13581,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13610,10 +13605,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>462684</v>
+        <v>462544</v>
       </c>
       <c r="R125" t="n">
-        <v>6769117</v>
+        <v>6768928</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13660,12 +13655,12 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
@@ -13774,10 +13769,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125000745</v>
+        <v>125017252</v>
       </c>
       <c r="B127" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13790,39 +13785,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>462414</v>
+        <v>462426</v>
       </c>
       <c r="R127" t="n">
-        <v>6768796</v>
+        <v>6768812</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13857,11 +13847,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
-        </is>
-      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
@@ -13874,22 +13859,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125017155</v>
+        <v>125017264</v>
       </c>
       <c r="B128" t="n">
-        <v>96522</v>
+        <v>78947</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13902,21 +13887,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13926,10 +13911,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>462427</v>
+        <v>462713</v>
       </c>
       <c r="R128" t="n">
-        <v>6768776</v>
+        <v>6769148</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13988,10 +13973,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125017278</v>
+        <v>125000745</v>
       </c>
       <c r="B129" t="n">
-        <v>78592</v>
+        <v>57635</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14004,34 +13989,39 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>462544</v>
+        <v>462414</v>
       </c>
       <c r="R129" t="n">
-        <v>6768928</v>
+        <v>6768796</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14066,6 +14056,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
+        </is>
+      </c>
       <c r="AD129" t="b">
         <v>0</v>
       </c>
@@ -14078,22 +14073,22 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>125017252</v>
+        <v>124999142</v>
       </c>
       <c r="B130" t="n">
-        <v>78947</v>
+        <v>78979</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14106,21 +14101,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14130,10 +14125,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>462426</v>
+        <v>462684</v>
       </c>
       <c r="R130" t="n">
-        <v>6768812</v>
+        <v>6769117</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14180,22 +14175,22 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125017264</v>
+        <v>125017210</v>
       </c>
       <c r="B131" t="n">
-        <v>78947</v>
+        <v>8447</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14204,38 +14199,43 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>462713</v>
+        <v>462636</v>
       </c>
       <c r="R131" t="n">
-        <v>6769148</v>
+        <v>6769113</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -19045,10 +19045,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>125300260</v>
+        <v>125300481</v>
       </c>
       <c r="B178" t="n">
-        <v>96395</v>
+        <v>75025</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -19057,25 +19057,25 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>2869</v>
+        <v>6440</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -19085,10 +19085,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>462418</v>
+        <v>462425</v>
       </c>
       <c r="R178" t="n">
-        <v>6768801</v>
+        <v>6768760</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19147,10 +19147,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>125300481</v>
+        <v>125300260</v>
       </c>
       <c r="B179" t="n">
-        <v>75025</v>
+        <v>96395</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -19159,25 +19159,25 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6440</v>
+        <v>2869</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -19187,10 +19187,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>462425</v>
+        <v>462418</v>
       </c>
       <c r="R179" t="n">
-        <v>6768760</v>
+        <v>6768801</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>

--- a/artfynd/A 18527-2025 artfynd.xlsx
+++ b/artfynd/A 18527-2025 artfynd.xlsx
@@ -20698,10 +20698,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>125340174</v>
+        <v>125339448</v>
       </c>
       <c r="B202" t="n">
-        <v>78999</v>
+        <v>78967</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -20709,34 +20709,34 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Lädsån, Dlr</t>
+          <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>462599</v>
+        <v>462879</v>
       </c>
       <c r="R202" t="n">
-        <v>6769078</v>
+        <v>6769344</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -20795,32 +20795,32 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>125339448</v>
+        <v>125339670</v>
       </c>
       <c r="B203" t="n">
-        <v>78967</v>
+        <v>8447</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -20830,10 +20830,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>462879</v>
+        <v>462858</v>
       </c>
       <c r="R203" t="n">
-        <v>6769344</v>
+        <v>6769291</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -20866,6 +20866,11 @@
       <c r="AA203" t="inlineStr">
         <is>
           <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AC203" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -20892,7 +20897,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>125339670</v>
+        <v>125339496</v>
       </c>
       <c r="B204" t="n">
         <v>8447</v>
@@ -20927,10 +20932,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>462858</v>
+        <v>462897</v>
       </c>
       <c r="R204" t="n">
-        <v>6769291</v>
+        <v>6769360</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -20963,11 +20968,6 @@
       <c r="AA204" t="inlineStr">
         <is>
           <t>2025-05-23</t>
-        </is>
-      </c>
-      <c r="AC204" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -20994,45 +20994,45 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>125339496</v>
+        <v>125340174</v>
       </c>
       <c r="B205" t="n">
-        <v>8447</v>
+        <v>78999</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Salutjärnen, Dlr</t>
+          <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>462897</v>
+        <v>462599</v>
       </c>
       <c r="R205" t="n">
-        <v>6769360</v>
+        <v>6769078</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>

--- a/artfynd/A 18527-2025 artfynd.xlsx
+++ b/artfynd/A 18527-2025 artfynd.xlsx
@@ -18348,7 +18348,7 @@
         <v>125300260</v>
       </c>
       <c r="B178" t="n">
-        <v>96450</v>
+        <v>96457</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18445,7 +18445,7 @@
         <v>125299810</v>
       </c>
       <c r="B179" t="n">
-        <v>92502</v>
+        <v>92509</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -18636,45 +18636,45 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>125302067</v>
+        <v>125300055</v>
       </c>
       <c r="B181" t="n">
-        <v>75066</v>
+        <v>92509</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6440</v>
+        <v>4364</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Lädsån, Dlr</t>
+          <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>462318</v>
+        <v>462458</v>
       </c>
       <c r="R181" t="n">
-        <v>6768701</v>
+        <v>6768846</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -18733,7 +18733,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>125303042</v>
+        <v>125302067</v>
       </c>
       <c r="B182" t="n">
         <v>75066</v>
@@ -18768,10 +18768,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>462288</v>
+        <v>462318</v>
       </c>
       <c r="R182" t="n">
-        <v>6768602</v>
+        <v>6768701</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -18830,7 +18830,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>125303298</v>
+        <v>125303042</v>
       </c>
       <c r="B183" t="n">
         <v>75066</v>
@@ -18865,10 +18865,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>462263</v>
+        <v>462288</v>
       </c>
       <c r="R183" t="n">
-        <v>6768595</v>
+        <v>6768602</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -18927,45 +18927,45 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>125300055</v>
+        <v>125303298</v>
       </c>
       <c r="B184" t="n">
-        <v>92502</v>
+        <v>75066</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>4364</v>
+        <v>6440</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Salutjärnen, Dlr</t>
+          <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>462458</v>
+        <v>462263</v>
       </c>
       <c r="R184" t="n">
-        <v>6768846</v>
+        <v>6768595</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19024,32 +19024,32 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>125299647</v>
+        <v>125299886</v>
       </c>
       <c r="B185" t="n">
-        <v>78967</v>
+        <v>92509</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19059,10 +19059,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>462563</v>
+        <v>462462</v>
       </c>
       <c r="R185" t="n">
-        <v>6768994</v>
+        <v>6768859</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19121,32 +19121,32 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>125299886</v>
+        <v>125299647</v>
       </c>
       <c r="B186" t="n">
-        <v>92502</v>
+        <v>78967</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19156,10 +19156,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>462462</v>
+        <v>462563</v>
       </c>
       <c r="R186" t="n">
-        <v>6768859</v>
+        <v>6768994</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20698,10 +20698,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>125339448</v>
+        <v>125340174</v>
       </c>
       <c r="B202" t="n">
-        <v>78967</v>
+        <v>78999</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -20709,34 +20709,34 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Salutjärnen, Dlr</t>
+          <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>462879</v>
+        <v>462599</v>
       </c>
       <c r="R202" t="n">
-        <v>6769344</v>
+        <v>6769078</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -20795,32 +20795,32 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>125339670</v>
+        <v>125339448</v>
       </c>
       <c r="B203" t="n">
-        <v>8447</v>
+        <v>78967</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -20830,10 +20830,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>462858</v>
+        <v>462879</v>
       </c>
       <c r="R203" t="n">
-        <v>6769291</v>
+        <v>6769344</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -20866,11 +20866,6 @@
       <c r="AA203" t="inlineStr">
         <is>
           <t>2025-05-23</t>
-        </is>
-      </c>
-      <c r="AC203" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -20897,7 +20892,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>125339496</v>
+        <v>125339670</v>
       </c>
       <c r="B204" t="n">
         <v>8447</v>
@@ -20932,10 +20927,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>462897</v>
+        <v>462858</v>
       </c>
       <c r="R204" t="n">
-        <v>6769360</v>
+        <v>6769291</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -20968,6 +20963,11 @@
       <c r="AA204" t="inlineStr">
         <is>
           <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AC204" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -20994,45 +20994,45 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>125340174</v>
+        <v>125339496</v>
       </c>
       <c r="B205" t="n">
-        <v>78999</v>
+        <v>8447</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Lädsån, Dlr</t>
+          <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>462599</v>
+        <v>462897</v>
       </c>
       <c r="R205" t="n">
-        <v>6769078</v>
+        <v>6769360</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21094,7 +21094,7 @@
         <v>125017199</v>
       </c>
       <c r="B206" t="n">
-        <v>96568</v>
+        <v>96575</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>

--- a/artfynd/A 18527-2025 artfynd.xlsx
+++ b/artfynd/A 18527-2025 artfynd.xlsx
@@ -18151,10 +18151,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>125302979</v>
+        <v>125300490</v>
       </c>
       <c r="B176" t="n">
-        <v>75066</v>
+        <v>82779</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18162,21 +18162,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18186,10 +18186,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>462292</v>
+        <v>462425</v>
       </c>
       <c r="R176" t="n">
-        <v>6768618</v>
+        <v>6768760</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18248,10 +18248,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>125300490</v>
+        <v>125302979</v>
       </c>
       <c r="B177" t="n">
-        <v>82779</v>
+        <v>75066</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18259,21 +18259,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18283,10 +18283,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>462425</v>
+        <v>462292</v>
       </c>
       <c r="R177" t="n">
-        <v>6768760</v>
+        <v>6768618</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19320,10 +19320,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>125299980</v>
+        <v>125303598</v>
       </c>
       <c r="B188" t="n">
-        <v>78967</v>
+        <v>75066</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -19331,34 +19331,34 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Salutjärnen, Dlr</t>
+          <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>462462</v>
+        <v>462205</v>
       </c>
       <c r="R188" t="n">
-        <v>6768859</v>
+        <v>6768587</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19417,10 +19417,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>125303598</v>
+        <v>125299980</v>
       </c>
       <c r="B189" t="n">
-        <v>75066</v>
+        <v>78967</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -19428,34 +19428,34 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Lädsån, Dlr</t>
+          <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>462205</v>
+        <v>462462</v>
       </c>
       <c r="R189" t="n">
-        <v>6768587</v>
+        <v>6768859</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>

--- a/artfynd/A 18527-2025 artfynd.xlsx
+++ b/artfynd/A 18527-2025 artfynd.xlsx
@@ -20698,45 +20698,45 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>125340174</v>
+        <v>125339670</v>
       </c>
       <c r="B202" t="n">
-        <v>78999</v>
+        <v>8447</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Lädsån, Dlr</t>
+          <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>462599</v>
+        <v>462858</v>
       </c>
       <c r="R202" t="n">
-        <v>6769078</v>
+        <v>6769291</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -20769,6 +20769,11 @@
       <c r="AA202" t="inlineStr">
         <is>
           <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -20795,32 +20800,32 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>125339448</v>
+        <v>125339496</v>
       </c>
       <c r="B203" t="n">
-        <v>78967</v>
+        <v>8447</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -20830,10 +20835,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>462879</v>
+        <v>462897</v>
       </c>
       <c r="R203" t="n">
-        <v>6769344</v>
+        <v>6769360</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -20892,45 +20897,45 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>125339670</v>
+        <v>125340174</v>
       </c>
       <c r="B204" t="n">
-        <v>8447</v>
+        <v>78999</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Salutjärnen, Dlr</t>
+          <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>462858</v>
+        <v>462599</v>
       </c>
       <c r="R204" t="n">
-        <v>6769291</v>
+        <v>6769078</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -20963,11 +20968,6 @@
       <c r="AA204" t="inlineStr">
         <is>
           <t>2025-05-23</t>
-        </is>
-      </c>
-      <c r="AC204" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -20994,32 +20994,32 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>125339496</v>
+        <v>125339448</v>
       </c>
       <c r="B205" t="n">
-        <v>8447</v>
+        <v>78967</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -21029,10 +21029,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>462897</v>
+        <v>462879</v>
       </c>
       <c r="R205" t="n">
-        <v>6769360</v>
+        <v>6769344</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>

--- a/artfynd/A 18527-2025 artfynd.xlsx
+++ b/artfynd/A 18527-2025 artfynd.xlsx
@@ -17276,7 +17276,7 @@
         <v>125304145</v>
       </c>
       <c r="B167" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17373,7 +17373,7 @@
         <v>125302283</v>
       </c>
       <c r="B168" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17470,7 +17470,7 @@
         <v>125300481</v>
       </c>
       <c r="B169" t="n">
-        <v>75066</v>
+        <v>75067</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17567,7 +17567,7 @@
         <v>125300151</v>
       </c>
       <c r="B170" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17669,7 +17669,7 @@
         <v>125303878</v>
       </c>
       <c r="B171" t="n">
-        <v>75066</v>
+        <v>75067</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17766,7 +17766,7 @@
         <v>125300882</v>
       </c>
       <c r="B172" t="n">
-        <v>82779</v>
+        <v>82780</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17863,7 +17863,7 @@
         <v>125302464</v>
       </c>
       <c r="B173" t="n">
-        <v>75066</v>
+        <v>75067</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17960,7 +17960,7 @@
         <v>125303152</v>
       </c>
       <c r="B174" t="n">
-        <v>75066</v>
+        <v>75067</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18057,7 +18057,7 @@
         <v>125302780</v>
       </c>
       <c r="B175" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>125300490</v>
       </c>
       <c r="B176" t="n">
-        <v>82779</v>
+        <v>82780</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18251,7 +18251,7 @@
         <v>125302979</v>
       </c>
       <c r="B177" t="n">
-        <v>75066</v>
+        <v>75067</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18348,7 +18348,7 @@
         <v>125300260</v>
       </c>
       <c r="B178" t="n">
-        <v>96457</v>
+        <v>96460</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18445,7 +18445,7 @@
         <v>125299810</v>
       </c>
       <c r="B179" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -18542,7 +18542,7 @@
         <v>125303428</v>
       </c>
       <c r="B180" t="n">
-        <v>75066</v>
+        <v>75067</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18636,45 +18636,45 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>125300055</v>
+        <v>125302067</v>
       </c>
       <c r="B181" t="n">
-        <v>92509</v>
+        <v>75067</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>4364</v>
+        <v>6440</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Salutjärnen, Dlr</t>
+          <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>462458</v>
+        <v>462318</v>
       </c>
       <c r="R181" t="n">
-        <v>6768846</v>
+        <v>6768701</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -18733,10 +18733,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>125302067</v>
+        <v>125303042</v>
       </c>
       <c r="B182" t="n">
-        <v>75066</v>
+        <v>75067</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -18768,10 +18768,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>462318</v>
+        <v>462288</v>
       </c>
       <c r="R182" t="n">
-        <v>6768701</v>
+        <v>6768602</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -18830,45 +18830,45 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>125303042</v>
+        <v>125300055</v>
       </c>
       <c r="B183" t="n">
-        <v>75066</v>
+        <v>92518</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6440</v>
+        <v>4364</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Lädsån, Dlr</t>
+          <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>462288</v>
+        <v>462458</v>
       </c>
       <c r="R183" t="n">
-        <v>6768602</v>
+        <v>6768846</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -18930,7 +18930,7 @@
         <v>125303298</v>
       </c>
       <c r="B184" t="n">
-        <v>75066</v>
+        <v>75067</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19024,32 +19024,32 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>125299886</v>
+        <v>125299647</v>
       </c>
       <c r="B185" t="n">
-        <v>92509</v>
+        <v>78968</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19059,10 +19059,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>462462</v>
+        <v>462563</v>
       </c>
       <c r="R185" t="n">
-        <v>6768859</v>
+        <v>6768994</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19121,32 +19121,32 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>125299647</v>
+        <v>125299886</v>
       </c>
       <c r="B186" t="n">
-        <v>78967</v>
+        <v>92518</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19156,10 +19156,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>462563</v>
+        <v>462462</v>
       </c>
       <c r="R186" t="n">
-        <v>6768994</v>
+        <v>6768859</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19323,7 +19323,7 @@
         <v>125303598</v>
       </c>
       <c r="B188" t="n">
-        <v>75066</v>
+        <v>75067</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -19420,7 +19420,7 @@
         <v>125299980</v>
       </c>
       <c r="B189" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -19517,7 +19517,7 @@
         <v>125302077</v>
       </c>
       <c r="B190" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -19614,7 +19614,7 @@
         <v>125300225</v>
       </c>
       <c r="B191" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -19711,7 +19711,7 @@
         <v>125302321</v>
       </c>
       <c r="B192" t="n">
-        <v>75066</v>
+        <v>75067</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -19808,7 +19808,7 @@
         <v>125339979</v>
       </c>
       <c r="B193" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -20109,7 +20109,7 @@
         <v>125340372</v>
       </c>
       <c r="B196" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20206,7 +20206,7 @@
         <v>125339503</v>
       </c>
       <c r="B197" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20303,7 +20303,7 @@
         <v>125339426</v>
       </c>
       <c r="B198" t="n">
-        <v>75066</v>
+        <v>75067</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -20502,7 +20502,7 @@
         <v>125340274</v>
       </c>
       <c r="B200" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -20698,32 +20698,32 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>125339670</v>
+        <v>125339448</v>
       </c>
       <c r="B202" t="n">
-        <v>8447</v>
+        <v>78968</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -20733,10 +20733,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>462858</v>
+        <v>462879</v>
       </c>
       <c r="R202" t="n">
-        <v>6769291</v>
+        <v>6769344</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -20769,11 +20769,6 @@
       <c r="AA202" t="inlineStr">
         <is>
           <t>2025-05-23</t>
-        </is>
-      </c>
-      <c r="AC202" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -20800,7 +20795,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>125339496</v>
+        <v>125339670</v>
       </c>
       <c r="B203" t="n">
         <v>8447</v>
@@ -20835,10 +20830,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>462897</v>
+        <v>462858</v>
       </c>
       <c r="R203" t="n">
-        <v>6769360</v>
+        <v>6769291</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -20871,6 +20866,11 @@
       <c r="AA203" t="inlineStr">
         <is>
           <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AC203" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -20897,45 +20897,45 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>125340174</v>
+        <v>125339496</v>
       </c>
       <c r="B204" t="n">
-        <v>78999</v>
+        <v>8447</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Lädsån, Dlr</t>
+          <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>462599</v>
+        <v>462897</v>
       </c>
       <c r="R204" t="n">
-        <v>6769078</v>
+        <v>6769360</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -20994,10 +20994,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>125339448</v>
+        <v>125340174</v>
       </c>
       <c r="B205" t="n">
-        <v>78967</v>
+        <v>79000</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -21005,34 +21005,34 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Salutjärnen, Dlr</t>
+          <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>462879</v>
+        <v>462599</v>
       </c>
       <c r="R205" t="n">
-        <v>6769344</v>
+        <v>6769078</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21094,7 +21094,7 @@
         <v>125017199</v>
       </c>
       <c r="B206" t="n">
-        <v>96575</v>
+        <v>96578</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>

--- a/artfynd/A 18527-2025 artfynd.xlsx
+++ b/artfynd/A 18527-2025 artfynd.xlsx
@@ -19024,32 +19024,32 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>125299647</v>
+        <v>125299886</v>
       </c>
       <c r="B185" t="n">
-        <v>78968</v>
+        <v>92518</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19059,10 +19059,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>462563</v>
+        <v>462462</v>
       </c>
       <c r="R185" t="n">
-        <v>6768994</v>
+        <v>6768859</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19121,32 +19121,32 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>125299886</v>
+        <v>125299647</v>
       </c>
       <c r="B186" t="n">
-        <v>92518</v>
+        <v>78968</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19156,10 +19156,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>462462</v>
+        <v>462563</v>
       </c>
       <c r="R186" t="n">
-        <v>6768859</v>
+        <v>6768994</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>

--- a/artfynd/A 18527-2025 artfynd.xlsx
+++ b/artfynd/A 18527-2025 artfynd.xlsx
@@ -19808,7 +19808,7 @@
         <v>125339979</v>
       </c>
       <c r="B193" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19902,7 +19902,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>125339821</v>
+        <v>125340065</v>
       </c>
       <c r="B194" t="n">
         <v>8447</v>
@@ -19931,16 +19931,21 @@
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P194" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>462779</v>
+        <v>462643</v>
       </c>
       <c r="R194" t="n">
-        <v>6769243</v>
+        <v>6769103</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -19975,11 +19980,6 @@
           <t>2025-05-23</t>
         </is>
       </c>
-      <c r="AC194" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD194" t="b">
         <v>0</v>
       </c>
@@ -19992,19 +19992,19 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>125340065</v>
+        <v>125339821</v>
       </c>
       <c r="B195" t="n">
         <v>8447</v>
@@ -20033,21 +20033,16 @@
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P195" t="inlineStr">
         <is>
           <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>462643</v>
+        <v>462779</v>
       </c>
       <c r="R195" t="n">
-        <v>6769103</v>
+        <v>6769243</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20082,6 +20077,11 @@
           <t>2025-05-23</t>
         </is>
       </c>
+      <c r="AC195" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD195" t="b">
         <v>0</v>
       </c>
@@ -20094,12 +20094,12 @@
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
@@ -20109,7 +20109,7 @@
         <v>125340372</v>
       </c>
       <c r="B196" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20206,7 +20206,7 @@
         <v>125339503</v>
       </c>
       <c r="B197" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20502,7 +20502,7 @@
         <v>125340274</v>
       </c>
       <c r="B200" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>125339448</v>
       </c>
       <c r="B202" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -20795,45 +20795,45 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>125339670</v>
+        <v>125340174</v>
       </c>
       <c r="B203" t="n">
-        <v>8447</v>
+        <v>79004</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Salutjärnen, Dlr</t>
+          <t>Lädsån, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>462858</v>
+        <v>462599</v>
       </c>
       <c r="R203" t="n">
-        <v>6769291</v>
+        <v>6769078</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -20866,11 +20866,6 @@
       <c r="AA203" t="inlineStr">
         <is>
           <t>2025-05-23</t>
-        </is>
-      </c>
-      <c r="AC203" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -20994,45 +20989,45 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>125340174</v>
+        <v>125339670</v>
       </c>
       <c r="B205" t="n">
-        <v>79000</v>
+        <v>8447</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Lädsån, Dlr</t>
+          <t>Salutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>462599</v>
+        <v>462858</v>
       </c>
       <c r="R205" t="n">
-        <v>6769078</v>
+        <v>6769291</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21065,6 +21060,11 @@
       <c r="AA205" t="inlineStr">
         <is>
           <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AC205" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -21094,7 +21094,7 @@
         <v>125017199</v>
       </c>
       <c r="B206" t="n">
-        <v>96578</v>
+        <v>96582</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>

--- a/artfynd/A 18527-2025 artfynd.xlsx
+++ b/artfynd/A 18527-2025 artfynd.xlsx
@@ -21094,7 +21094,7 @@
         <v>125017199</v>
       </c>
       <c r="B206" t="n">
-        <v>96582</v>
+        <v>96583</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>

--- a/artfynd/A 18527-2025 artfynd.xlsx
+++ b/artfynd/A 18527-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY206"/>
+  <dimension ref="A1:AY207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21191,6 +21191,108 @@
       </c>
       <c r="AY206" t="inlineStr"/>
     </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>132673840</v>
+      </c>
+      <c r="B207" t="n">
+        <v>96589</v>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>2170</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Dicranum flagellare</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr"/>
+      <c r="J207" t="inlineStr"/>
+      <c r="K207" t="inlineStr"/>
+      <c r="L207" t="inlineStr"/>
+      <c r="N207" t="inlineStr"/>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>Lädsån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q207" t="n">
+        <v>462437</v>
+      </c>
+      <c r="R207" t="n">
+        <v>6768755</v>
+      </c>
+      <c r="S207" t="n">
+        <v>25</v>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y207" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AD207" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE207" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF207" t="inlineStr"/>
+      <c r="AG207" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT207" t="inlineStr"/>
+      <c r="AW207" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AX207" t="inlineStr">
+        <is>
+          <t>Dennis Nyström, Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY207" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18527-2025 artfynd.xlsx
+++ b/artfynd/A 18527-2025 artfynd.xlsx
@@ -21196,7 +21196,7 @@
         <v>132673840</v>
       </c>
       <c r="B207" t="n">
-        <v>96589</v>
+        <v>96599</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>

--- a/artfynd/A 18527-2025 artfynd.xlsx
+++ b/artfynd/A 18527-2025 artfynd.xlsx
@@ -21196,7 +21196,7 @@
         <v>132673840</v>
       </c>
       <c r="B207" t="n">
-        <v>96599</v>
+        <v>96600</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>

--- a/artfynd/A 18527-2025 artfynd.xlsx
+++ b/artfynd/A 18527-2025 artfynd.xlsx
@@ -21196,7 +21196,7 @@
         <v>132673840</v>
       </c>
       <c r="B207" t="n">
-        <v>96600</v>
+        <v>96601</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>

--- a/artfynd/A 18527-2025 artfynd.xlsx
+++ b/artfynd/A 18527-2025 artfynd.xlsx
@@ -21196,7 +21196,7 @@
         <v>132673840</v>
       </c>
       <c r="B207" t="n">
-        <v>96601</v>
+        <v>96602</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>

--- a/artfynd/A 18527-2025 artfynd.xlsx
+++ b/artfynd/A 18527-2025 artfynd.xlsx
@@ -21196,7 +21196,7 @@
         <v>132673840</v>
       </c>
       <c r="B207" t="n">
-        <v>96602</v>
+        <v>96604</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>

--- a/artfynd/A 18527-2025 artfynd.xlsx
+++ b/artfynd/A 18527-2025 artfynd.xlsx
@@ -21196,7 +21196,7 @@
         <v>132673840</v>
       </c>
       <c r="B207" t="n">
-        <v>96604</v>
+        <v>96605</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>

--- a/artfynd/A 18527-2025 artfynd.xlsx
+++ b/artfynd/A 18527-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY267"/>
+  <dimension ref="A1:AZ267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017143</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017144</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017145</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017149</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017150</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017153</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017154</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017155</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017156</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125302019</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1744,6 +1799,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017199</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1841,6 +1901,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124999142</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1938,6 +2003,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017134</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2035,6 +2105,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017135</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2132,6 +2207,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017136</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2229,6 +2309,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017137</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2326,6 +2411,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017138</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2423,6 +2513,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017139</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2520,6 +2615,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017140</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2617,6 +2717,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017141</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2714,6 +2819,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017142</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2811,6 +2921,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125340174</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2908,6 +3023,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017269</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3005,6 +3125,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017270</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3102,6 +3227,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017271</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3199,6 +3329,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017273</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3296,6 +3431,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017274</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3393,6 +3533,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017275</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3490,6 +3635,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017276</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3587,6 +3737,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017277</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3684,6 +3839,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017278</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3781,6 +3941,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017279</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3878,6 +4043,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017202</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3975,6 +4145,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017232</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4072,6 +4247,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017167</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4169,6 +4349,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017170</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4266,6 +4451,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017171</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4363,6 +4553,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017284</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4460,6 +4655,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125301340</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4557,6 +4757,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017241</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4654,6 +4859,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125300490</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4751,6 +4961,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125300786</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4848,6 +5063,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125300882</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4945,6 +5165,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125301019</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5042,6 +5267,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125301107</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5139,6 +5369,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125301913</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5236,6 +5471,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017166</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5338,6 +5578,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132673840</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5440,6 +5685,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017227</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5542,6 +5792,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017228</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5639,6 +5894,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017280</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5736,6 +5996,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125300260</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5842,6 +6107,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017266</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5948,6 +6218,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017268</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6045,6 +6320,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125299810</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6142,6 +6422,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125299886</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6239,6 +6524,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125300055</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6342,6 +6632,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017285</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6439,6 +6734,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017157</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6536,6 +6836,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017158</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6633,6 +6938,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017160</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6730,6 +7040,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124771180</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6827,6 +7142,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124774056</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6924,6 +7244,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124774189</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7021,6 +7346,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124774463</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7118,6 +7448,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124774558</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7220,6 +7555,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124775105</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7317,6 +7657,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124775446</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7414,6 +7759,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124777471</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7516,6 +7866,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124778521</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7618,6 +7973,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124781860</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7715,6 +8075,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124781969</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7812,6 +8177,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124782138</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7909,6 +8279,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124782169</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8011,6 +8386,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124836271</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8108,6 +8488,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124837026</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8210,6 +8595,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124837260</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8307,6 +8697,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125000045</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8409,6 +8804,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125000794</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8506,6 +8906,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017244</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8603,6 +9008,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017245</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8700,6 +9110,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017246</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8797,6 +9212,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017247</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8894,6 +9314,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017249</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -8991,6 +9416,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017250</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9088,6 +9518,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017251</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9185,6 +9620,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017252</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9282,6 +9722,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017253</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9379,6 +9824,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017254</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9476,6 +9926,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017255</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9573,6 +10028,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017256</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9670,6 +10130,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017257</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9767,6 +10232,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017258</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9864,6 +10334,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017259</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -9961,6 +10436,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017260</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10058,6 +10538,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017261</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10155,6 +10640,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017262</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10252,6 +10742,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017263</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10349,6 +10844,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017264</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10446,6 +10946,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017265</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10543,6 +11048,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125299647</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10640,6 +11150,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125299980</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10742,6 +11257,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125300151</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -10839,6 +11359,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125300225</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -10936,6 +11461,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125302077</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11033,6 +11563,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125302283</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11130,6 +11665,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125302780</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11227,6 +11767,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125304145</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11324,6 +11869,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125339257</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11421,6 +11971,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125339268</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11518,6 +12073,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125339358</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11615,6 +12175,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125339375</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11712,6 +12277,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125339448</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -11809,6 +12379,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125339503</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -11906,6 +12481,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125339347</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12003,6 +12583,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125340452</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12100,6 +12685,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017282</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12197,6 +12787,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125340503</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12294,6 +12889,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124770579</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12391,6 +12991,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124772894</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12488,6 +13093,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124776376</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -12590,6 +13200,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124776534</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -12687,6 +13302,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124777178</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -12784,6 +13404,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125300481</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -12881,6 +13506,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125301015</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -12978,6 +13608,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125301166</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13075,6 +13710,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125301315</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13172,6 +13812,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125302067</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13269,6 +13914,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125302321</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13366,6 +14016,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125302464</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13463,6 +14118,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125302979</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -13560,6 +14220,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125303042</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -13657,6 +14322,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125303152</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -13754,6 +14424,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125303298</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -13851,6 +14526,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125303428</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -13948,6 +14628,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125303598</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14045,6 +14730,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125303878</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14142,6 +14832,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125304584</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14239,6 +14934,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125304744</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14336,6 +15036,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125339426</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -14438,6 +15143,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124834205</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -14540,6 +15250,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124836148</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -14642,6 +15357,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124836445</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -14739,6 +15459,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017234</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -14836,6 +15561,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017236</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -14933,6 +15663,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017237</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15030,6 +15765,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017238</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -15127,6 +15867,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125340464</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -15224,6 +15969,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124834191</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -15321,6 +16071,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124999240</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -15423,6 +16178,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124999607</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -15525,6 +16285,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125001145</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -15627,6 +16392,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125007547</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -15729,6 +16499,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125007648</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -15831,6 +16606,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125007719</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -15928,6 +16708,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017105</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -16025,6 +16810,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017106</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -16122,6 +16912,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017107</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -16219,6 +17014,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017108</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -16316,6 +17116,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017109</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -16413,6 +17218,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017110</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -16510,6 +17320,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017112</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -16607,6 +17422,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017113</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -16704,6 +17524,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017114</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -16801,6 +17626,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017115</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -16898,6 +17728,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017116</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -16995,6 +17830,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017117</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -17092,6 +17932,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017118</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -17189,6 +18034,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017119</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -17286,6 +18136,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017120</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -17383,6 +18238,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017121</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -17480,6 +18340,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017122</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -17577,6 +18442,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017123</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -17674,6 +18544,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017124</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -17771,6 +18646,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017125</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -17868,6 +18748,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017127</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -17965,6 +18850,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017128</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -18062,6 +18952,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017130</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -18159,6 +19054,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017162</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -18256,6 +19156,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125339979</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -18353,6 +19258,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125340274</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -18450,6 +19360,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125340310</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -18547,6 +19462,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125340372</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -18649,6 +19569,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017181</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -18751,6 +19676,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124770303</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -18858,6 +19788,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124770632</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -18965,6 +19900,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124772023</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -19072,6 +20012,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124772212</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -19174,6 +20119,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124773032</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -19281,6 +20231,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124773955</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -19383,6 +20338,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124774814</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -19485,6 +20445,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124774922</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -19592,6 +20557,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124775405</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -19694,6 +20664,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124776266</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -19801,6 +20776,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124777762</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -19908,6 +20888,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124778690</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -20010,6 +20995,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124781784</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -20112,6 +21102,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124781915</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -20214,6 +21209,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124838423</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -20316,6 +21316,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124999027</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -20418,6 +21423,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124999088</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -20520,6 +21530,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124999177</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -20622,6 +21637,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124999865</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -20724,6 +21744,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125000666</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -20831,6 +21856,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125001339</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -20938,6 +21968,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125001767</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -21045,6 +22080,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125004378</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -21151,6 +22191,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017186</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -21253,6 +22298,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017188</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -21355,6 +22405,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017190</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -21457,6 +22512,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017193</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -21559,6 +22619,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017195</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -21661,6 +22726,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017198</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -21768,6 +22838,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125000745</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -21870,6 +22945,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124782461</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -21977,6 +23057,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125001616</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -22079,6 +23164,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125001637</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -22181,6 +23271,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017173</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -22283,6 +23378,11 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017175</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -22385,6 +23485,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125299865</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -22497,6 +23602,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125305194</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -22599,6 +23709,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125339507</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -22696,6 +23811,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017230</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -22798,6 +23918,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124771314</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -22895,6 +24020,11 @@
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017177</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -22992,6 +24122,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017240</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -23089,6 +24224,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124774494</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -23186,6 +24326,11 @@
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124774845</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -23288,6 +24433,11 @@
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124774975</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -23385,6 +24535,11 @@
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124825418</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -23482,6 +24637,11 @@
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124833451</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -23584,6 +24744,11 @@
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124833941</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -23686,6 +24851,11 @@
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124835714</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -23788,6 +24958,11 @@
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124835908</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -23885,6 +25060,11 @@
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124999190</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -23987,6 +25167,11 @@
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124999425</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -24089,6 +25274,11 @@
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125000267</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -24191,6 +25381,11 @@
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017205</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -24293,6 +25488,11 @@
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017207</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -24395,6 +25595,11 @@
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017209</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -24497,6 +25702,11 @@
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017210</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -24599,6 +25809,11 @@
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017212</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -24701,6 +25916,11 @@
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017217</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -24803,6 +26023,11 @@
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017219</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -24905,6 +26130,11 @@
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017220</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -25007,6 +26237,11 @@
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017225</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -25104,6 +26339,11 @@
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125339496</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -25206,6 +26446,11 @@
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125339670</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -25308,6 +26553,11 @@
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125339782</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -25410,6 +26660,11 @@
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125339821</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -25512,6 +26767,11 @@
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125340065</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -25614,6 +26874,11 @@
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125340305</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -25716,6 +26981,11 @@
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125340565</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -25818,6 +27088,11 @@
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125340713</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -25924,6 +27199,11 @@
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017239</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -26021,6 +27301,11 @@
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125341141</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -26118,6 +27403,11 @@
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017204</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -26215,6 +27505,11 @@
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017185</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -26312,6 +27607,11 @@
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017224</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -26414,6 +27714,11 @@
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124836527</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -26520,6 +27825,11 @@
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017288</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -26621,6 +27931,11 @@
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132485849</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -26723,6 +28038,11 @@
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
+      <c r="AZ264" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124772690</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -26820,6 +28140,11 @@
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
+      <c r="AZ265" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124774260</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -26917,6 +28242,11 @@
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
+      <c r="AZ266" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125017178</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -27014,8 +28344,281 @@
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
+      <c r="AZ267" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125339321</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ267" r:id="rId266"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>